--- a/Personal_Money_Tracker_Braun.xlsx
+++ b/Personal_Money_Tracker_Braun.xlsx
@@ -22,13 +22,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="MMM YYYY"/>
-    <numFmt numFmtId="165" formatCode="D MMM"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="MMM YYYY"/>
+    <numFmt numFmtId="168" formatCode="D MMM"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,14 +57,8 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="006E6E6E"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="001A1A1A"/>
-      <sz val="16"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -73,8 +68,20 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00E35205"/>
-      <sz val="28"/>
+      <color rgb="006E6E6E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A1A1A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A1A1A"/>
+      <sz val="16"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -85,20 +92,8 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001A1A1A"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001A1A1A"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="006E6E6E"/>
-      <sz val="11"/>
+      <color rgb="00E35205"/>
+      <sz val="28"/>
     </font>
   </fonts>
   <fills count="3">
@@ -114,7 +109,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -132,80 +127,45 @@
         <color rgb="00D6D6D6"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00D6D6D6"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <right/>
-      <bottom style="thin">
-        <color rgb="00D6D6D6"/>
-      </bottom>
-    </border>
     <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -581,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -611,7 +571,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>One place to see what remains. Add spends on Log.</t>
+          <t>Bills (rent/subs) auto-count. You only log day-to-day on Log.</t>
         </is>
       </c>
     </row>
@@ -677,7 +637,7 @@
         <f>Balances!B5</f>
         <v/>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="10">
         <f>Balances!C5</f>
         <v/>
       </c>
@@ -696,14 +656,14 @@
         <f>Balances!B6</f>
         <v/>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="10">
         <f>Balances!C6</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="12">
-        <f>'Plan'!B20-B12</f>
+      <c r="A9" s="11">
+        <f>'Plan'!B20-'Plan'!B21-B12</f>
         <v/>
       </c>
       <c r="F9" s="9">
@@ -714,7 +674,7 @@
         <f>Balances!B7</f>
         <v/>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="10">
         <f>Balances!C7</f>
         <v/>
       </c>
@@ -722,7 +682,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Expected income minus expenses logged this month</t>
+          <t>Income − automatic bills − day-to-day logged this month</t>
         </is>
       </c>
       <c r="F10" s="9">
@@ -733,7 +693,7 @@
         <f>Balances!B8</f>
         <v/>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="10">
         <f>Balances!C8</f>
         <v/>
       </c>
@@ -746,10 +706,15 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>DAY-TO-DAY</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>BILLS (AUTO)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>NET LOGGED</t>
         </is>
@@ -762,21 +727,25 @@
         <f>Balances!B9</f>
         <v/>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="10">
         <f>Balances!C9</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13">
+      <c r="A12" s="12">
         <f>SUMIFS(Log!$C$5:$C$311,Log!$D$5:$D$311,"Income",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)</f>
         <v/>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="12">
         <f>SUMIFS(Log!$C$5:$C$311,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)</f>
         <v/>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="12">
+        <f>'Plan'!B21</f>
+        <v/>
+      </c>
+      <c r="D12" s="12">
         <f>A12-B12</f>
         <v/>
       </c>
@@ -788,7 +757,7 @@
         <f>Balances!B10</f>
         <v/>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="10">
         <f>Balances!C10</f>
         <v/>
       </c>
@@ -802,7 +771,7 @@
         <f>Balances!B11</f>
         <v/>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="10">
         <f>Balances!C11</f>
         <v/>
       </c>
@@ -821,7 +790,7 @@
         <f>Balances!B12</f>
         <v/>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="10">
         <f>Balances!C12</f>
         <v/>
       </c>
@@ -855,45 +824,45 @@
         <f>Balances!B13</f>
         <v/>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="10">
         <f>Balances!C13</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Rent</t>
         </is>
       </c>
-      <c r="B16" s="15">
-        <f>IFERROR(VLOOKUP(A16,Plan!$A$6:$B$19,2,FALSE),0)</f>
+      <c r="B16" s="13">
+        <f>IFERROR(VLOOKUP(A16,Plan!$A$6:$B$18,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="C16" s="16">
-        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A16,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)</f>
+      <c r="C16" s="10">
+        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A16,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)+IFERROR(VLOOKUP(A16,Plan!$H$6:$I$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="10">
         <f>B16-C16</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B17" s="15">
-        <f>IFERROR(VLOOKUP(A17,Plan!$A$6:$B$19,2,FALSE),0)</f>
+      <c r="B17" s="13">
+        <f>IFERROR(VLOOKUP(A17,Plan!$A$6:$B$18,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="C17" s="16">
-        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A17,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)</f>
+      <c r="C17" s="10">
+        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A17,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)+IFERROR(VLOOKUP(A17,Plan!$H$6:$I$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="10">
         <f>B17-C17</f>
         <v/>
       </c>
@@ -902,253 +871,251 @@
           <t>OWED TOTAL</t>
         </is>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="14">
         <f>Balances!B15</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Subscriptions</t>
         </is>
       </c>
-      <c r="B18" s="15">
-        <f>IFERROR(VLOOKUP(A18,Plan!$A$6:$B$19,2,FALSE),0)</f>
+      <c r="B18" s="13">
+        <f>IFERROR(VLOOKUP(A18,Plan!$A$6:$B$18,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="C18" s="16">
-        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A18,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)</f>
+      <c r="C18" s="10">
+        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A18,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)+IFERROR(VLOOKUP(A18,Plan!$H$6:$I$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="10">
         <f>B18-C18</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Grocery</t>
         </is>
       </c>
-      <c r="B19" s="15">
-        <f>IFERROR(VLOOKUP(A19,Plan!$A$6:$B$19,2,FALSE),0)</f>
+      <c r="B19" s="13">
+        <f>IFERROR(VLOOKUP(A19,Plan!$A$6:$B$18,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="C19" s="16">
-        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A19,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)</f>
+      <c r="C19" s="10">
+        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A19,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)+IFERROR(VLOOKUP(A19,Plan!$H$6:$I$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="10">
         <f>B19-C19</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Dining</t>
         </is>
       </c>
-      <c r="B20" s="15">
-        <f>IFERROR(VLOOKUP(A20,Plan!$A$6:$B$19,2,FALSE),0)</f>
+      <c r="B20" s="13">
+        <f>IFERROR(VLOOKUP(A20,Plan!$A$6:$B$18,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="C20" s="16">
-        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A20,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)</f>
+      <c r="C20" s="10">
+        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A20,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)+IFERROR(VLOOKUP(A20,Plan!$H$6:$I$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="10">
         <f>B20-C20</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Transit</t>
         </is>
       </c>
-      <c r="B21" s="15">
-        <f>IFERROR(VLOOKUP(A21,Plan!$A$6:$B$19,2,FALSE),0)</f>
+      <c r="B21" s="13">
+        <f>IFERROR(VLOOKUP(A21,Plan!$A$6:$B$18,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="C21" s="16">
-        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A21,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)</f>
+      <c r="C21" s="10">
+        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A21,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)+IFERROR(VLOOKUP(A21,Plan!$H$6:$I$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="10">
         <f>B21-C21</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Shopping</t>
         </is>
       </c>
-      <c r="B22" s="15">
-        <f>IFERROR(VLOOKUP(A22,Plan!$A$6:$B$19,2,FALSE),0)</f>
+      <c r="B22" s="13">
+        <f>IFERROR(VLOOKUP(A22,Plan!$A$6:$B$18,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="C22" s="16">
-        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A22,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)</f>
+      <c r="C22" s="10">
+        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A22,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)+IFERROR(VLOOKUP(A22,Plan!$H$6:$I$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="10">
         <f>B22-C22</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="B23" s="15">
-        <f>IFERROR(VLOOKUP(A23,Plan!$A$6:$B$19,2,FALSE),0)</f>
+      <c r="B23" s="13">
+        <f>IFERROR(VLOOKUP(A23,Plan!$A$6:$B$18,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="C23" s="16">
-        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A23,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)</f>
+      <c r="C23" s="10">
+        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A23,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)+IFERROR(VLOOKUP(A23,Plan!$H$6:$I$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="10">
         <f>B23-C23</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="14" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="B24" s="15">
-        <f>IFERROR(VLOOKUP(A24,Plan!$A$6:$B$19,2,FALSE),0)</f>
+      <c r="B24" s="13">
+        <f>IFERROR(VLOOKUP(A24,Plan!$A$6:$B$18,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="C24" s="16">
-        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A24,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)</f>
+      <c r="C24" s="10">
+        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A24,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)+IFERROR(VLOOKUP(A24,Plan!$H$6:$I$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="10">
         <f>B24-C24</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Health</t>
         </is>
       </c>
-      <c r="B25" s="15">
-        <f>IFERROR(VLOOKUP(A25,Plan!$A$6:$B$19,2,FALSE),0)</f>
+      <c r="B25" s="13">
+        <f>IFERROR(VLOOKUP(A25,Plan!$A$6:$B$18,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="C25" s="16">
-        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A25,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)</f>
+      <c r="C25" s="10">
+        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A25,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)+IFERROR(VLOOKUP(A25,Plan!$H$6:$I$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="10">
         <f>B25-C25</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="14" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="B26" s="15">
-        <f>IFERROR(VLOOKUP(A26,Plan!$A$6:$B$19,2,FALSE),0)</f>
+      <c r="B26" s="13">
+        <f>IFERROR(VLOOKUP(A26,Plan!$A$6:$B$18,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="C26" s="16">
-        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A26,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)</f>
+      <c r="C26" s="10">
+        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A26,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)+IFERROR(VLOOKUP(A26,Plan!$H$6:$I$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="10">
         <f>B26-C26</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="14" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Savings</t>
         </is>
       </c>
-      <c r="B27" s="15">
-        <f>IFERROR(VLOOKUP(A27,Plan!$A$6:$B$19,2,FALSE),0)</f>
+      <c r="B27" s="13">
+        <f>IFERROR(VLOOKUP(A27,Plan!$A$6:$B$18,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="C27" s="16">
-        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A27,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)</f>
+      <c r="C27" s="10">
+        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A27,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)+IFERROR(VLOOKUP(A27,Plan!$H$6:$I$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="10">
         <f>B27-C27</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="14" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Misc</t>
         </is>
       </c>
-      <c r="B28" s="15">
-        <f>IFERROR(VLOOKUP(A28,Plan!$A$6:$B$19,2,FALSE),0)</f>
+      <c r="B28" s="13">
+        <f>IFERROR(VLOOKUP(A28,Plan!$A$6:$B$18,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="C28" s="16">
-        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A28,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)</f>
+      <c r="C28" s="10">
+        <f>SUMIFS(Log!$C$5:$C$311,Log!$E$5:$E$311,A28,Log!$D$5:$D$311,"Expense",Log!$A$5:$A$311,"&gt;="&amp;$C$6,Log!$A$5:$A$311,"&lt;="&amp;$D$6)+IFERROR(VLOOKUP(A28,Plan!$H$6:$I$20,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="10">
         <f>B28-C28</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B29" s="19">
+      <c r="B29" s="16">
         <f>SUM(B16:B28)</f>
         <v/>
       </c>
-      <c r="C29" s="19">
+      <c r="C29" s="16">
         <f>SUM(C16:C28)</f>
         <v/>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="16">
         <f>B29-C29</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Edit year/month above · Log every purchase · Adjust Plan when life changes</t>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Flip month above · Log only day-to-day · Rent &amp; subs auto-count from Plan</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="3">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A35:D35"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <conditionalFormatting sqref="D16:D28">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
@@ -1179,7 +1146,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>MONEY</t>
         </is>
@@ -1195,376 +1162,376 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>New entries in the top rows. Amounts are always positive. Type sets Expense / Income / Transfer.</t>
+          <t>Day-to-day only (coffee, bodega, grocery, shopping). Rent &amp; subscriptions auto-count from Plan — do not log those here.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>WHAT</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>AMOUNT</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>CATEGORY</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>ACCOUNT</t>
         </is>
       </c>
-      <c r="G4" s="21" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>WHO</t>
         </is>
       </c>
-      <c r="H4" s="21" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="22" t="n"/>
-      <c r="B5" s="23" t="n"/>
-      <c r="C5" s="24" t="n"/>
-      <c r="D5" s="23" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E5" s="23" t="n"/>
-      <c r="F5" s="23" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="G5" s="23" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="17" t="n"/>
+      <c r="B5" s="18" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="n"/>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
         <is>
           <t>Roberto</t>
         </is>
       </c>
-      <c r="H5" s="23" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="22" t="n"/>
-      <c r="B6" s="23" t="n"/>
-      <c r="C6" s="24" t="n"/>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E6" s="23" t="n"/>
-      <c r="F6" s="23" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="G6" s="23" t="inlineStr">
+      <c r="H5" s="18" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="n"/>
+      <c r="B6" s="18" t="n"/>
+      <c r="C6" s="19" t="n"/>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="n"/>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t>Roberto</t>
         </is>
       </c>
-      <c r="H6" s="23" t="n"/>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="22" t="n"/>
-      <c r="B7" s="23" t="n"/>
-      <c r="C7" s="24" t="n"/>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="n"/>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="G7" s="23" t="inlineStr">
+      <c r="H6" s="18" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="n"/>
+      <c r="B7" s="18" t="n"/>
+      <c r="C7" s="19" t="n"/>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="n"/>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t>Roberto</t>
         </is>
       </c>
-      <c r="H7" s="23" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="22" t="n"/>
-      <c r="B8" s="23" t="n"/>
-      <c r="C8" s="24" t="n"/>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E8" s="23" t="n"/>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="H7" s="18" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="n"/>
+      <c r="B8" s="18" t="n"/>
+      <c r="C8" s="19" t="n"/>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>Roberto</t>
         </is>
       </c>
-      <c r="H8" s="23" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="22" t="n"/>
-      <c r="B9" s="23" t="n"/>
-      <c r="C9" s="24" t="n"/>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="n"/>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="H8" s="18" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n"/>
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="19" t="n"/>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>Roberto</t>
         </is>
       </c>
-      <c r="H9" s="23" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="23" t="n"/>
-      <c r="C10" s="24" t="n"/>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="n"/>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="H9" s="18" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n"/>
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>Roberto</t>
         </is>
       </c>
-      <c r="H10" s="23" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="22" t="n"/>
-      <c r="B11" s="23" t="n"/>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="n"/>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="G11" s="23" t="inlineStr">
+      <c r="H10" s="18" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n"/>
+      <c r="B11" s="18" t="n"/>
+      <c r="C11" s="19" t="n"/>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>Roberto</t>
         </is>
       </c>
-      <c r="H11" s="23" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="22" t="n"/>
-      <c r="B12" s="23" t="n"/>
-      <c r="C12" s="24" t="n"/>
-      <c r="D12" s="23" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="n"/>
-      <c r="F12" s="23" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="H11" s="18" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>Roberto</t>
         </is>
       </c>
-      <c r="H12" s="23" t="n"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="22" t="n"/>
-      <c r="B13" s="23" t="n"/>
-      <c r="C13" s="24" t="n"/>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="n"/>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="G13" s="23" t="inlineStr">
+      <c r="H12" s="18" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="n"/>
+      <c r="B13" s="18" t="n"/>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>Roberto</t>
         </is>
       </c>
-      <c r="H13" s="23" t="n"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="22" t="n"/>
-      <c r="B14" s="23" t="n"/>
-      <c r="C14" s="24" t="n"/>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="n"/>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="G14" s="23" t="inlineStr">
+      <c r="H13" s="18" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="n"/>
+      <c r="B14" s="18" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t>Roberto</t>
         </is>
       </c>
-      <c r="H14" s="23" t="n"/>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="22" t="n"/>
-      <c r="B15" s="23" t="n"/>
-      <c r="C15" s="24" t="n"/>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="n"/>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="G15" s="23" t="inlineStr">
+      <c r="H14" s="18" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="n"/>
+      <c r="B15" s="18" t="n"/>
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="inlineStr">
         <is>
           <t>Roberto</t>
         </is>
       </c>
-      <c r="H15" s="23" t="n"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="22" t="n"/>
-      <c r="B16" s="23" t="n"/>
-      <c r="C16" s="24" t="n"/>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="n"/>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="H15" s="18" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="n"/>
+      <c r="B16" s="18" t="n"/>
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>Roberto</t>
         </is>
       </c>
-      <c r="H16" s="23" t="n"/>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="22" t="n"/>
-      <c r="B17" s="23" t="n"/>
-      <c r="C17" s="24" t="n"/>
-      <c r="D17" s="23" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E17" s="23" t="n"/>
-      <c r="F17" s="23" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="G17" s="23" t="inlineStr">
+      <c r="H16" s="18" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="n"/>
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="G17" s="18" t="inlineStr">
         <is>
           <t>Roberto</t>
         </is>
       </c>
-      <c r="H17" s="23" t="n"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="22" t="n"/>
-      <c r="B18" s="23" t="n"/>
-      <c r="C18" s="24" t="n"/>
-      <c r="D18" s="23" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="E18" s="23" t="n"/>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="G18" s="23" t="inlineStr">
+      <c r="H17" s="18" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="n"/>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="n"/>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="inlineStr">
         <is>
           <t>Roberto</t>
         </is>
       </c>
-      <c r="H18" s="23" t="n"/>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="H18" s="18" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>HISTORY</t>
         </is>
       </c>
-      <c r="B19" s="36" t="n"/>
-      <c r="C19" s="37" t="n"/>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
-      <c r="G19" s="36" t="n"/>
-      <c r="H19" s="36" t="n"/>
-    </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="26" t="n">
+      <c r="B19" s="21" t="n"/>
+      <c r="C19" s="22" t="n"/>
+      <c r="D19" s="21" t="n"/>
+      <c r="E19" s="21" t="n"/>
+      <c r="F19" s="21" t="n"/>
+      <c r="G19" s="21" t="n"/>
+      <c r="H19" s="21" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="n">
         <v>46163</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -1572,7 +1539,7 @@
           <t>Cat food</t>
         </is>
       </c>
-      <c r="C20" s="10" t="n">
+      <c r="C20" s="24" t="n">
         <v>43.4</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
@@ -1593,8 +1560,8 @@
       <c r="G20" s="9" t="inlineStr"/>
       <c r="H20" s="9" t="n"/>
     </row>
-    <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="26" t="n">
+    <row r="21">
+      <c r="A21" s="23" t="n">
         <v>46163</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1602,7 +1569,7 @@
           <t>Amazon: Protein Bars</t>
         </is>
       </c>
-      <c r="C21" s="10" t="n">
+      <c r="C21" s="24" t="n">
         <v>14.99</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -1623,8 +1590,8 @@
       <c r="G21" s="9" t="inlineStr"/>
       <c r="H21" s="9" t="n"/>
     </row>
-    <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="26" t="n">
+    <row r="22">
+      <c r="A22" s="23" t="n">
         <v>46163</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -1632,7 +1599,7 @@
           <t>Grocery: City Fresh</t>
         </is>
       </c>
-      <c r="C22" s="10" t="n">
+      <c r="C22" s="24" t="n">
         <v>39.19</v>
       </c>
       <c r="D22" s="9" t="inlineStr">
@@ -1653,8 +1620,8 @@
       <c r="G22" s="9" t="inlineStr"/>
       <c r="H22" s="9" t="n"/>
     </row>
-    <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="26" t="n">
+    <row r="23">
+      <c r="A23" s="23" t="n">
         <v>46163</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1662,7 +1629,7 @@
           <t>Amazon: Toothpast, Chlorophyll, Oil sprayer</t>
         </is>
       </c>
-      <c r="C23" s="10" t="n">
+      <c r="C23" s="24" t="n">
         <v>51.01</v>
       </c>
       <c r="D23" s="9" t="inlineStr">
@@ -1683,8 +1650,8 @@
       <c r="G23" s="9" t="inlineStr"/>
       <c r="H23" s="9" t="n"/>
     </row>
-    <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="26" t="n">
+    <row r="24">
+      <c r="A24" s="23" t="n">
         <v>46163</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1692,7 +1659,7 @@
           <t>Grocery: Green Valley</t>
         </is>
       </c>
-      <c r="C24" s="10" t="n">
+      <c r="C24" s="24" t="n">
         <v>21.46</v>
       </c>
       <c r="D24" s="9" t="inlineStr">
@@ -1713,8 +1680,8 @@
       <c r="G24" s="9" t="inlineStr"/>
       <c r="H24" s="9" t="n"/>
     </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="26" t="n">
+    <row r="25">
+      <c r="A25" s="23" t="n">
         <v>46163</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -1722,7 +1689,7 @@
           <t>Rose Glycerin Spray</t>
         </is>
       </c>
-      <c r="C25" s="10" t="n">
+      <c r="C25" s="24" t="n">
         <v>11.94</v>
       </c>
       <c r="D25" s="9" t="inlineStr">
@@ -1743,8 +1710,8 @@
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="n"/>
     </row>
-    <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="26" t="n">
+    <row r="26">
+      <c r="A26" s="23" t="n">
         <v>46163</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1752,7 +1719,7 @@
           <t>Grocery: DoorDash</t>
         </is>
       </c>
-      <c r="C26" s="10" t="n">
+      <c r="C26" s="24" t="n">
         <v>86</v>
       </c>
       <c r="D26" s="9" t="inlineStr">
@@ -1773,8 +1740,8 @@
       <c r="G26" s="9" t="inlineStr"/>
       <c r="H26" s="9" t="n"/>
     </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="26" t="n">
+    <row r="27">
+      <c r="A27" s="23" t="n">
         <v>46163</v>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1782,7 +1749,7 @@
           <t>Klarna</t>
         </is>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C27" s="24" t="n">
         <v>134.75</v>
       </c>
       <c r="D27" s="9" t="inlineStr">
@@ -1803,8 +1770,8 @@
       <c r="G27" s="9" t="inlineStr"/>
       <c r="H27" s="9" t="n"/>
     </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="26" t="n">
+    <row r="28">
+      <c r="A28" s="23" t="n">
         <v>46125</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1812,7 +1779,7 @@
           <t>KLARNA*OVERSTOCK 041126</t>
         </is>
       </c>
-      <c r="C28" s="10" t="n">
+      <c r="C28" s="24" t="n">
         <v>134.75</v>
       </c>
       <c r="D28" s="9" t="inlineStr">
@@ -1833,8 +1800,8 @@
       <c r="G28" s="9" t="inlineStr"/>
       <c r="H28" s="9" t="n"/>
     </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="26" t="n">
+    <row r="29">
+      <c r="A29" s="23" t="n">
         <v>46125</v>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1842,7 +1809,7 @@
           <t>SQ *MILK &amp; PULL (RDG 041126</t>
         </is>
       </c>
-      <c r="C29" s="10" t="n">
+      <c r="C29" s="24" t="n">
         <v>6.8</v>
       </c>
       <c r="D29" s="9" t="inlineStr">
@@ -1863,8 +1830,8 @@
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="9" t="n"/>
     </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="26" t="n">
+    <row r="30">
+      <c r="A30" s="23" t="n">
         <v>46125</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -1872,7 +1839,7 @@
           <t>CITY FRESH MARKET PL 041026</t>
         </is>
       </c>
-      <c r="C30" s="10" t="n">
+      <c r="C30" s="24" t="n">
         <v>7.22</v>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -1893,8 +1860,8 @@
       <c r="G30" s="9" t="inlineStr"/>
       <c r="H30" s="9" t="n"/>
     </row>
-    <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="26" t="n">
+    <row r="31">
+      <c r="A31" s="23" t="n">
         <v>46125</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -1902,7 +1869,7 @@
           <t>BURGER KING #1898 041026</t>
         </is>
       </c>
-      <c r="C31" s="10" t="n">
+      <c r="C31" s="24" t="n">
         <v>12.17</v>
       </c>
       <c r="D31" s="9" t="inlineStr">
@@ -1923,8 +1890,8 @@
       <c r="G31" s="9" t="inlineStr"/>
       <c r="H31" s="9" t="n"/>
     </row>
-    <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="26" t="n">
+    <row r="32">
+      <c r="A32" s="23" t="n">
         <v>46120</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1932,7 +1899,7 @@
           <t>National Grid</t>
         </is>
       </c>
-      <c r="C32" s="10" t="n">
+      <c r="C32" s="24" t="n">
         <v>33.83</v>
       </c>
       <c r="D32" s="9" t="inlineStr">
@@ -1953,8 +1920,8 @@
       <c r="G32" s="9" t="inlineStr"/>
       <c r="H32" s="9" t="n"/>
     </row>
-    <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="26" t="n">
+    <row r="33">
+      <c r="A33" s="23" t="n">
         <v>46119</v>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1962,7 +1929,7 @@
           <t>Old Mill Cafe</t>
         </is>
       </c>
-      <c r="C33" s="10" t="n">
+      <c r="C33" s="24" t="n">
         <v>8.380000000000001</v>
       </c>
       <c r="D33" s="9" t="inlineStr">
@@ -1983,8 +1950,8 @@
       <c r="G33" s="9" t="inlineStr"/>
       <c r="H33" s="9" t="n"/>
     </row>
-    <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="26" t="n">
+    <row r="34">
+      <c r="A34" s="23" t="n">
         <v>46119</v>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1992,7 +1959,7 @@
           <t>Con Edison</t>
         </is>
       </c>
-      <c r="C34" s="10" t="n">
+      <c r="C34" s="24" t="n">
         <v>106.18</v>
       </c>
       <c r="D34" s="9" t="inlineStr">
@@ -2013,8 +1980,8 @@
       <c r="G34" s="9" t="inlineStr"/>
       <c r="H34" s="9" t="n"/>
     </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="26" t="n">
+    <row r="35">
+      <c r="A35" s="23" t="n">
         <v>46118</v>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -2022,7 +1989,7 @@
           <t>Google cloud</t>
         </is>
       </c>
-      <c r="C35" s="10" t="n">
+      <c r="C35" s="24" t="n">
         <v>82.20999999999999</v>
       </c>
       <c r="D35" s="9" t="inlineStr">
@@ -2043,8 +2010,8 @@
       <c r="G35" s="9" t="inlineStr"/>
       <c r="H35" s="9" t="n"/>
     </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="26" t="n">
+    <row r="36">
+      <c r="A36" s="23" t="n">
         <v>46118</v>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -2052,7 +2019,7 @@
           <t>Club entrance</t>
         </is>
       </c>
-      <c r="C36" s="10" t="n">
+      <c r="C36" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D36" s="9" t="inlineStr">
@@ -2073,8 +2040,8 @@
       <c r="G36" s="9" t="inlineStr"/>
       <c r="H36" s="9" t="n"/>
     </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="26" t="n">
+    <row r="37">
+      <c r="A37" s="23" t="n">
         <v>46118</v>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -2082,7 +2049,7 @@
           <t>Uber</t>
         </is>
       </c>
-      <c r="C37" s="10" t="n">
+      <c r="C37" s="24" t="n">
         <v>17.94</v>
       </c>
       <c r="D37" s="9" t="inlineStr">
@@ -2103,8 +2070,8 @@
       <c r="G37" s="9" t="inlineStr"/>
       <c r="H37" s="9" t="n"/>
     </row>
-    <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="26" t="n">
+    <row r="38">
+      <c r="A38" s="23" t="n">
         <v>46118</v>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -2112,7 +2079,7 @@
           <t>Wilson Express</t>
         </is>
       </c>
-      <c r="C38" s="10" t="n">
+      <c r="C38" s="24" t="n">
         <v>14.04</v>
       </c>
       <c r="D38" s="9" t="inlineStr">
@@ -2133,8 +2100,8 @@
       <c r="G38" s="9" t="inlineStr"/>
       <c r="H38" s="9" t="n"/>
     </row>
-    <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="26" t="n">
+    <row r="39">
+      <c r="A39" s="23" t="n">
         <v>46118</v>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -2142,7 +2109,7 @@
           <t>Transfer from Venmo</t>
         </is>
       </c>
-      <c r="C39" s="10" t="n">
+      <c r="C39" s="24" t="n">
         <v>38.57</v>
       </c>
       <c r="D39" s="9" t="inlineStr">
@@ -2163,8 +2130,8 @@
       <c r="G39" s="9" t="inlineStr"/>
       <c r="H39" s="9" t="n"/>
     </row>
-    <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="26" t="n">
+    <row r="40">
+      <c r="A40" s="23" t="n">
         <v>46115</v>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -2172,7 +2139,7 @@
           <t>bodega</t>
         </is>
       </c>
-      <c r="C40" s="10" t="n">
+      <c r="C40" s="24" t="n">
         <v>7.8</v>
       </c>
       <c r="D40" s="9" t="inlineStr">
@@ -2193,8 +2160,8 @@
       <c r="G40" s="9" t="inlineStr"/>
       <c r="H40" s="9" t="n"/>
     </row>
-    <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="26" t="n">
+    <row r="41">
+      <c r="A41" s="23" t="n">
         <v>46115</v>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -2202,7 +2169,7 @@
           <t>Wilson Express</t>
         </is>
       </c>
-      <c r="C41" s="10" t="n">
+      <c r="C41" s="24" t="n">
         <v>7.8</v>
       </c>
       <c r="D41" s="9" t="inlineStr">
@@ -2223,8 +2190,8 @@
       <c r="G41" s="9" t="inlineStr"/>
       <c r="H41" s="9" t="n"/>
     </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="26" t="n">
+    <row r="42">
+      <c r="A42" s="23" t="n">
         <v>46114</v>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -2232,7 +2199,7 @@
           <t>paypal payment</t>
         </is>
       </c>
-      <c r="C42" s="10" t="n">
+      <c r="C42" s="24" t="n">
         <v>78.34</v>
       </c>
       <c r="D42" s="9" t="inlineStr">
@@ -2253,8 +2220,8 @@
       <c r="G42" s="9" t="inlineStr"/>
       <c r="H42" s="9" t="n"/>
     </row>
-    <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="26" t="n">
+    <row r="43">
+      <c r="A43" s="23" t="n">
         <v>46114</v>
       </c>
       <c r="B43" s="9" t="inlineStr">
@@ -2262,7 +2229,7 @@
           <t>Apple Credit Card</t>
         </is>
       </c>
-      <c r="C43" s="10" t="n">
+      <c r="C43" s="24" t="n">
         <v>78.34</v>
       </c>
       <c r="D43" s="9" t="inlineStr">
@@ -2283,8 +2250,8 @@
       <c r="G43" s="9" t="inlineStr"/>
       <c r="H43" s="9" t="n"/>
     </row>
-    <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="26" t="n">
+    <row r="44">
+      <c r="A44" s="23" t="n">
         <v>46114</v>
       </c>
       <c r="B44" s="9" t="inlineStr">
@@ -2292,7 +2259,7 @@
           <t>Bilt</t>
         </is>
       </c>
-      <c r="C44" s="10" t="n">
+      <c r="C44" s="24" t="n">
         <v>69.92</v>
       </c>
       <c r="D44" s="9" t="inlineStr">
@@ -2313,8 +2280,8 @@
       <c r="G44" s="9" t="inlineStr"/>
       <c r="H44" s="9" t="n"/>
     </row>
-    <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="26" t="n">
+    <row r="45">
+      <c r="A45" s="23" t="n">
         <v>46113</v>
       </c>
       <c r="B45" s="9" t="inlineStr">
@@ -2322,7 +2289,7 @@
           <t>city fresh</t>
         </is>
       </c>
-      <c r="C45" s="10" t="n">
+      <c r="C45" s="24" t="n">
         <v>17.42</v>
       </c>
       <c r="D45" s="9" t="inlineStr">
@@ -2343,8 +2310,8 @@
       <c r="G45" s="9" t="inlineStr"/>
       <c r="H45" s="9" t="n"/>
     </row>
-    <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="26" t="n">
+    <row r="46">
+      <c r="A46" s="23" t="n">
         <v>46113</v>
       </c>
       <c r="B46" s="9" t="inlineStr">
@@ -2352,7 +2319,7 @@
           <t>AG Hardware</t>
         </is>
       </c>
-      <c r="C46" s="10" t="n">
+      <c r="C46" s="24" t="n">
         <v>34.07</v>
       </c>
       <c r="D46" s="9" t="inlineStr">
@@ -2373,8 +2340,8 @@
       <c r="G46" s="9" t="inlineStr"/>
       <c r="H46" s="9" t="n"/>
     </row>
-    <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="26" t="n">
+    <row r="47">
+      <c r="A47" s="23" t="n">
         <v>46113</v>
       </c>
       <c r="B47" s="9" t="inlineStr">
@@ -2382,7 +2349,7 @@
           <t>klarna</t>
         </is>
       </c>
-      <c r="C47" s="10" t="n">
+      <c r="C47" s="24" t="n">
         <v>134.74</v>
       </c>
       <c r="D47" s="9" t="inlineStr">
@@ -2403,8 +2370,8 @@
       <c r="G47" s="9" t="inlineStr"/>
       <c r="H47" s="9" t="n"/>
     </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="26" t="n">
+    <row r="48">
+      <c r="A48" s="23" t="n">
         <v>46113</v>
       </c>
       <c r="B48" s="9" t="inlineStr">
@@ -2412,7 +2379,7 @@
           <t>city fresh</t>
         </is>
       </c>
-      <c r="C48" s="10" t="n">
+      <c r="C48" s="24" t="n">
         <v>31.34</v>
       </c>
       <c r="D48" s="9" t="inlineStr">
@@ -2433,8 +2400,8 @@
       <c r="G48" s="9" t="inlineStr"/>
       <c r="H48" s="9" t="n"/>
     </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="26" t="n">
+    <row r="49">
+      <c r="A49" s="23" t="n">
         <v>46113</v>
       </c>
       <c r="B49" s="9" t="inlineStr">
@@ -2442,7 +2409,7 @@
           <t>bunker cafe</t>
         </is>
       </c>
-      <c r="C49" s="10" t="n">
+      <c r="C49" s="24" t="n">
         <v>8.359999999999999</v>
       </c>
       <c r="D49" s="9" t="inlineStr">
@@ -2463,8 +2430,8 @@
       <c r="G49" s="9" t="inlineStr"/>
       <c r="H49" s="9" t="n"/>
     </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="26" t="n">
+    <row r="50">
+      <c r="A50" s="23" t="n">
         <v>46113</v>
       </c>
       <c r="B50" s="9" t="inlineStr">
@@ -2472,7 +2439,7 @@
           <t>doordash/grocery</t>
         </is>
       </c>
-      <c r="C50" s="10" t="n">
+      <c r="C50" s="24" t="n">
         <v>109.72</v>
       </c>
       <c r="D50" s="9" t="inlineStr">
@@ -2493,8 +2460,8 @@
       <c r="G50" s="9" t="inlineStr"/>
       <c r="H50" s="9" t="n"/>
     </row>
-    <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="26" t="n">
+    <row r="51">
+      <c r="A51" s="23" t="n">
         <v>46113</v>
       </c>
       <c r="B51" s="9" t="inlineStr">
@@ -2502,7 +2469,7 @@
           <t>all night skate</t>
         </is>
       </c>
-      <c r="C51" s="10" t="n">
+      <c r="C51" s="24" t="n">
         <v>58.79</v>
       </c>
       <c r="D51" s="9" t="inlineStr">
@@ -2523,8 +2490,8 @@
       <c r="G51" s="9" t="inlineStr"/>
       <c r="H51" s="9" t="n"/>
     </row>
-    <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="26" t="n">
+    <row r="52">
+      <c r="A52" s="23" t="n">
         <v>46113</v>
       </c>
       <c r="B52" s="9" t="inlineStr">
@@ -2532,7 +2499,7 @@
           <t>tax hawk</t>
         </is>
       </c>
-      <c r="C52" s="10" t="n">
+      <c r="C52" s="24" t="n">
         <v>17.41</v>
       </c>
       <c r="D52" s="9" t="inlineStr">
@@ -2553,8 +2520,8 @@
       <c r="G52" s="9" t="inlineStr"/>
       <c r="H52" s="9" t="n"/>
     </row>
-    <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="26" t="n">
+    <row r="53">
+      <c r="A53" s="23" t="n">
         <v>46113</v>
       </c>
       <c r="B53" s="9" t="inlineStr">
@@ -2562,7 +2529,7 @@
           <t>bushniwa</t>
         </is>
       </c>
-      <c r="C53" s="10" t="n">
+      <c r="C53" s="24" t="n">
         <v>31.36</v>
       </c>
       <c r="D53" s="9" t="inlineStr">
@@ -2583,8 +2550,8 @@
       <c r="G53" s="9" t="inlineStr"/>
       <c r="H53" s="9" t="n"/>
     </row>
-    <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="26" t="n">
+    <row r="54">
+      <c r="A54" s="23" t="n">
         <v>46113</v>
       </c>
       <c r="B54" s="9" t="inlineStr">
@@ -2592,7 +2559,7 @@
           <t>dice</t>
         </is>
       </c>
-      <c r="C54" s="10" t="n">
+      <c r="C54" s="24" t="n">
         <v>17</v>
       </c>
       <c r="D54" s="9" t="inlineStr">
@@ -2613,8 +2580,8 @@
       <c r="G54" s="9" t="inlineStr"/>
       <c r="H54" s="9" t="n"/>
     </row>
-    <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="26" t="n">
+    <row r="55">
+      <c r="A55" s="23" t="n">
         <v>46113</v>
       </c>
       <c r="B55" s="9" t="inlineStr">
@@ -2622,7 +2589,7 @@
           <t>purgatory</t>
         </is>
       </c>
-      <c r="C55" s="10" t="n">
+      <c r="C55" s="24" t="n">
         <v>48</v>
       </c>
       <c r="D55" s="9" t="inlineStr">
@@ -2643,8 +2610,8 @@
       <c r="G55" s="9" t="inlineStr"/>
       <c r="H55" s="9" t="n"/>
     </row>
-    <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="26" t="n">
+    <row r="56">
+      <c r="A56" s="23" t="n">
         <v>46113</v>
       </c>
       <c r="B56" s="9" t="inlineStr">
@@ -2652,7 +2619,7 @@
           <t>bodega</t>
         </is>
       </c>
-      <c r="C56" s="10" t="n">
+      <c r="C56" s="24" t="n">
         <v>6.24</v>
       </c>
       <c r="D56" s="9" t="inlineStr">
@@ -2673,8 +2640,8 @@
       <c r="G56" s="9" t="inlineStr"/>
       <c r="H56" s="9" t="n"/>
     </row>
-    <row r="57" ht="17" customHeight="1">
-      <c r="A57" s="26" t="n">
+    <row r="57">
+      <c r="A57" s="23" t="n">
         <v>46113</v>
       </c>
       <c r="B57" s="9" t="inlineStr">
@@ -2682,7 +2649,7 @@
           <t>terra kaffe</t>
         </is>
       </c>
-      <c r="C57" s="10" t="n">
+      <c r="C57" s="24" t="n">
         <v>69.14</v>
       </c>
       <c r="D57" s="9" t="inlineStr">
@@ -2703,8 +2670,8 @@
       <c r="G57" s="9" t="inlineStr"/>
       <c r="H57" s="9" t="n"/>
     </row>
-    <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="26" t="n">
+    <row r="58">
+      <c r="A58" s="23" t="n">
         <v>46070</v>
       </c>
       <c r="B58" s="9" t="inlineStr">
@@ -2712,7 +2679,7 @@
           <t>Popeyes</t>
         </is>
       </c>
-      <c r="C58" s="10" t="n">
+      <c r="C58" s="24" t="n">
         <v>12.5</v>
       </c>
       <c r="D58" s="9" t="inlineStr">
@@ -2737,8 +2704,8 @@
       </c>
       <c r="H58" s="9" t="n"/>
     </row>
-    <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="26" t="n">
+    <row r="59">
+      <c r="A59" s="23" t="n">
         <v>46070</v>
       </c>
       <c r="B59" s="9" t="inlineStr">
@@ -2746,7 +2713,7 @@
           <t>Koneko</t>
         </is>
       </c>
-      <c r="C59" s="10" t="n">
+      <c r="C59" s="24" t="n">
         <v>19</v>
       </c>
       <c r="D59" s="9" t="inlineStr">
@@ -2771,8 +2738,8 @@
       </c>
       <c r="H59" s="9" t="n"/>
     </row>
-    <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="26" t="n">
+    <row r="60">
+      <c r="A60" s="23" t="n">
         <v>46068</v>
       </c>
       <c r="B60" s="9" t="inlineStr">
@@ -2780,7 +2747,7 @@
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C60" s="10" t="n">
+      <c r="C60" s="24" t="n">
         <v>9.16</v>
       </c>
       <c r="D60" s="9" t="inlineStr">
@@ -2805,8 +2772,8 @@
       </c>
       <c r="H60" s="9" t="n"/>
     </row>
-    <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="26" t="n">
+    <row r="61">
+      <c r="A61" s="23" t="n">
         <v>46068</v>
       </c>
       <c r="B61" s="9" t="inlineStr">
@@ -2814,7 +2781,7 @@
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C61" s="10" t="n">
+      <c r="C61" s="24" t="n">
         <v>19.54</v>
       </c>
       <c r="D61" s="9" t="inlineStr">
@@ -2839,8 +2806,8 @@
       </c>
       <c r="H61" s="9" t="n"/>
     </row>
-    <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="26" t="n">
+    <row r="62">
+      <c r="A62" s="23" t="n">
         <v>46068</v>
       </c>
       <c r="B62" s="9" t="inlineStr">
@@ -2848,7 +2815,7 @@
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C62" s="10" t="n">
+      <c r="C62" s="24" t="n">
         <v>9.449999999999999</v>
       </c>
       <c r="D62" s="9" t="inlineStr">
@@ -2873,8 +2840,8 @@
       </c>
       <c r="H62" s="9" t="n"/>
     </row>
-    <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="26" t="n">
+    <row r="63">
+      <c r="A63" s="23" t="n">
         <v>46066</v>
       </c>
       <c r="B63" s="9" t="inlineStr">
@@ -2882,7 +2849,7 @@
           <t>Bodgega</t>
         </is>
       </c>
-      <c r="C63" s="10" t="n">
+      <c r="C63" s="24" t="n">
         <v>5.2</v>
       </c>
       <c r="D63" s="9" t="inlineStr">
@@ -2907,8 +2874,8 @@
       </c>
       <c r="H63" s="9" t="n"/>
     </row>
-    <row r="64" ht="17" customHeight="1">
-      <c r="A64" s="26" t="n">
+    <row r="64">
+      <c r="A64" s="23" t="n">
         <v>46066</v>
       </c>
       <c r="B64" s="9" t="inlineStr">
@@ -2916,7 +2883,7 @@
           <t>Groceries</t>
         </is>
       </c>
-      <c r="C64" s="10" t="n">
+      <c r="C64" s="24" t="n">
         <v>70</v>
       </c>
       <c r="D64" s="9" t="inlineStr">
@@ -2937,8 +2904,8 @@
       <c r="G64" s="9" t="inlineStr"/>
       <c r="H64" s="9" t="n"/>
     </row>
-    <row r="65" ht="17" customHeight="1">
-      <c r="A65" s="26" t="n">
+    <row r="65">
+      <c r="A65" s="23" t="n">
         <v>46065</v>
       </c>
       <c r="B65" s="9" t="inlineStr">
@@ -2946,7 +2913,7 @@
           <t>City Fresh</t>
         </is>
       </c>
-      <c r="C65" s="10" t="n">
+      <c r="C65" s="24" t="n">
         <v>12.29</v>
       </c>
       <c r="D65" s="9" t="inlineStr">
@@ -2971,8 +2938,8 @@
       </c>
       <c r="H65" s="9" t="n"/>
     </row>
-    <row r="66" ht="17" customHeight="1">
-      <c r="A66" s="26" t="n">
+    <row r="66">
+      <c r="A66" s="23" t="n">
         <v>46064</v>
       </c>
       <c r="B66" s="9" t="inlineStr">
@@ -2980,7 +2947,7 @@
           <t>City Fresh</t>
         </is>
       </c>
-      <c r="C66" s="10" t="n">
+      <c r="C66" s="24" t="n">
         <v>34.18</v>
       </c>
       <c r="D66" s="9" t="inlineStr">
@@ -3005,8 +2972,8 @@
       </c>
       <c r="H66" s="9" t="n"/>
     </row>
-    <row r="67" ht="17" customHeight="1">
-      <c r="A67" s="26" t="n">
+    <row r="67">
+      <c r="A67" s="23" t="n">
         <v>46063</v>
       </c>
       <c r="B67" s="9" t="inlineStr">
@@ -3014,7 +2981,7 @@
           <t>Bodgega</t>
         </is>
       </c>
-      <c r="C67" s="10" t="n">
+      <c r="C67" s="24" t="n">
         <v>5.72</v>
       </c>
       <c r="D67" s="9" t="inlineStr">
@@ -3039,8 +3006,8 @@
       </c>
       <c r="H67" s="9" t="n"/>
     </row>
-    <row r="68" ht="17" customHeight="1">
-      <c r="A68" s="26" t="n">
+    <row r="68">
+      <c r="A68" s="23" t="n">
         <v>46063</v>
       </c>
       <c r="B68" s="9" t="inlineStr">
@@ -3048,7 +3015,7 @@
           <t>Tailor Home</t>
         </is>
       </c>
-      <c r="C68" s="10" t="n">
+      <c r="C68" s="24" t="n">
         <v>15.46</v>
       </c>
       <c r="D68" s="9" t="inlineStr">
@@ -3073,8 +3040,8 @@
       </c>
       <c r="H68" s="9" t="n"/>
     </row>
-    <row r="69" ht="17" customHeight="1">
-      <c r="A69" s="26" t="n">
+    <row r="69">
+      <c r="A69" s="23" t="n">
         <v>46063</v>
       </c>
       <c r="B69" s="9" t="inlineStr">
@@ -3082,7 +3049,7 @@
           <t>Pai ATM</t>
         </is>
       </c>
-      <c r="C69" s="10" t="n">
+      <c r="C69" s="24" t="n">
         <v>63.5</v>
       </c>
       <c r="D69" s="9" t="inlineStr">
@@ -3107,8 +3074,8 @@
       </c>
       <c r="H69" s="9" t="n"/>
     </row>
-    <row r="70" ht="17" customHeight="1">
-      <c r="A70" s="26" t="n">
+    <row r="70">
+      <c r="A70" s="23" t="n">
         <v>46063</v>
       </c>
       <c r="B70" s="9" t="inlineStr">
@@ -3116,7 +3083,7 @@
           <t>PostNet</t>
         </is>
       </c>
-      <c r="C70" s="10" t="n">
+      <c r="C70" s="24" t="n">
         <v>15.51</v>
       </c>
       <c r="D70" s="9" t="inlineStr">
@@ -3141,8 +3108,8 @@
       </c>
       <c r="H70" s="9" t="n"/>
     </row>
-    <row r="71" ht="17" customHeight="1">
-      <c r="A71" s="26" t="n">
+    <row r="71">
+      <c r="A71" s="23" t="n">
         <v>46063</v>
       </c>
       <c r="B71" s="9" t="inlineStr">
@@ -3150,7 +3117,7 @@
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C71" s="10" t="n">
+      <c r="C71" s="24" t="n">
         <v>11.94</v>
       </c>
       <c r="D71" s="9" t="inlineStr">
@@ -3175,8 +3142,8 @@
       </c>
       <c r="H71" s="9" t="n"/>
     </row>
-    <row r="72" ht="17" customHeight="1">
-      <c r="A72" s="26" t="n">
+    <row r="72">
+      <c r="A72" s="23" t="n">
         <v>46063</v>
       </c>
       <c r="B72" s="9" t="inlineStr">
@@ -3184,7 +3151,7 @@
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C72" s="10" t="n">
+      <c r="C72" s="24" t="n">
         <v>28.3</v>
       </c>
       <c r="D72" s="9" t="inlineStr">
@@ -3209,8 +3176,8 @@
       </c>
       <c r="H72" s="9" t="n"/>
     </row>
-    <row r="73" ht="17" customHeight="1">
-      <c r="A73" s="26" t="n">
+    <row r="73">
+      <c r="A73" s="23" t="n">
         <v>46063</v>
       </c>
       <c r="B73" s="9" t="inlineStr">
@@ -3218,7 +3185,7 @@
           <t>Angelika</t>
         </is>
       </c>
-      <c r="C73" s="10" t="n">
+      <c r="C73" s="24" t="n">
         <v>42.38</v>
       </c>
       <c r="D73" s="9" t="inlineStr">
@@ -3243,8 +3210,8 @@
       </c>
       <c r="H73" s="9" t="n"/>
     </row>
-    <row r="74" ht="17" customHeight="1">
-      <c r="A74" s="26" t="n">
+    <row r="74">
+      <c r="A74" s="23" t="n">
         <v>46062</v>
       </c>
       <c r="B74" s="9" t="inlineStr">
@@ -3252,7 +3219,7 @@
           <t>bodega</t>
         </is>
       </c>
-      <c r="C74" s="10" t="n">
+      <c r="C74" s="24" t="n">
         <v>3.12</v>
       </c>
       <c r="D74" s="9" t="inlineStr">
@@ -3277,8 +3244,8 @@
       </c>
       <c r="H74" s="9" t="n"/>
     </row>
-    <row r="75" ht="17" customHeight="1">
-      <c r="A75" s="26" t="n">
+    <row r="75">
+      <c r="A75" s="23" t="n">
         <v>46062</v>
       </c>
       <c r="B75" s="9" t="inlineStr">
@@ -3286,7 +3253,7 @@
           <t>city fresh</t>
         </is>
       </c>
-      <c r="C75" s="10" t="n">
+      <c r="C75" s="24" t="n">
         <v>3.99</v>
       </c>
       <c r="D75" s="9" t="inlineStr">
@@ -3311,8 +3278,8 @@
       </c>
       <c r="H75" s="9" t="n"/>
     </row>
-    <row r="76" ht="17" customHeight="1">
-      <c r="A76" s="26" t="n">
+    <row r="76">
+      <c r="A76" s="23" t="n">
         <v>46062</v>
       </c>
       <c r="B76" s="9" t="inlineStr">
@@ -3320,7 +3287,7 @@
           <t>3 diamond</t>
         </is>
       </c>
-      <c r="C76" s="10" t="n">
+      <c r="C76" s="24" t="n">
         <v>30.04</v>
       </c>
       <c r="D76" s="9" t="inlineStr">
@@ -3345,8 +3312,8 @@
       </c>
       <c r="H76" s="9" t="n"/>
     </row>
-    <row r="77" ht="17" customHeight="1">
-      <c r="A77" s="26" t="n">
+    <row r="77">
+      <c r="A77" s="23" t="n">
         <v>46062</v>
       </c>
       <c r="B77" s="9" t="inlineStr">
@@ -3354,7 +3321,7 @@
           <t>ayat</t>
         </is>
       </c>
-      <c r="C77" s="10" t="n">
+      <c r="C77" s="24" t="n">
         <v>35.4</v>
       </c>
       <c r="D77" s="9" t="inlineStr">
@@ -3379,8 +3346,8 @@
       </c>
       <c r="H77" s="9" t="n"/>
     </row>
-    <row r="78" ht="17" customHeight="1">
-      <c r="A78" s="26" t="n">
+    <row r="78">
+      <c r="A78" s="23" t="n">
         <v>46062</v>
       </c>
       <c r="B78" s="9" t="inlineStr">
@@ -3388,7 +3355,7 @@
           <t>nowhere</t>
         </is>
       </c>
-      <c r="C78" s="10" t="n">
+      <c r="C78" s="24" t="n">
         <v>54</v>
       </c>
       <c r="D78" s="9" t="inlineStr">
@@ -3413,8 +3380,8 @@
       </c>
       <c r="H78" s="9" t="n"/>
     </row>
-    <row r="79" ht="17" customHeight="1">
-      <c r="A79" s="26" t="n">
+    <row r="79">
+      <c r="A79" s="23" t="n">
         <v>46062</v>
       </c>
       <c r="B79" s="9" t="inlineStr">
@@ -3422,7 +3389,7 @@
           <t>Uber</t>
         </is>
       </c>
-      <c r="C79" s="10" t="n">
+      <c r="C79" s="24" t="n">
         <v>16.94</v>
       </c>
       <c r="D79" s="9" t="inlineStr">
@@ -3447,8 +3414,8 @@
       </c>
       <c r="H79" s="9" t="n"/>
     </row>
-    <row r="80" ht="17" customHeight="1">
-      <c r="A80" s="26" t="n">
+    <row r="80">
+      <c r="A80" s="23" t="n">
         <v>46062</v>
       </c>
       <c r="B80" s="9" t="inlineStr">
@@ -3456,7 +3423,7 @@
           <t>Ikea</t>
         </is>
       </c>
-      <c r="C80" s="10" t="n">
+      <c r="C80" s="24" t="n">
         <v>36.97</v>
       </c>
       <c r="D80" s="9" t="inlineStr">
@@ -3481,8 +3448,8 @@
       </c>
       <c r="H80" s="9" t="n"/>
     </row>
-    <row r="81" ht="17" customHeight="1">
-      <c r="A81" s="26" t="n">
+    <row r="81">
+      <c r="A81" s="23" t="n">
         <v>46062</v>
       </c>
       <c r="B81" s="9" t="inlineStr">
@@ -3490,7 +3457,7 @@
           <t>Staples</t>
         </is>
       </c>
-      <c r="C81" s="10" t="n">
+      <c r="C81" s="24" t="n">
         <v>23.7</v>
       </c>
       <c r="D81" s="9" t="inlineStr">
@@ -3515,8 +3482,8 @@
       </c>
       <c r="H81" s="9" t="n"/>
     </row>
-    <row r="82" ht="17" customHeight="1">
-      <c r="A82" s="26" t="n">
+    <row r="82">
+      <c r="A82" s="23" t="n">
         <v>46059</v>
       </c>
       <c r="B82" s="9" t="inlineStr">
@@ -3524,7 +3491,7 @@
           <t>playground bar</t>
         </is>
       </c>
-      <c r="C82" s="10" t="n">
+      <c r="C82" s="24" t="n">
         <v>9.17</v>
       </c>
       <c r="D82" s="9" t="inlineStr">
@@ -3549,8 +3516,8 @@
       </c>
       <c r="H82" s="9" t="n"/>
     </row>
-    <row r="83" ht="17" customHeight="1">
-      <c r="A83" s="26" t="n">
+    <row r="83">
+      <c r="A83" s="23" t="n">
         <v>46059</v>
       </c>
       <c r="B83" s="9" t="inlineStr">
@@ -3558,7 +3525,7 @@
           <t>city fresh</t>
         </is>
       </c>
-      <c r="C83" s="10" t="n">
+      <c r="C83" s="24" t="n">
         <v>12.47</v>
       </c>
       <c r="D83" s="9" t="inlineStr">
@@ -3583,8 +3550,8 @@
       </c>
       <c r="H83" s="9" t="n"/>
     </row>
-    <row r="84" ht="17" customHeight="1">
-      <c r="A84" s="26" t="n">
+    <row r="84">
+      <c r="A84" s="23" t="n">
         <v>46057</v>
       </c>
       <c r="B84" s="9" t="inlineStr">
@@ -3592,7 +3559,7 @@
           <t>sandbar</t>
         </is>
       </c>
-      <c r="C84" s="10" t="n">
+      <c r="C84" s="24" t="n">
         <v>39.6</v>
       </c>
       <c r="D84" s="9" t="inlineStr">
@@ -3617,8 +3584,8 @@
       </c>
       <c r="H84" s="9" t="n"/>
     </row>
-    <row r="85" ht="17" customHeight="1">
-      <c r="A85" s="26" t="n">
+    <row r="85">
+      <c r="A85" s="23" t="n">
         <v>46056</v>
       </c>
       <c r="B85" s="9" t="inlineStr">
@@ -3626,7 +3593,7 @@
           <t>amazon</t>
         </is>
       </c>
-      <c r="C85" s="10" t="n">
+      <c r="C85" s="24" t="n">
         <v>17.39</v>
       </c>
       <c r="D85" s="9" t="inlineStr">
@@ -3651,8 +3618,8 @@
       </c>
       <c r="H85" s="9" t="n"/>
     </row>
-    <row r="86" ht="17" customHeight="1">
-      <c r="A86" s="26" t="n">
+    <row r="86">
+      <c r="A86" s="23" t="n">
         <v>46055</v>
       </c>
       <c r="B86" s="9" t="inlineStr">
@@ -3660,7 +3627,7 @@
           <t>uber</t>
         </is>
       </c>
-      <c r="C86" s="10" t="n">
+      <c r="C86" s="24" t="n">
         <v>14.94</v>
       </c>
       <c r="D86" s="9" t="inlineStr">
@@ -3685,8 +3652,8 @@
       </c>
       <c r="H86" s="9" t="n"/>
     </row>
-    <row r="87" ht="17" customHeight="1">
-      <c r="A87" s="26" t="n">
+    <row r="87">
+      <c r="A87" s="23" t="n">
         <v>46055</v>
       </c>
       <c r="B87" s="9" t="inlineStr">
@@ -3694,7 +3661,7 @@
           <t>uber</t>
         </is>
       </c>
-      <c r="C87" s="10" t="n">
+      <c r="C87" s="24" t="n">
         <v>25.22</v>
       </c>
       <c r="D87" s="9" t="inlineStr">
@@ -3719,8 +3686,8 @@
       </c>
       <c r="H87" s="9" t="n"/>
     </row>
-    <row r="88" ht="17" customHeight="1">
-      <c r="A88" s="26" t="n">
+    <row r="88">
+      <c r="A88" s="23" t="n">
         <v>46040</v>
       </c>
       <c r="B88" s="9" t="inlineStr">
@@ -3728,7 +3695,7 @@
           <t>Vocal Lesson</t>
         </is>
       </c>
-      <c r="C88" s="10" t="n">
+      <c r="C88" s="24" t="n">
         <v>100</v>
       </c>
       <c r="D88" s="9" t="inlineStr">
@@ -3749,8 +3716,8 @@
       <c r="G88" s="9" t="inlineStr"/>
       <c r="H88" s="9" t="n"/>
     </row>
-    <row r="89" ht="17" customHeight="1">
-      <c r="A89" s="26" t="n">
+    <row r="89">
+      <c r="A89" s="23" t="n">
         <v>46040</v>
       </c>
       <c r="B89" s="9" t="inlineStr">
@@ -3758,7 +3725,7 @@
           <t>Grocery (Doordash)</t>
         </is>
       </c>
-      <c r="C89" s="10" t="n">
+      <c r="C89" s="24" t="n">
         <v>77.5</v>
       </c>
       <c r="D89" s="9" t="inlineStr">
@@ -3787,8 +3754,8 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="17" customHeight="1">
-      <c r="A90" s="26" t="n">
+    <row r="90">
+      <c r="A90" s="23" t="n">
         <v>46037</v>
       </c>
       <c r="B90" s="9" t="inlineStr">
@@ -3796,7 +3763,7 @@
           <t>amazon</t>
         </is>
       </c>
-      <c r="C90" s="10" t="n">
+      <c r="C90" s="24" t="n">
         <v>7.61</v>
       </c>
       <c r="D90" s="9" t="inlineStr">
@@ -3821,8 +3788,8 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="17" customHeight="1">
-      <c r="A91" s="26" t="n">
+    <row r="91">
+      <c r="A91" s="23" t="n">
         <v>46033</v>
       </c>
       <c r="B91" s="9" t="inlineStr">
@@ -3830,7 +3797,7 @@
           <t>Warby Parker (Cliff)</t>
         </is>
       </c>
-      <c r="C91" s="10" t="n">
+      <c r="C91" s="24" t="n">
         <v>235</v>
       </c>
       <c r="D91" s="9" t="inlineStr">
@@ -3851,8 +3818,8 @@
       <c r="G91" s="9" t="inlineStr"/>
       <c r="H91" s="9" t="n"/>
     </row>
-    <row r="92" ht="17" customHeight="1">
-      <c r="A92" s="26" t="n">
+    <row r="92">
+      <c r="A92" s="23" t="n">
         <v>46033</v>
       </c>
       <c r="B92" s="9" t="inlineStr">
@@ -3860,7 +3827,7 @@
           <t>uber to warby</t>
         </is>
       </c>
-      <c r="C92" s="10" t="n">
+      <c r="C92" s="24" t="n">
         <v>18.93</v>
       </c>
       <c r="D92" s="9" t="inlineStr">
@@ -3881,8 +3848,8 @@
       <c r="G92" s="9" t="inlineStr"/>
       <c r="H92" s="9" t="n"/>
     </row>
-    <row r="93" ht="17" customHeight="1">
-      <c r="A93" s="26" t="n">
+    <row r="93">
+      <c r="A93" s="23" t="n">
         <v>46027</v>
       </c>
       <c r="B93" s="9" t="inlineStr">
@@ -3890,7 +3857,7 @@
           <t>City Fresh</t>
         </is>
       </c>
-      <c r="C93" s="10" t="n">
+      <c r="C93" s="24" t="n">
         <v>15.74</v>
       </c>
       <c r="D93" s="9" t="inlineStr">
@@ -3911,8 +3878,8 @@
       <c r="G93" s="9" t="inlineStr"/>
       <c r="H93" s="9" t="n"/>
     </row>
-    <row r="94" ht="17" customHeight="1">
-      <c r="A94" s="26" t="n">
+    <row r="94">
+      <c r="A94" s="23" t="n">
         <v>46027</v>
       </c>
       <c r="B94" s="9" t="inlineStr">
@@ -3920,7 +3887,7 @@
           <t>Bodega</t>
         </is>
       </c>
-      <c r="C94" s="10" t="n">
+      <c r="C94" s="24" t="n">
         <v>17.86</v>
       </c>
       <c r="D94" s="9" t="inlineStr">
@@ -3941,8 +3908,8 @@
       <c r="G94" s="9" t="inlineStr"/>
       <c r="H94" s="9" t="n"/>
     </row>
-    <row r="95" ht="17" customHeight="1">
-      <c r="A95" s="26" t="n">
+    <row r="95">
+      <c r="A95" s="23" t="n">
         <v>46026</v>
       </c>
       <c r="B95" s="9" t="inlineStr">
@@ -3950,7 +3917,7 @@
           <t>amazon</t>
         </is>
       </c>
-      <c r="C95" s="10" t="n">
+      <c r="C95" s="24" t="n">
         <v>13.84</v>
       </c>
       <c r="D95" s="9" t="inlineStr">
@@ -3975,8 +3942,8 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="17" customHeight="1">
-      <c r="A96" s="26" t="n">
+    <row r="96">
+      <c r="A96" s="23" t="n">
         <v>46026</v>
       </c>
       <c r="B96" s="9" t="inlineStr">
@@ -3984,7 +3951,7 @@
           <t>amazon 2</t>
         </is>
       </c>
-      <c r="C96" s="10" t="n">
+      <c r="C96" s="24" t="n">
         <v>15.72</v>
       </c>
       <c r="D96" s="9" t="inlineStr">
@@ -4009,8 +3976,8 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="17" customHeight="1">
-      <c r="A97" s="26" t="n">
+    <row r="97">
+      <c r="A97" s="23" t="n">
         <v>46026</v>
       </c>
       <c r="B97" s="9" t="inlineStr">
@@ -4018,7 +3985,7 @@
           <t>amazon3</t>
         </is>
       </c>
-      <c r="C97" s="10" t="n">
+      <c r="C97" s="24" t="n">
         <v>14.14</v>
       </c>
       <c r="D97" s="9" t="inlineStr">
@@ -4043,8 +4010,8 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="17" customHeight="1">
-      <c r="A98" s="26" t="n">
+    <row r="98">
+      <c r="A98" s="23" t="n">
         <v>46026</v>
       </c>
       <c r="B98" s="9" t="inlineStr">
@@ -4052,7 +4019,7 @@
           <t>amazon 4</t>
         </is>
       </c>
-      <c r="C98" s="10" t="n">
+      <c r="C98" s="24" t="n">
         <v>6.85</v>
       </c>
       <c r="D98" s="9" t="inlineStr">
@@ -4077,8 +4044,8 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="17" customHeight="1">
-      <c r="A99" s="26" t="n">
+    <row r="99">
+      <c r="A99" s="23" t="n">
         <v>46026</v>
       </c>
       <c r="B99" s="9" t="inlineStr">
@@ -4086,7 +4053,7 @@
           <t>amazon 5</t>
         </is>
       </c>
-      <c r="C99" s="10" t="n">
+      <c r="C99" s="24" t="n">
         <v>7.61</v>
       </c>
       <c r="D99" s="9" t="inlineStr">
@@ -4111,8 +4078,8 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="17" customHeight="1">
-      <c r="A100" s="26" t="n">
+    <row r="100">
+      <c r="A100" s="23" t="n">
         <v>46026</v>
       </c>
       <c r="B100" s="9" t="inlineStr">
@@ -4120,7 +4087,7 @@
           <t>amazon 6</t>
         </is>
       </c>
-      <c r="C100" s="10" t="n">
+      <c r="C100" s="24" t="n">
         <v>97.93000000000001</v>
       </c>
       <c r="D100" s="9" t="inlineStr">
@@ -4145,8 +4112,8 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="17" customHeight="1">
-      <c r="A101" s="26" t="n">
+    <row r="101">
+      <c r="A101" s="23" t="n">
         <v>46026</v>
       </c>
       <c r="B101" s="9" t="inlineStr">
@@ -4154,7 +4121,7 @@
           <t>amazon 7</t>
         </is>
       </c>
-      <c r="C101" s="10" t="n">
+      <c r="C101" s="24" t="n">
         <v>10.88</v>
       </c>
       <c r="D101" s="9" t="inlineStr">
@@ -4179,8 +4146,8 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="17" customHeight="1">
-      <c r="A102" s="26" t="n">
+    <row r="102">
+      <c r="A102" s="23" t="n">
         <v>46026</v>
       </c>
       <c r="B102" s="9" t="inlineStr">
@@ -4188,7 +4155,7 @@
           <t>Radegast hall</t>
         </is>
       </c>
-      <c r="C102" s="10" t="n">
+      <c r="C102" s="24" t="n">
         <v>20.3</v>
       </c>
       <c r="D102" s="9" t="inlineStr">
@@ -4209,8 +4176,8 @@
       <c r="G102" s="9" t="inlineStr"/>
       <c r="H102" s="9" t="n"/>
     </row>
-    <row r="103" ht="17" customHeight="1">
-      <c r="A103" s="26" t="n">
+    <row r="103">
+      <c r="A103" s="23" t="n">
         <v>46026</v>
       </c>
       <c r="B103" s="9" t="inlineStr">
@@ -4218,7 +4185,7 @@
           <t>Home Depot</t>
         </is>
       </c>
-      <c r="C103" s="10" t="n">
+      <c r="C103" s="24" t="n">
         <v>18.4</v>
       </c>
       <c r="D103" s="9" t="inlineStr">
@@ -4239,8 +4206,8 @@
       <c r="G103" s="9" t="inlineStr"/>
       <c r="H103" s="9" t="n"/>
     </row>
-    <row r="104" ht="17" customHeight="1">
-      <c r="A104" s="26" t="n">
+    <row r="104">
+      <c r="A104" s="23" t="n">
         <v>46026</v>
       </c>
       <c r="B104" s="9" t="inlineStr">
@@ -4248,7 +4215,7 @@
           <t>Dollar Store</t>
         </is>
       </c>
-      <c r="C104" s="10" t="n">
+      <c r="C104" s="24" t="n">
         <v>20.65</v>
       </c>
       <c r="D104" s="9" t="inlineStr">
@@ -4269,8 +4236,8 @@
       <c r="G104" s="9" t="inlineStr"/>
       <c r="H104" s="9" t="n"/>
     </row>
-    <row r="105" ht="17" customHeight="1">
-      <c r="A105" s="26" t="n">
+    <row r="105">
+      <c r="A105" s="23" t="n">
         <v>46023</v>
       </c>
       <c r="B105" s="9" t="inlineStr">
@@ -4278,7 +4245,7 @@
           <t>Nook</t>
         </is>
       </c>
-      <c r="C105" s="10" t="n">
+      <c r="C105" s="24" t="n">
         <v>7.8</v>
       </c>
       <c r="D105" s="9" t="inlineStr">
@@ -4299,8 +4266,8 @@
       <c r="G105" s="9" t="inlineStr"/>
       <c r="H105" s="9" t="n"/>
     </row>
-    <row r="106" ht="17" customHeight="1">
-      <c r="A106" s="26" t="n">
+    <row r="106">
+      <c r="A106" s="23" t="n">
         <v>46023</v>
       </c>
       <c r="B106" s="9" t="inlineStr">
@@ -4308,7 +4275,7 @@
           <t>Caraotas</t>
         </is>
       </c>
-      <c r="C106" s="10" t="n">
+      <c r="C106" s="24" t="n">
         <v>50.36</v>
       </c>
       <c r="D106" s="9" t="inlineStr">
@@ -4329,8 +4296,8 @@
       <c r="G106" s="9" t="inlineStr"/>
       <c r="H106" s="9" t="n"/>
     </row>
-    <row r="107" ht="17" customHeight="1">
-      <c r="A107" s="26" t="n">
+    <row r="107">
+      <c r="A107" s="23" t="n">
         <v>46023</v>
       </c>
       <c r="B107" s="9" t="inlineStr">
@@ -4338,7 +4305,7 @@
           <t>Uber 1</t>
         </is>
       </c>
-      <c r="C107" s="10" t="n">
+      <c r="C107" s="24" t="n">
         <v>12.99</v>
       </c>
       <c r="D107" s="9" t="inlineStr">
@@ -4359,8 +4326,8 @@
       <c r="G107" s="9" t="inlineStr"/>
       <c r="H107" s="9" t="n"/>
     </row>
-    <row r="108" ht="17" customHeight="1">
-      <c r="A108" s="26" t="n">
+    <row r="108">
+      <c r="A108" s="23" t="n">
         <v>46023</v>
       </c>
       <c r="B108" s="9" t="inlineStr">
@@ -4368,7 +4335,7 @@
           <t>Uber 2</t>
         </is>
       </c>
-      <c r="C108" s="10" t="n">
+      <c r="C108" s="24" t="n">
         <v>20.61</v>
       </c>
       <c r="D108" s="9" t="inlineStr">
@@ -4389,8 +4356,8 @@
       <c r="G108" s="9" t="inlineStr"/>
       <c r="H108" s="9" t="n"/>
     </row>
-    <row r="109" ht="17" customHeight="1">
-      <c r="A109" s="26" t="n">
+    <row r="109">
+      <c r="A109" s="23" t="n">
         <v>46023</v>
       </c>
       <c r="B109" s="9" t="inlineStr">
@@ -4398,7 +4365,7 @@
           <t>Cat food + litter</t>
         </is>
       </c>
-      <c r="C109" s="10" t="n">
+      <c r="C109" s="24" t="n">
         <v>51.06</v>
       </c>
       <c r="D109" s="9" t="inlineStr">
@@ -4419,8 +4386,8 @@
       <c r="G109" s="9" t="inlineStr"/>
       <c r="H109" s="9" t="n"/>
     </row>
-    <row r="110" ht="17" customHeight="1">
-      <c r="A110" s="26" t="n">
+    <row r="110">
+      <c r="A110" s="23" t="n">
         <v>46023</v>
       </c>
       <c r="B110" s="9" t="inlineStr">
@@ -4428,7 +4395,7 @@
           <t>bodega</t>
         </is>
       </c>
-      <c r="C110" s="10" t="n">
+      <c r="C110" s="24" t="n">
         <v>17.86</v>
       </c>
       <c r="D110" s="9" t="inlineStr">
@@ -4449,8 +4416,8 @@
       <c r="G110" s="9" t="inlineStr"/>
       <c r="H110" s="9" t="n"/>
     </row>
-    <row r="111" ht="17" customHeight="1">
-      <c r="A111" s="26" t="n">
+    <row r="111">
+      <c r="A111" s="23" t="n">
         <v>46023</v>
       </c>
       <c r="B111" s="9" t="inlineStr">
@@ -4458,7 +4425,7 @@
           <t>the craic</t>
         </is>
       </c>
-      <c r="C111" s="10" t="n">
+      <c r="C111" s="24" t="n">
         <v>39.12</v>
       </c>
       <c r="D111" s="9" t="inlineStr">
@@ -4479,8 +4446,8 @@
       <c r="G111" s="9" t="inlineStr"/>
       <c r="H111" s="9" t="n"/>
     </row>
-    <row r="112" ht="17" customHeight="1">
-      <c r="A112" s="26" t="n">
+    <row r="112">
+      <c r="A112" s="23" t="n">
         <v>46023</v>
       </c>
       <c r="B112" s="9" t="inlineStr">
@@ -4488,7 +4455,7 @@
           <t>amazon</t>
         </is>
       </c>
-      <c r="C112" s="10" t="n">
+      <c r="C112" s="24" t="n">
         <v>22.82</v>
       </c>
       <c r="D112" s="9" t="inlineStr">
@@ -4513,8 +4480,8 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="17" customHeight="1">
-      <c r="A113" s="26" t="n">
+    <row r="113">
+      <c r="A113" s="23" t="n">
         <v>46023</v>
       </c>
       <c r="B113" s="9" t="inlineStr">
@@ -4522,7 +4489,7 @@
           <t>Late to work bag</t>
         </is>
       </c>
-      <c r="C113" s="10" t="n">
+      <c r="C113" s="24" t="n">
         <v>279.91</v>
       </c>
       <c r="D113" s="9" t="inlineStr">
@@ -4543,8 +4510,8 @@
       <c r="G113" s="9" t="inlineStr"/>
       <c r="H113" s="9" t="n"/>
     </row>
-    <row r="114" ht="17" customHeight="1">
-      <c r="A114" s="26" t="n">
+    <row r="114">
+      <c r="A114" s="23" t="n">
         <v>46006</v>
       </c>
       <c r="B114" s="9" t="inlineStr">
@@ -4552,7 +4519,7 @@
           <t>Shell</t>
         </is>
       </c>
-      <c r="C114" s="10" t="n">
+      <c r="C114" s="24" t="n">
         <v>17.48</v>
       </c>
       <c r="D114" s="9" t="inlineStr">
@@ -4573,8 +4540,8 @@
       <c r="G114" s="9" t="inlineStr"/>
       <c r="H114" s="9" t="n"/>
     </row>
-    <row r="115" ht="17" customHeight="1">
-      <c r="A115" s="26" t="n">
+    <row r="115">
+      <c r="A115" s="23" t="n">
         <v>46006</v>
       </c>
       <c r="B115" s="9" t="inlineStr">
@@ -4582,7 +4549,7 @@
           <t>Nectar</t>
         </is>
       </c>
-      <c r="C115" s="10" t="n">
+      <c r="C115" s="24" t="n">
         <v>21.72</v>
       </c>
       <c r="D115" s="9" t="inlineStr">
@@ -4603,8 +4570,8 @@
       <c r="G115" s="9" t="inlineStr"/>
       <c r="H115" s="9" t="n"/>
     </row>
-    <row r="116" ht="17" customHeight="1">
-      <c r="A116" s="26" t="n">
+    <row r="116">
+      <c r="A116" s="23" t="n">
         <v>46006</v>
       </c>
       <c r="B116" s="9" t="inlineStr">
@@ -4612,7 +4579,7 @@
           <t>ATM</t>
         </is>
       </c>
-      <c r="C116" s="10" t="n">
+      <c r="C116" s="24" t="n">
         <v>23</v>
       </c>
       <c r="D116" s="9" t="inlineStr">
@@ -4633,8 +4600,8 @@
       <c r="G116" s="9" t="inlineStr"/>
       <c r="H116" s="9" t="n"/>
     </row>
-    <row r="117" ht="17" customHeight="1">
-      <c r="A117" s="26" t="n">
+    <row r="117">
+      <c r="A117" s="23" t="n">
         <v>46005</v>
       </c>
       <c r="B117" s="9" t="inlineStr">
@@ -4642,7 +4609,7 @@
           <t>McDonalds</t>
         </is>
       </c>
-      <c r="C117" s="10" t="n">
+      <c r="C117" s="24" t="n">
         <v>6.45</v>
       </c>
       <c r="D117" s="9" t="inlineStr">
@@ -4663,8 +4630,8 @@
       <c r="G117" s="9" t="inlineStr"/>
       <c r="H117" s="9" t="n"/>
     </row>
-    <row r="118" ht="17" customHeight="1">
-      <c r="A118" s="26" t="n">
+    <row r="118">
+      <c r="A118" s="23" t="n">
         <v>46005</v>
       </c>
       <c r="B118" s="9" t="inlineStr">
@@ -4672,7 +4639,7 @@
           <t>Dose</t>
         </is>
       </c>
-      <c r="C118" s="10" t="n">
+      <c r="C118" s="24" t="n">
         <v>7.58</v>
       </c>
       <c r="D118" s="9" t="inlineStr">
@@ -4693,8 +4660,8 @@
       <c r="G118" s="9" t="inlineStr"/>
       <c r="H118" s="9" t="n"/>
     </row>
-    <row r="119" ht="17" customHeight="1">
-      <c r="A119" s="26" t="n">
+    <row r="119">
+      <c r="A119" s="23" t="n">
         <v>46005</v>
       </c>
       <c r="B119" s="9" t="inlineStr">
@@ -4702,7 +4669,7 @@
           <t>Play</t>
         </is>
       </c>
-      <c r="C119" s="10" t="n">
+      <c r="C119" s="24" t="n">
         <v>13.12</v>
       </c>
       <c r="D119" s="9" t="inlineStr">
@@ -4723,8 +4690,8 @@
       <c r="G119" s="9" t="inlineStr"/>
       <c r="H119" s="9" t="n"/>
     </row>
-    <row r="120" ht="17" customHeight="1">
-      <c r="A120" s="26" t="n">
+    <row r="120">
+      <c r="A120" s="23" t="n">
         <v>46005</v>
       </c>
       <c r="B120" s="9" t="inlineStr">
@@ -4732,7 +4699,7 @@
           <t>Eastside Bowl</t>
         </is>
       </c>
-      <c r="C120" s="10" t="n">
+      <c r="C120" s="24" t="n">
         <v>14.7</v>
       </c>
       <c r="D120" s="9" t="inlineStr">
@@ -4753,8 +4720,8 @@
       <c r="G120" s="9" t="inlineStr"/>
       <c r="H120" s="9" t="n"/>
     </row>
-    <row r="121" ht="17" customHeight="1">
-      <c r="A121" s="26" t="n">
+    <row r="121">
+      <c r="A121" s="23" t="n">
         <v>46004</v>
       </c>
       <c r="B121" s="9" t="inlineStr">
@@ -4762,7 +4729,7 @@
           <t>Turnip Truck</t>
         </is>
       </c>
-      <c r="C121" s="10" t="n">
+      <c r="C121" s="24" t="n">
         <v>14.25</v>
       </c>
       <c r="D121" s="9" t="inlineStr">
@@ -4783,8 +4750,8 @@
       <c r="G121" s="9" t="inlineStr"/>
       <c r="H121" s="9" t="n"/>
     </row>
-    <row r="122" ht="17" customHeight="1">
-      <c r="A122" s="26" t="n">
+    <row r="122">
+      <c r="A122" s="23" t="n">
         <v>46004</v>
       </c>
       <c r="B122" s="9" t="inlineStr">
@@ -4792,7 +4759,7 @@
           <t>WeGo</t>
         </is>
       </c>
-      <c r="C122" s="10" t="n">
+      <c r="C122" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D122" s="9" t="inlineStr">
@@ -4813,8 +4780,8 @@
       <c r="G122" s="9" t="inlineStr"/>
       <c r="H122" s="9" t="n"/>
     </row>
-    <row r="123" ht="17" customHeight="1">
-      <c r="A123" s="26" t="n">
+    <row r="123">
+      <c r="A123" s="23" t="n">
         <v>46004</v>
       </c>
       <c r="B123" s="9" t="inlineStr">
@@ -4822,7 +4789,7 @@
           <t>Something</t>
         </is>
       </c>
-      <c r="C123" s="10" t="n">
+      <c r="C123" s="24" t="n">
         <v>5.26</v>
       </c>
       <c r="D123" s="9" t="inlineStr">
@@ -4843,8 +4810,8 @@
       <c r="G123" s="9" t="inlineStr"/>
       <c r="H123" s="9" t="n"/>
     </row>
-    <row r="124" ht="17" customHeight="1">
-      <c r="A124" s="26" t="n">
+    <row r="124">
+      <c r="A124" s="23" t="n">
         <v>46004</v>
       </c>
       <c r="B124" s="9" t="inlineStr">
@@ -4852,7 +4819,7 @@
           <t>Parking</t>
         </is>
       </c>
-      <c r="C124" s="10" t="n">
+      <c r="C124" s="24" t="n">
         <v>6</v>
       </c>
       <c r="D124" s="9" t="inlineStr">
@@ -4873,8 +4840,8 @@
       <c r="G124" s="9" t="inlineStr"/>
       <c r="H124" s="9" t="n"/>
     </row>
-    <row r="125" ht="17" customHeight="1">
-      <c r="A125" s="26" t="n">
+    <row r="125">
+      <c r="A125" s="23" t="n">
         <v>46003</v>
       </c>
       <c r="B125" s="9" t="inlineStr">
@@ -4882,7 +4849,7 @@
           <t>Tower</t>
         </is>
       </c>
-      <c r="C125" s="10" t="n">
+      <c r="C125" s="24" t="n">
         <v>7.14</v>
       </c>
       <c r="D125" s="9" t="inlineStr">
@@ -4903,8 +4870,8 @@
       <c r="G125" s="9" t="inlineStr"/>
       <c r="H125" s="9" t="n"/>
     </row>
-    <row r="126" ht="17" customHeight="1">
-      <c r="A126" s="26" t="n">
+    <row r="126">
+      <c r="A126" s="23" t="n">
         <v>46003</v>
       </c>
       <c r="B126" s="9" t="inlineStr">
@@ -4912,7 +4879,7 @@
           <t>Retrograde</t>
         </is>
       </c>
-      <c r="C126" s="10" t="n">
+      <c r="C126" s="24" t="n">
         <v>8.31</v>
       </c>
       <c r="D126" s="9" t="inlineStr">
@@ -4933,8 +4900,8 @@
       <c r="G126" s="9" t="inlineStr"/>
       <c r="H126" s="9" t="n"/>
     </row>
-    <row r="127" ht="17" customHeight="1">
-      <c r="A127" s="26" t="n">
+    <row r="127">
+      <c r="A127" s="23" t="n">
         <v>46003</v>
       </c>
       <c r="B127" s="9" t="inlineStr">
@@ -4942,7 +4909,7 @@
           <t>Mcdonalds</t>
         </is>
       </c>
-      <c r="C127" s="10" t="n">
+      <c r="C127" s="24" t="n">
         <v>9.41</v>
       </c>
       <c r="D127" s="9" t="inlineStr">
@@ -4963,8 +4930,8 @@
       <c r="G127" s="9" t="inlineStr"/>
       <c r="H127" s="9" t="n"/>
     </row>
-    <row r="128" ht="17" customHeight="1">
-      <c r="A128" s="26" t="n">
+    <row r="128">
+      <c r="A128" s="23" t="n">
         <v>46003</v>
       </c>
       <c r="B128" s="9" t="inlineStr">
@@ -4972,7 +4939,7 @@
           <t>Low Bar</t>
         </is>
       </c>
-      <c r="C128" s="10" t="n">
+      <c r="C128" s="24" t="n">
         <v>10.86</v>
       </c>
       <c r="D128" s="9" t="inlineStr">
@@ -4993,8 +4960,8 @@
       <c r="G128" s="9" t="inlineStr"/>
       <c r="H128" s="9" t="n"/>
     </row>
-    <row r="129" ht="17" customHeight="1">
-      <c r="A129" s="26" t="n">
+    <row r="129">
+      <c r="A129" s="23" t="n">
         <v>46002</v>
       </c>
       <c r="B129" s="9" t="inlineStr">
@@ -5002,7 +4969,7 @@
           <t>Mcdonalds</t>
         </is>
       </c>
-      <c r="C129" s="10" t="n">
+      <c r="C129" s="24" t="n">
         <v>9.73</v>
       </c>
       <c r="D129" s="9" t="inlineStr">
@@ -5023,8 +4990,8 @@
       <c r="G129" s="9" t="inlineStr"/>
       <c r="H129" s="9" t="n"/>
     </row>
-    <row r="130" ht="17" customHeight="1">
-      <c r="A130" s="26" t="n">
+    <row r="130">
+      <c r="A130" s="23" t="n">
         <v>46002</v>
       </c>
       <c r="B130" s="9" t="inlineStr">
@@ -5032,7 +4999,7 @@
           <t>Tower</t>
         </is>
       </c>
-      <c r="C130" s="10" t="n">
+      <c r="C130" s="24" t="n">
         <v>11.57</v>
       </c>
       <c r="D130" s="9" t="inlineStr">
@@ -5053,8 +5020,8 @@
       <c r="G130" s="9" t="inlineStr"/>
       <c r="H130" s="9" t="n"/>
     </row>
-    <row r="131" ht="17" customHeight="1">
-      <c r="A131" s="26" t="n">
+    <row r="131">
+      <c r="A131" s="23" t="n">
         <v>46002</v>
       </c>
       <c r="B131" s="9" t="inlineStr">
@@ -5062,7 +5029,7 @@
           <t>Radish</t>
         </is>
       </c>
-      <c r="C131" s="10" t="n">
+      <c r="C131" s="24" t="n">
         <v>17.46</v>
       </c>
       <c r="D131" s="9" t="inlineStr">
@@ -5083,8 +5050,8 @@
       <c r="G131" s="9" t="inlineStr"/>
       <c r="H131" s="9" t="n"/>
     </row>
-    <row r="132" ht="17" customHeight="1">
-      <c r="A132" s="26" t="n">
+    <row r="132">
+      <c r="A132" s="23" t="n">
         <v>46002</v>
       </c>
       <c r="B132" s="9" t="inlineStr">
@@ -5092,7 +5059,7 @@
           <t>Uber</t>
         </is>
       </c>
-      <c r="C132" s="10" t="n">
+      <c r="C132" s="24" t="n">
         <v>16.16</v>
       </c>
       <c r="D132" s="9" t="inlineStr">
@@ -5113,8 +5080,8 @@
       <c r="G132" s="9" t="inlineStr"/>
       <c r="H132" s="9" t="n"/>
     </row>
-    <row r="133" ht="17" customHeight="1">
-      <c r="A133" s="26" t="n">
+    <row r="133">
+      <c r="A133" s="23" t="n">
         <v>46001</v>
       </c>
       <c r="B133" s="9" t="inlineStr">
@@ -5122,7 +5089,7 @@
           <t>Lyft</t>
         </is>
       </c>
-      <c r="C133" s="10" t="n">
+      <c r="C133" s="24" t="n">
         <v>7</v>
       </c>
       <c r="D133" s="9" t="inlineStr">
@@ -5143,8 +5110,8 @@
       <c r="G133" s="9" t="inlineStr"/>
       <c r="H133" s="9" t="n"/>
     </row>
-    <row r="134" ht="17" customHeight="1">
-      <c r="A134" s="26" t="n">
+    <row r="134">
+      <c r="A134" s="23" t="n">
         <v>46001</v>
       </c>
       <c r="B134" s="9" t="inlineStr">
@@ -5152,7 +5119,7 @@
           <t>Nashville WeGo</t>
         </is>
       </c>
-      <c r="C134" s="10" t="n">
+      <c r="C134" s="24" t="n">
         <v>6</v>
       </c>
       <c r="D134" s="9" t="inlineStr">
@@ -5173,8 +5140,8 @@
       <c r="G134" s="9" t="inlineStr"/>
       <c r="H134" s="9" t="n"/>
     </row>
-    <row r="135" ht="17" customHeight="1">
-      <c r="A135" s="26" t="n">
+    <row r="135">
+      <c r="A135" s="23" t="n">
         <v>46001</v>
       </c>
       <c r="B135" s="9" t="inlineStr">
@@ -5182,7 +5149,7 @@
           <t>The Horn Cafe</t>
         </is>
       </c>
-      <c r="C135" s="10" t="n">
+      <c r="C135" s="24" t="n">
         <v>7.09</v>
       </c>
       <c r="D135" s="9" t="inlineStr">
@@ -5203,8 +5170,8 @@
       <c r="G135" s="9" t="inlineStr"/>
       <c r="H135" s="9" t="n"/>
     </row>
-    <row r="136" ht="17" customHeight="1">
-      <c r="A136" s="26" t="n">
+    <row r="136">
+      <c r="A136" s="23" t="n">
         <v>46001</v>
       </c>
       <c r="B136" s="9" t="inlineStr">
@@ -5212,7 +5179,7 @@
           <t>Kyuramen</t>
         </is>
       </c>
-      <c r="C136" s="10" t="n">
+      <c r="C136" s="24" t="n">
         <v>36.23</v>
       </c>
       <c r="D136" s="9" t="inlineStr">
@@ -5233,8 +5200,8 @@
       <c r="G136" s="9" t="inlineStr"/>
       <c r="H136" s="9" t="n"/>
     </row>
-    <row r="137" ht="17" customHeight="1">
-      <c r="A137" s="26" t="n">
+    <row r="137">
+      <c r="A137" s="23" t="n">
         <v>46001</v>
       </c>
       <c r="B137" s="9" t="inlineStr">
@@ -5242,7 +5209,7 @@
           <t>Mama Bread</t>
         </is>
       </c>
-      <c r="C137" s="10" t="n">
+      <c r="C137" s="24" t="n">
         <v>8.73</v>
       </c>
       <c r="D137" s="9" t="inlineStr">
@@ -5263,8 +5230,8 @@
       <c r="G137" s="9" t="inlineStr"/>
       <c r="H137" s="9" t="n"/>
     </row>
-    <row r="138" ht="17" customHeight="1">
-      <c r="A138" s="26" t="n">
+    <row r="138">
+      <c r="A138" s="23" t="n">
         <v>46001</v>
       </c>
       <c r="B138" s="9" t="inlineStr">
@@ -5272,7 +5239,7 @@
           <t>Van Leeuwen</t>
         </is>
       </c>
-      <c r="C138" s="10" t="n">
+      <c r="C138" s="24" t="n">
         <v>8.24</v>
       </c>
       <c r="D138" s="9" t="inlineStr">
@@ -5293,8 +5260,8 @@
       <c r="G138" s="9" t="inlineStr"/>
       <c r="H138" s="9" t="n"/>
     </row>
-    <row r="139" ht="17" customHeight="1">
-      <c r="A139" s="26" t="n">
+    <row r="139">
+      <c r="A139" s="23" t="n">
         <v>46001</v>
       </c>
       <c r="B139" s="9" t="inlineStr">
@@ -5302,7 +5269,7 @@
           <t>Belcourt Theatre</t>
         </is>
       </c>
-      <c r="C139" s="10" t="n">
+      <c r="C139" s="24" t="n">
         <v>27</v>
       </c>
       <c r="D139" s="9" t="inlineStr">
@@ -5323,8 +5290,8 @@
       <c r="G139" s="9" t="inlineStr"/>
       <c r="H139" s="9" t="n"/>
     </row>
-    <row r="140" ht="17" customHeight="1">
-      <c r="A140" s="26" t="n">
+    <row r="140">
+      <c r="A140" s="23" t="n">
         <v>46001</v>
       </c>
       <c r="B140" s="9" t="inlineStr">
@@ -5332,7 +5299,7 @@
           <t>Groceries bar</t>
         </is>
       </c>
-      <c r="C140" s="10" t="n">
+      <c r="C140" s="24" t="n">
         <v>45</v>
       </c>
       <c r="D140" s="9" t="inlineStr">
@@ -5353,8 +5320,8 @@
       <c r="G140" s="9" t="inlineStr"/>
       <c r="H140" s="9" t="n"/>
     </row>
-    <row r="141" ht="17" customHeight="1">
-      <c r="A141" s="26" t="n">
+    <row r="141">
+      <c r="A141" s="23" t="n">
         <v>46000</v>
       </c>
       <c r="B141" s="9" t="inlineStr">
@@ -5362,7 +5329,7 @@
           <t>Paypal payment</t>
         </is>
       </c>
-      <c r="C141" s="10" t="n">
+      <c r="C141" s="24" t="n">
         <v>24</v>
       </c>
       <c r="D141" s="9" t="inlineStr">
@@ -5383,8 +5350,8 @@
       <c r="G141" s="9" t="inlineStr"/>
       <c r="H141" s="9" t="n"/>
     </row>
-    <row r="142" ht="17" customHeight="1">
-      <c r="A142" s="26" t="n">
+    <row r="142">
+      <c r="A142" s="23" t="n">
         <v>46000</v>
       </c>
       <c r="B142" s="9" t="inlineStr">
@@ -5392,7 +5359,7 @@
           <t>Uber from ai</t>
         </is>
       </c>
-      <c r="C142" s="10" t="n">
+      <c r="C142" s="24" t="n">
         <v>21</v>
       </c>
       <c r="D142" s="9" t="inlineStr">
@@ -5413,8 +5380,8 @@
       <c r="G142" s="9" t="inlineStr"/>
       <c r="H142" s="9" t="n"/>
     </row>
-    <row r="143" ht="17" customHeight="1">
-      <c r="A143" s="26" t="n">
+    <row r="143">
+      <c r="A143" s="23" t="n">
         <v>46000</v>
       </c>
       <c r="B143" s="9" t="inlineStr">
@@ -5422,7 +5389,7 @@
           <t>Turo car rental</t>
         </is>
       </c>
-      <c r="C143" s="10" t="n">
+      <c r="C143" s="24" t="n">
         <v>408</v>
       </c>
       <c r="D143" s="9" t="inlineStr">
@@ -5443,8 +5410,8 @@
       <c r="G143" s="9" t="inlineStr"/>
       <c r="H143" s="9" t="n"/>
     </row>
-    <row r="144" ht="17" customHeight="1">
-      <c r="A144" s="26" t="n">
+    <row r="144">
+      <c r="A144" s="23" t="n">
         <v>46000</v>
       </c>
       <c r="B144" s="9" t="inlineStr">
@@ -5452,7 +5419,7 @@
           <t>Uber holiday party 1</t>
         </is>
       </c>
-      <c r="C144" s="10" t="n">
+      <c r="C144" s="24" t="n">
         <v>8</v>
       </c>
       <c r="D144" s="9" t="inlineStr">
@@ -5473,8 +5440,8 @@
       <c r="G144" s="9" t="inlineStr"/>
       <c r="H144" s="9" t="n"/>
     </row>
-    <row r="145" ht="17" customHeight="1">
-      <c r="A145" s="26" t="n">
+    <row r="145">
+      <c r="A145" s="23" t="n">
         <v>46000</v>
       </c>
       <c r="B145" s="9" t="inlineStr">
@@ -5482,7 +5449,7 @@
           <t>Uber holiday party 2</t>
         </is>
       </c>
-      <c r="C145" s="10" t="n">
+      <c r="C145" s="24" t="n">
         <v>7</v>
       </c>
       <c r="D145" s="9" t="inlineStr">
@@ -5503,8 +5470,8 @@
       <c r="G145" s="9" t="inlineStr"/>
       <c r="H145" s="9" t="n"/>
     </row>
-    <row r="146" ht="17" customHeight="1">
-      <c r="A146" s="26" t="n">
+    <row r="146">
+      <c r="A146" s="23" t="n">
         <v>46000</v>
       </c>
       <c r="B146" s="9" t="inlineStr">
@@ -5512,7 +5479,7 @@
           <t>Taco Bell</t>
         </is>
       </c>
-      <c r="C146" s="10" t="n">
+      <c r="C146" s="24" t="n">
         <v>18</v>
       </c>
       <c r="D146" s="9" t="inlineStr">
@@ -5533,8 +5500,8 @@
       <c r="G146" s="9" t="inlineStr"/>
       <c r="H146" s="9" t="n"/>
     </row>
-    <row r="147" ht="17" customHeight="1">
-      <c r="A147" s="26" t="n">
+    <row r="147">
+      <c r="A147" s="23" t="n">
         <v>45999</v>
       </c>
       <c r="B147" s="9" t="inlineStr">
@@ -5542,7 +5509,7 @@
           <t>LGA Airport food</t>
         </is>
       </c>
-      <c r="C147" s="10" t="n">
+      <c r="C147" s="24" t="n">
         <v>12</v>
       </c>
       <c r="D147" s="9" t="inlineStr">
@@ -5563,8 +5530,8 @@
       <c r="G147" s="9" t="inlineStr"/>
       <c r="H147" s="9" t="n"/>
     </row>
-    <row r="148" ht="17" customHeight="1">
-      <c r="A148" s="26" t="n">
+    <row r="148">
+      <c r="A148" s="23" t="n">
         <v>45999</v>
       </c>
       <c r="B148" s="9" t="inlineStr">
@@ -5572,7 +5539,7 @@
           <t>Barista Parlor</t>
         </is>
       </c>
-      <c r="C148" s="10" t="n">
+      <c r="C148" s="24" t="n">
         <v>8</v>
       </c>
       <c r="D148" s="9" t="inlineStr">
@@ -5593,8 +5560,8 @@
       <c r="G148" s="9" t="inlineStr"/>
       <c r="H148" s="9" t="n"/>
     </row>
-    <row r="149" ht="17" customHeight="1">
-      <c r="A149" s="26" t="n">
+    <row r="149">
+      <c r="A149" s="23" t="n">
         <v>45999</v>
       </c>
       <c r="B149" s="9" t="inlineStr">
@@ -5602,7 +5569,7 @@
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="C149" s="10" t="n">
+      <c r="C149" s="24" t="n">
         <v>17</v>
       </c>
       <c r="D149" s="9" t="inlineStr">
@@ -5623,8 +5590,8 @@
       <c r="G149" s="9" t="inlineStr"/>
       <c r="H149" s="9" t="n"/>
     </row>
-    <row r="150" ht="17" customHeight="1">
-      <c r="A150" s="26" t="n">
+    <row r="150">
+      <c r="A150" s="23" t="n">
         <v>45999</v>
       </c>
       <c r="B150" s="9" t="inlineStr">
@@ -5632,7 +5599,7 @@
           <t>Sprouts</t>
         </is>
       </c>
-      <c r="C150" s="10" t="n">
+      <c r="C150" s="24" t="n">
         <v>25</v>
       </c>
       <c r="D150" s="9" t="inlineStr">
@@ -5653,8 +5620,8 @@
       <c r="G150" s="9" t="inlineStr"/>
       <c r="H150" s="9" t="n"/>
     </row>
-    <row r="151" ht="17" customHeight="1">
-      <c r="A151" s="26" t="n">
+    <row r="151">
+      <c r="A151" s="23" t="n">
         <v>45999</v>
       </c>
       <c r="B151" s="9" t="inlineStr">
@@ -5662,7 +5629,7 @@
           <t>Dollar general</t>
         </is>
       </c>
-      <c r="C151" s="10" t="n">
+      <c r="C151" s="24" t="n">
         <v>9</v>
       </c>
       <c r="D151" s="9" t="inlineStr">
@@ -5683,8 +5650,8 @@
       <c r="G151" s="9" t="inlineStr"/>
       <c r="H151" s="9" t="n"/>
     </row>
-    <row r="152" ht="17" customHeight="1">
-      <c r="A152" s="26" t="n">
+    <row r="152">
+      <c r="A152" s="23" t="n">
         <v>45999</v>
       </c>
       <c r="B152" s="9" t="inlineStr">
@@ -5692,7 +5659,7 @@
           <t>Osa Coffe</t>
         </is>
       </c>
-      <c r="C152" s="10" t="n">
+      <c r="C152" s="24" t="n">
         <v>10.1</v>
       </c>
       <c r="D152" s="9" t="inlineStr">
@@ -5713,8 +5680,8 @@
       <c r="G152" s="9" t="inlineStr"/>
       <c r="H152" s="9" t="n"/>
     </row>
-    <row r="153" ht="17" customHeight="1">
-      <c r="A153" s="26" t="n">
+    <row r="153">
+      <c r="A153" s="23" t="n">
         <v>45998</v>
       </c>
       <c r="B153" s="9" t="inlineStr">
@@ -5722,7 +5689,7 @@
           <t>Publix</t>
         </is>
       </c>
-      <c r="C153" s="10" t="n">
+      <c r="C153" s="24" t="n">
         <v>41.12</v>
       </c>
       <c r="D153" s="9" t="inlineStr">
@@ -5743,8 +5710,8 @@
       <c r="G153" s="9" t="inlineStr"/>
       <c r="H153" s="9" t="n"/>
     </row>
-    <row r="154" ht="17" customHeight="1">
-      <c r="A154" s="26" t="n">
+    <row r="154">
+      <c r="A154" s="23" t="n">
         <v>45996</v>
       </c>
       <c r="B154" s="9" t="inlineStr">
@@ -5752,7 +5719,7 @@
           <t>Uber to LH Nashville</t>
         </is>
       </c>
-      <c r="C154" s="10" t="n">
+      <c r="C154" s="24" t="n">
         <v>21</v>
       </c>
       <c r="D154" s="9" t="inlineStr">
@@ -5773,8 +5740,8 @@
       <c r="G154" s="9" t="inlineStr"/>
       <c r="H154" s="9" t="n"/>
     </row>
-    <row r="155" ht="17" customHeight="1">
-      <c r="A155" s="26" t="n">
+    <row r="155">
+      <c r="A155" s="23" t="n">
         <v>45995</v>
       </c>
       <c r="B155" s="9" t="inlineStr">
@@ -5782,7 +5749,7 @@
           <t>Glasses Appt</t>
         </is>
       </c>
-      <c r="C155" s="10" t="n">
+      <c r="C155" s="24" t="n">
         <v>319.2</v>
       </c>
       <c r="D155" s="9" t="inlineStr">
@@ -5807,8 +5774,8 @@
       </c>
       <c r="H155" s="9" t="n"/>
     </row>
-    <row r="156" ht="17" customHeight="1">
-      <c r="A156" s="26" t="n">
+    <row r="156">
+      <c r="A156" s="23" t="n">
         <v>45994</v>
       </c>
       <c r="B156" s="9" t="inlineStr">
@@ -5816,7 +5783,7 @@
           <t>Bass Guitar Repair</t>
         </is>
       </c>
-      <c r="C156" s="10" t="n">
+      <c r="C156" s="24" t="n">
         <v>150</v>
       </c>
       <c r="D156" s="9" t="inlineStr">
@@ -5841,8 +5808,8 @@
       </c>
       <c r="H156" s="9" t="n"/>
     </row>
-    <row r="157" ht="17" customHeight="1">
-      <c r="A157" s="26" t="n">
+    <row r="157">
+      <c r="A157" s="23" t="n">
         <v>45993</v>
       </c>
       <c r="B157" s="9" t="inlineStr">
@@ -5850,7 +5817,7 @@
           <t>Animal (Bar)</t>
         </is>
       </c>
-      <c r="C157" s="10" t="n">
+      <c r="C157" s="24" t="n">
         <v>12</v>
       </c>
       <c r="D157" s="9" t="inlineStr">
@@ -5875,8 +5842,8 @@
       </c>
       <c r="H157" s="9" t="n"/>
     </row>
-    <row r="158" ht="17" customHeight="1">
-      <c r="A158" s="26" t="n">
+    <row r="158">
+      <c r="A158" s="23" t="n">
         <v>45993</v>
       </c>
       <c r="B158" s="9" t="inlineStr">
@@ -5884,7 +5851,7 @@
           <t>Bodega</t>
         </is>
       </c>
-      <c r="C158" s="10" t="n">
+      <c r="C158" s="24" t="n">
         <v>8</v>
       </c>
       <c r="D158" s="9" t="inlineStr">
@@ -5909,8 +5876,8 @@
       </c>
       <c r="H158" s="9" t="n"/>
     </row>
-    <row r="159" ht="17" customHeight="1">
-      <c r="A159" s="26" t="n">
+    <row r="159">
+      <c r="A159" s="23" t="n">
         <v>45992</v>
       </c>
       <c r="B159" s="9" t="inlineStr">
@@ -5918,7 +5885,7 @@
           <t>Curtains</t>
         </is>
       </c>
-      <c r="C159" s="10" t="n">
+      <c r="C159" s="24" t="n">
         <v>80</v>
       </c>
       <c r="D159" s="9" t="inlineStr">
@@ -5943,8 +5910,8 @@
       </c>
       <c r="H159" s="9" t="n"/>
     </row>
-    <row r="160" ht="17" customHeight="1">
-      <c r="A160" s="26" t="n">
+    <row r="160">
+      <c r="A160" s="23" t="n">
         <v>45992</v>
       </c>
       <c r="B160" s="9" t="inlineStr">
@@ -5952,7 +5919,7 @@
           <t>Adam T5v Monitors</t>
         </is>
       </c>
-      <c r="C160" s="10" t="n">
+      <c r="C160" s="24" t="n">
         <v>270</v>
       </c>
       <c r="D160" s="9" t="inlineStr">
@@ -5977,8 +5944,8 @@
       </c>
       <c r="H160" s="9" t="n"/>
     </row>
-    <row r="161" ht="17" customHeight="1">
-      <c r="A161" s="26" t="n">
+    <row r="161">
+      <c r="A161" s="23" t="n">
         <v>45992</v>
       </c>
       <c r="B161" s="9" t="inlineStr">
@@ -5986,7 +5953,7 @@
           <t>Grocery (Doordash)</t>
         </is>
       </c>
-      <c r="C161" s="10" t="n">
+      <c r="C161" s="24" t="n">
         <v>58</v>
       </c>
       <c r="D161" s="9" t="inlineStr">
@@ -6015,8 +5982,8 @@
         </is>
       </c>
     </row>
-    <row r="162" ht="17" customHeight="1">
-      <c r="A162" s="26" t="n">
+    <row r="162">
+      <c r="A162" s="23" t="n">
         <v>45989</v>
       </c>
       <c r="B162" s="9" t="inlineStr">
@@ -6024,7 +5991,7 @@
           <t>TikTokShop</t>
         </is>
       </c>
-      <c r="C162" s="10" t="n">
+      <c r="C162" s="24" t="n">
         <v>230</v>
       </c>
       <c r="D162" s="9" t="inlineStr">
@@ -6049,8 +6016,8 @@
       </c>
       <c r="H162" s="9" t="n"/>
     </row>
-    <row r="163" ht="17" customHeight="1">
-      <c r="A163" s="26" t="n">
+    <row r="163">
+      <c r="A163" s="23" t="n">
         <v>45989</v>
       </c>
       <c r="B163" s="9" t="inlineStr">
@@ -6058,7 +6025,7 @@
           <t>Blue Bottle Coffee</t>
         </is>
       </c>
-      <c r="C163" s="10" t="n">
+      <c r="C163" s="24" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="D163" s="9" t="inlineStr">
@@ -6079,8 +6046,8 @@
       <c r="G163" s="9" t="inlineStr"/>
       <c r="H163" s="9" t="n"/>
     </row>
-    <row r="164" ht="17" customHeight="1">
-      <c r="A164" s="26" t="n">
+    <row r="164">
+      <c r="A164" s="23" t="n">
         <v>45989</v>
       </c>
       <c r="B164" s="9" t="inlineStr">
@@ -6088,7 +6055,7 @@
           <t>Dining Chairs</t>
         </is>
       </c>
-      <c r="C164" s="10" t="n">
+      <c r="C164" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D164" s="9" t="inlineStr">
@@ -6113,8 +6080,8 @@
       </c>
       <c r="H164" s="9" t="n"/>
     </row>
-    <row r="165" ht="17" customHeight="1">
-      <c r="A165" s="26" t="n">
+    <row r="165">
+      <c r="A165" s="23" t="n">
         <v>45986</v>
       </c>
       <c r="B165" s="9" t="inlineStr">
@@ -6122,7 +6089,7 @@
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C165" s="10" t="n">
+      <c r="C165" s="24" t="n">
         <v>24.81</v>
       </c>
       <c r="D165" s="9" t="inlineStr">
@@ -6151,8 +6118,8 @@
         </is>
       </c>
     </row>
-    <row r="166" ht="17" customHeight="1">
-      <c r="A166" s="26" t="n">
+    <row r="166">
+      <c r="A166" s="23" t="n">
         <v>45986</v>
       </c>
       <c r="B166" s="9" t="inlineStr">
@@ -6160,7 +6127,7 @@
           <t>GoFundmE</t>
         </is>
       </c>
-      <c r="C166" s="10" t="n">
+      <c r="C166" s="24" t="n">
         <v>20</v>
       </c>
       <c r="D166" s="9" t="inlineStr">
@@ -6181,8 +6148,8 @@
       <c r="G166" s="9" t="inlineStr"/>
       <c r="H166" s="9" t="n"/>
     </row>
-    <row r="167" ht="17" customHeight="1">
-      <c r="A167" s="26" t="n">
+    <row r="167">
+      <c r="A167" s="23" t="n">
         <v>45984</v>
       </c>
       <c r="B167" s="9" t="inlineStr">
@@ -6190,7 +6157,7 @@
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C167" s="10" t="n">
+      <c r="C167" s="24" t="n">
         <v>175</v>
       </c>
       <c r="D167" s="9" t="inlineStr">
@@ -6215,8 +6182,8 @@
         </is>
       </c>
     </row>
-    <row r="168" ht="17" customHeight="1">
-      <c r="A168" s="26" t="n">
+    <row r="168">
+      <c r="A168" s="23" t="n">
         <v>45984</v>
       </c>
       <c r="B168" s="9" t="inlineStr">
@@ -6224,7 +6191,7 @@
           <t>Melodyne</t>
         </is>
       </c>
-      <c r="C168" s="10" t="n">
+      <c r="C168" s="24" t="n">
         <v>75</v>
       </c>
       <c r="D168" s="9" t="inlineStr">
@@ -6249,8 +6216,8 @@
         </is>
       </c>
     </row>
-    <row r="169" ht="17" customHeight="1">
-      <c r="A169" s="26" t="n">
+    <row r="169">
+      <c r="A169" s="23" t="n">
         <v>45983</v>
       </c>
       <c r="B169" s="9" t="inlineStr">
@@ -6258,7 +6225,7 @@
           <t>Wheelhouse</t>
         </is>
       </c>
-      <c r="C169" s="10" t="n">
+      <c r="C169" s="24" t="n">
         <v>10.16</v>
       </c>
       <c r="D169" s="9" t="inlineStr">
@@ -6279,8 +6246,8 @@
       <c r="G169" s="9" t="inlineStr"/>
       <c r="H169" s="9" t="n"/>
     </row>
-    <row r="170" ht="17" customHeight="1">
-      <c r="A170" s="26" t="n">
+    <row r="170">
+      <c r="A170" s="23" t="n">
         <v>45982</v>
       </c>
       <c r="B170" s="9" t="inlineStr">
@@ -6288,7 +6255,7 @@
           <t>Bodega</t>
         </is>
       </c>
-      <c r="C170" s="10" t="n">
+      <c r="C170" s="24" t="n">
         <v>1.3</v>
       </c>
       <c r="D170" s="9" t="inlineStr">
@@ -6309,8 +6276,8 @@
       <c r="G170" s="9" t="inlineStr"/>
       <c r="H170" s="9" t="n"/>
     </row>
-    <row r="171" ht="17" customHeight="1">
-      <c r="A171" s="26" t="n">
+    <row r="171">
+      <c r="A171" s="23" t="n">
         <v>45982</v>
       </c>
       <c r="B171" s="9" t="inlineStr">
@@ -6318,7 +6285,7 @@
           <t>Bodega</t>
         </is>
       </c>
-      <c r="C171" s="10" t="n">
+      <c r="C171" s="24" t="n">
         <v>2.6</v>
       </c>
       <c r="D171" s="9" t="inlineStr">
@@ -6339,8 +6306,8 @@
       <c r="G171" s="9" t="inlineStr"/>
       <c r="H171" s="9" t="n"/>
     </row>
-    <row r="172" ht="17" customHeight="1">
-      <c r="A172" s="26" t="n">
+    <row r="172">
+      <c r="A172" s="23" t="n">
         <v>45982</v>
       </c>
       <c r="B172" s="9" t="inlineStr">
@@ -6348,7 +6315,7 @@
           <t>Bodega</t>
         </is>
       </c>
-      <c r="C172" s="10" t="n">
+      <c r="C172" s="24" t="n">
         <v>5.2</v>
       </c>
       <c r="D172" s="9" t="inlineStr">
@@ -6369,8 +6336,8 @@
       <c r="G172" s="9" t="inlineStr"/>
       <c r="H172" s="9" t="n"/>
     </row>
-    <row r="173" ht="17" customHeight="1">
-      <c r="A173" s="26" t="n">
+    <row r="173">
+      <c r="A173" s="23" t="n">
         <v>45982</v>
       </c>
       <c r="B173" s="9" t="inlineStr">
@@ -6378,7 +6345,7 @@
           <t>Bodega</t>
         </is>
       </c>
-      <c r="C173" s="10" t="n">
+      <c r="C173" s="24" t="n">
         <v>6.24</v>
       </c>
       <c r="D173" s="9" t="inlineStr">
@@ -6399,8 +6366,8 @@
       <c r="G173" s="9" t="inlineStr"/>
       <c r="H173" s="9" t="n"/>
     </row>
-    <row r="174" ht="17" customHeight="1">
-      <c r="A174" s="26" t="n">
+    <row r="174">
+      <c r="A174" s="23" t="n">
         <v>45982</v>
       </c>
       <c r="B174" s="9" t="inlineStr">
@@ -6408,7 +6375,7 @@
           <t>Bodega</t>
         </is>
       </c>
-      <c r="C174" s="10" t="n">
+      <c r="C174" s="24" t="n">
         <v>7.41</v>
       </c>
       <c r="D174" s="9" t="inlineStr">
@@ -6429,8 +6396,8 @@
       <c r="G174" s="9" t="inlineStr"/>
       <c r="H174" s="9" t="n"/>
     </row>
-    <row r="175" ht="17" customHeight="1">
-      <c r="A175" s="26" t="n">
+    <row r="175">
+      <c r="A175" s="23" t="n">
         <v>45982</v>
       </c>
       <c r="B175" s="9" t="inlineStr">
@@ -6438,7 +6405,7 @@
           <t>Key Food</t>
         </is>
       </c>
-      <c r="C175" s="10" t="n">
+      <c r="C175" s="24" t="n">
         <v>4.69</v>
       </c>
       <c r="D175" s="9" t="inlineStr">
@@ -6459,8 +6426,8 @@
       <c r="G175" s="9" t="inlineStr"/>
       <c r="H175" s="9" t="n"/>
     </row>
-    <row r="176" ht="17" customHeight="1">
-      <c r="A176" s="26" t="n">
+    <row r="176">
+      <c r="A176" s="23" t="n">
         <v>45982</v>
       </c>
       <c r="B176" s="9" t="inlineStr">
@@ -6468,7 +6435,7 @@
           <t>Rosie's</t>
         </is>
       </c>
-      <c r="C176" s="10" t="n">
+      <c r="C176" s="24" t="n">
         <v>13.06</v>
       </c>
       <c r="D176" s="9" t="inlineStr">
@@ -6489,8 +6456,8 @@
       <c r="G176" s="9" t="inlineStr"/>
       <c r="H176" s="9" t="n"/>
     </row>
-    <row r="177" ht="17" customHeight="1">
-      <c r="A177" s="26" t="n">
+    <row r="177">
+      <c r="A177" s="23" t="n">
         <v>45980</v>
       </c>
       <c r="B177" s="9" t="inlineStr">
@@ -6498,7 +6465,7 @@
           <t>Bodega</t>
         </is>
       </c>
-      <c r="C177" s="10" t="n">
+      <c r="C177" s="24" t="n">
         <v>6.24</v>
       </c>
       <c r="D177" s="9" t="inlineStr">
@@ -6519,8 +6486,8 @@
       <c r="G177" s="9" t="inlineStr"/>
       <c r="H177" s="9" t="n"/>
     </row>
-    <row r="178" ht="17" customHeight="1">
-      <c r="A178" s="26" t="n">
+    <row r="178">
+      <c r="A178" s="23" t="n">
         <v>45980</v>
       </c>
       <c r="B178" s="9" t="inlineStr">
@@ -6528,7 +6495,7 @@
           <t>City Fresh</t>
         </is>
       </c>
-      <c r="C178" s="10" t="n">
+      <c r="C178" s="24" t="n">
         <v>20.97</v>
       </c>
       <c r="D178" s="9" t="inlineStr">
@@ -6553,8 +6520,8 @@
         </is>
       </c>
     </row>
-    <row r="179" ht="17" customHeight="1">
-      <c r="A179" s="26" t="n">
+    <row r="179">
+      <c r="A179" s="23" t="n">
         <v>45979</v>
       </c>
       <c r="B179" s="9" t="inlineStr">
@@ -6562,7 +6529,7 @@
           <t>Crossroads</t>
         </is>
       </c>
-      <c r="C179" s="10" t="n">
+      <c r="C179" s="24" t="n">
         <v>7.62</v>
       </c>
       <c r="D179" s="9" t="inlineStr">
@@ -6583,8 +6550,8 @@
       <c r="G179" s="9" t="inlineStr"/>
       <c r="H179" s="9" t="n"/>
     </row>
-    <row r="180" ht="17" customHeight="1">
-      <c r="A180" s="26" t="n">
+    <row r="180">
+      <c r="A180" s="23" t="n">
         <v>45979</v>
       </c>
       <c r="B180" s="9" t="inlineStr">
@@ -6592,7 +6559,7 @@
           <t>Bodega</t>
         </is>
       </c>
-      <c r="C180" s="10" t="n">
+      <c r="C180" s="24" t="n">
         <v>12.15</v>
       </c>
       <c r="D180" s="9" t="inlineStr">
@@ -6613,8 +6580,8 @@
       <c r="G180" s="9" t="inlineStr"/>
       <c r="H180" s="9" t="n"/>
     </row>
-    <row r="181" ht="17" customHeight="1">
-      <c r="A181" s="26" t="n">
+    <row r="181">
+      <c r="A181" s="23" t="n">
         <v>45979</v>
       </c>
       <c r="B181" s="9" t="inlineStr">
@@ -6622,7 +6589,7 @@
           <t>Grocery (Doordash)</t>
         </is>
       </c>
-      <c r="C181" s="10" t="n">
+      <c r="C181" s="24" t="n">
         <v>45</v>
       </c>
       <c r="D181" s="9" t="inlineStr">
@@ -6651,8 +6618,8 @@
         </is>
       </c>
     </row>
-    <row r="182" ht="17" customHeight="1">
-      <c r="A182" s="26" t="n">
+    <row r="182">
+      <c r="A182" s="23" t="n">
         <v>45978</v>
       </c>
       <c r="B182" s="9" t="inlineStr">
@@ -6660,7 +6627,7 @@
           <t>Fine Time</t>
         </is>
       </c>
-      <c r="C182" s="10" t="n">
+      <c r="C182" s="24" t="n">
         <v>11.29</v>
       </c>
       <c r="D182" s="9" t="inlineStr">
@@ -6681,8 +6648,8 @@
       <c r="G182" s="9" t="inlineStr"/>
       <c r="H182" s="9" t="n"/>
     </row>
-    <row r="183" ht="17" customHeight="1">
-      <c r="A183" s="26" t="n">
+    <row r="183">
+      <c r="A183" s="23" t="n">
         <v>45978</v>
       </c>
       <c r="B183" s="9" t="inlineStr">
@@ -6690,7 +6657,7 @@
           <t>Left Hand Path</t>
         </is>
       </c>
-      <c r="C183" s="10" t="n">
+      <c r="C183" s="24" t="n">
         <v>15.15</v>
       </c>
       <c r="D183" s="9" t="inlineStr">
@@ -6711,8 +6678,8 @@
       <c r="G183" s="9" t="inlineStr"/>
       <c r="H183" s="9" t="n"/>
     </row>
-    <row r="184" ht="17" customHeight="1">
-      <c r="A184" s="26" t="n">
+    <row r="184">
+      <c r="A184" s="23" t="n">
         <v>45978</v>
       </c>
       <c r="B184" s="9" t="inlineStr">
@@ -6720,7 +6687,7 @@
           <t>Left Hand Path</t>
         </is>
       </c>
-      <c r="C184" s="10" t="n">
+      <c r="C184" s="24" t="n">
         <v>18.04</v>
       </c>
       <c r="D184" s="9" t="inlineStr">
@@ -6741,8 +6708,8 @@
       <c r="G184" s="9" t="inlineStr"/>
       <c r="H184" s="9" t="n"/>
     </row>
-    <row r="185" ht="17" customHeight="1">
-      <c r="A185" s="26" t="n">
+    <row r="185">
+      <c r="A185" s="23" t="n">
         <v>45978</v>
       </c>
       <c r="B185" s="9" t="inlineStr">
@@ -6750,7 +6717,7 @@
           <t>Paragon</t>
         </is>
       </c>
-      <c r="C185" s="10" t="n">
+      <c r="C185" s="24" t="n">
         <v>21.04</v>
       </c>
       <c r="D185" s="9" t="inlineStr">
@@ -6771,8 +6738,8 @@
       <c r="G185" s="9" t="inlineStr"/>
       <c r="H185" s="9" t="n"/>
     </row>
-    <row r="186" ht="17" customHeight="1">
-      <c r="A186" s="26" t="n">
+    <row r="186">
+      <c r="A186" s="23" t="n">
         <v>45978</v>
       </c>
       <c r="B186" s="9" t="inlineStr">
@@ -6780,7 +6747,7 @@
           <t>Uber</t>
         </is>
       </c>
-      <c r="C186" s="10" t="n">
+      <c r="C186" s="24" t="n">
         <v>11.67</v>
       </c>
       <c r="D186" s="9" t="inlineStr">
@@ -6801,8 +6768,8 @@
       <c r="G186" s="9" t="inlineStr"/>
       <c r="H186" s="9" t="n"/>
     </row>
-    <row r="187" ht="17" customHeight="1">
-      <c r="A187" s="26" t="n">
+    <row r="187">
+      <c r="A187" s="23" t="n">
         <v>45978</v>
       </c>
       <c r="B187" s="9" t="inlineStr">
@@ -6810,7 +6777,7 @@
           <t>Metro</t>
         </is>
       </c>
-      <c r="C187" s="10" t="n">
+      <c r="C187" s="24" t="n">
         <v>19</v>
       </c>
       <c r="D187" s="9" t="inlineStr">
@@ -6831,8 +6798,8 @@
       <c r="G187" s="9" t="inlineStr"/>
       <c r="H187" s="9" t="n"/>
     </row>
-    <row r="188" ht="17" customHeight="1">
-      <c r="A188" s="26" t="n">
+    <row r="188">
+      <c r="A188" s="23" t="n">
         <v>45978</v>
       </c>
       <c r="B188" s="9" t="inlineStr">
@@ -6840,7 +6807,7 @@
           <t>Popeyes</t>
         </is>
       </c>
-      <c r="C188" s="10" t="n">
+      <c r="C188" s="24" t="n">
         <v>10.87</v>
       </c>
       <c r="D188" s="9" t="inlineStr">
@@ -6861,8 +6828,8 @@
       <c r="G188" s="9" t="inlineStr"/>
       <c r="H188" s="9" t="n"/>
     </row>
-    <row r="189" ht="17" customHeight="1">
-      <c r="A189" s="26" t="n">
+    <row r="189">
+      <c r="A189" s="23" t="n">
         <v>45976</v>
       </c>
       <c r="B189" s="9" t="inlineStr">
@@ -6870,7 +6837,7 @@
           <t>City Fresh</t>
         </is>
       </c>
-      <c r="C189" s="10" t="n">
+      <c r="C189" s="24" t="n">
         <v>16.99</v>
       </c>
       <c r="D189" s="9" t="inlineStr">
@@ -6895,8 +6862,8 @@
         </is>
       </c>
     </row>
-    <row r="190" ht="17" customHeight="1">
-      <c r="A190" s="26" t="n">
+    <row r="190">
+      <c r="A190" s="23" t="n">
         <v>45976</v>
       </c>
       <c r="B190" s="9" t="inlineStr">
@@ -6904,7 +6871,7 @@
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C190" s="10" t="n">
+      <c r="C190" s="24" t="n">
         <v>33.25</v>
       </c>
       <c r="D190" s="9" t="inlineStr">
@@ -6929,8 +6896,8 @@
         </is>
       </c>
     </row>
-    <row r="191" ht="17" customHeight="1">
-      <c r="A191" s="26" t="n">
+    <row r="191">
+      <c r="A191" s="23" t="n">
         <v>45976</v>
       </c>
       <c r="B191" s="9" t="inlineStr">
@@ -6938,7 +6905,7 @@
           <t>City Fresh</t>
         </is>
       </c>
-      <c r="C191" s="10" t="n">
+      <c r="C191" s="24" t="n">
         <v>15.37</v>
       </c>
       <c r="D191" s="9" t="inlineStr">
@@ -6963,8 +6930,8 @@
         </is>
       </c>
     </row>
-    <row r="192" ht="17" customHeight="1">
-      <c r="A192" s="26" t="n">
+    <row r="192">
+      <c r="A192" s="23" t="n">
         <v>45975</v>
       </c>
       <c r="B192" s="9" t="inlineStr">
@@ -6972,7 +6939,7 @@
           <t>FKA Twigs Ticket</t>
         </is>
       </c>
-      <c r="C192" s="10" t="n">
+      <c r="C192" s="24" t="n">
         <v>29.47</v>
       </c>
       <c r="D192" s="9" t="inlineStr">
@@ -6993,8 +6960,8 @@
       <c r="G192" s="9" t="inlineStr"/>
       <c r="H192" s="9" t="n"/>
     </row>
-    <row r="193" ht="17" customHeight="1">
-      <c r="A193" s="26" t="n">
+    <row r="193">
+      <c r="A193" s="23" t="n">
         <v>45975</v>
       </c>
       <c r="B193" s="9" t="inlineStr">
@@ -7002,7 +6969,7 @@
           <t>Selva (w/Ana)</t>
         </is>
       </c>
-      <c r="C193" s="10" t="n">
+      <c r="C193" s="24" t="n">
         <v>15.14</v>
       </c>
       <c r="D193" s="9" t="inlineStr">
@@ -7023,8 +6990,8 @@
       <c r="G193" s="9" t="inlineStr"/>
       <c r="H193" s="9" t="n"/>
     </row>
-    <row r="194" ht="17" customHeight="1">
-      <c r="A194" s="26" t="n">
+    <row r="194">
+      <c r="A194" s="23" t="n">
         <v>45975</v>
       </c>
       <c r="B194" s="9" t="inlineStr">
@@ -7032,7 +6999,7 @@
           <t>Bodega on Wall St</t>
         </is>
       </c>
-      <c r="C194" s="10" t="n">
+      <c r="C194" s="24" t="n">
         <v>10.13</v>
       </c>
       <c r="D194" s="9" t="inlineStr">
@@ -7053,8 +7020,8 @@
       <c r="G194" s="9" t="inlineStr"/>
       <c r="H194" s="9" t="n"/>
     </row>
-    <row r="195" ht="17" customHeight="1">
-      <c r="A195" s="26" t="n">
+    <row r="195">
+      <c r="A195" s="23" t="n">
         <v>45975</v>
       </c>
       <c r="B195" s="9" t="inlineStr">
@@ -7062,7 +7029,7 @@
           <t>Doordash Popeyes</t>
         </is>
       </c>
-      <c r="C195" s="10" t="n">
+      <c r="C195" s="24" t="n">
         <v>19.96</v>
       </c>
       <c r="D195" s="9" t="inlineStr">
@@ -7083,8 +7050,8 @@
       <c r="G195" s="9" t="inlineStr"/>
       <c r="H195" s="9" t="n"/>
     </row>
-    <row r="196" ht="17" customHeight="1">
-      <c r="A196" s="26" t="n">
+    <row r="196">
+      <c r="A196" s="23" t="n">
         <v>45975</v>
       </c>
       <c r="B196" s="9" t="inlineStr">
@@ -7092,7 +7059,7 @@
           <t>Uber to home (1)</t>
         </is>
       </c>
-      <c r="C196" s="10" t="n">
+      <c r="C196" s="24" t="n">
         <v>9.9</v>
       </c>
       <c r="D196" s="9" t="inlineStr">
@@ -7117,8 +7084,8 @@
         </is>
       </c>
     </row>
-    <row r="197" ht="17" customHeight="1">
-      <c r="A197" s="26" t="n">
+    <row r="197">
+      <c r="A197" s="23" t="n">
         <v>45975</v>
       </c>
       <c r="B197" s="9" t="inlineStr">
@@ -7126,7 +7093,7 @@
           <t>Uber to club (2)</t>
         </is>
       </c>
-      <c r="C197" s="10" t="n">
+      <c r="C197" s="24" t="n">
         <v>11.29</v>
       </c>
       <c r="D197" s="9" t="inlineStr">
@@ -7151,8 +7118,8 @@
         </is>
       </c>
     </row>
-    <row r="198" ht="17" customHeight="1">
-      <c r="A198" s="26" t="n">
+    <row r="198">
+      <c r="A198" s="23" t="n">
         <v>45975</v>
       </c>
       <c r="B198" s="9" t="inlineStr">
@@ -7160,7 +7127,7 @@
           <t>154 Scott Drinks</t>
         </is>
       </c>
-      <c r="C198" s="10" t="n">
+      <c r="C198" s="24" t="n">
         <v>24.1</v>
       </c>
       <c r="D198" s="9" t="inlineStr">
@@ -7185,8 +7152,8 @@
         </is>
       </c>
     </row>
-    <row r="199" ht="17" customHeight="1">
-      <c r="A199" s="26" t="n">
+    <row r="199">
+      <c r="A199" s="23" t="n">
         <v>45975</v>
       </c>
       <c r="B199" s="9" t="inlineStr">
@@ -7194,7 +7161,7 @@
           <t>154 Drinks 2</t>
         </is>
       </c>
-      <c r="C199" s="10" t="n">
+      <c r="C199" s="24" t="n">
         <v>18.04</v>
       </c>
       <c r="D199" s="9" t="inlineStr">
@@ -7219,8 +7186,8 @@
         </is>
       </c>
     </row>
-    <row r="200" ht="17" customHeight="1">
-      <c r="A200" s="26" t="n">
+    <row r="200">
+      <c r="A200" s="23" t="n">
         <v>45975</v>
       </c>
       <c r="B200" s="9" t="inlineStr">
@@ -7228,7 +7195,7 @@
           <t>Uber home (3)</t>
         </is>
       </c>
-      <c r="C200" s="10" t="n">
+      <c r="C200" s="24" t="n">
         <v>11.63</v>
       </c>
       <c r="D200" s="9" t="inlineStr">
@@ -7253,8 +7220,8 @@
         </is>
       </c>
     </row>
-    <row r="201" ht="17" customHeight="1">
-      <c r="A201" s="26" t="n">
+    <row r="201">
+      <c r="A201" s="23" t="n">
         <v>45975</v>
       </c>
       <c r="B201" s="9" t="inlineStr">
@@ -7262,7 +7229,7 @@
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C201" s="10" t="n">
+      <c r="C201" s="24" t="n">
         <v>20.68</v>
       </c>
       <c r="D201" s="9" t="inlineStr">
@@ -7287,8 +7254,8 @@
         </is>
       </c>
     </row>
-    <row r="202" ht="17" customHeight="1">
-      <c r="A202" s="26" t="n">
+    <row r="202">
+      <c r="A202" s="23" t="n">
         <v>45973</v>
       </c>
       <c r="B202" s="9" t="inlineStr">
@@ -7296,7 +7263,7 @@
           <t>City Fresh</t>
         </is>
       </c>
-      <c r="C202" s="10" t="n">
+      <c r="C202" s="24" t="n">
         <v>13.98</v>
       </c>
       <c r="D202" s="9" t="inlineStr">
@@ -7321,8 +7288,8 @@
         </is>
       </c>
     </row>
-    <row r="203" ht="17" customHeight="1">
-      <c r="A203" s="26" t="n">
+    <row r="203">
+      <c r="A203" s="23" t="n">
         <v>45972</v>
       </c>
       <c r="B203" s="9" t="inlineStr">
@@ -7330,7 +7297,7 @@
           <t>Three Diamond Door</t>
         </is>
       </c>
-      <c r="C203" s="10" t="n">
+      <c r="C203" s="24" t="n">
         <v>12.3</v>
       </c>
       <c r="D203" s="9" t="inlineStr">
@@ -7355,8 +7322,8 @@
         </is>
       </c>
     </row>
-    <row r="204" ht="17" customHeight="1">
-      <c r="A204" s="26" t="n">
+    <row r="204">
+      <c r="A204" s="23" t="n">
         <v>45971</v>
       </c>
       <c r="B204" s="9" t="inlineStr">
@@ -7364,7 +7331,7 @@
           <t>Obscure Coffee</t>
         </is>
       </c>
-      <c r="C204" s="10" t="n">
+      <c r="C204" s="24" t="n">
         <v>8</v>
       </c>
       <c r="D204" s="9" t="inlineStr">
@@ -7385,8 +7352,8 @@
       <c r="G204" s="9" t="inlineStr"/>
       <c r="H204" s="9" t="n"/>
     </row>
-    <row r="205" ht="17" customHeight="1">
-      <c r="A205" s="26" t="n">
+    <row r="205">
+      <c r="A205" s="23" t="n">
         <v>45971</v>
       </c>
       <c r="B205" s="9" t="inlineStr">
@@ -7394,7 +7361,7 @@
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C205" s="10" t="n">
+      <c r="C205" s="24" t="n">
         <v>21.76</v>
       </c>
       <c r="D205" s="9" t="inlineStr">
@@ -7419,8 +7386,8 @@
         </is>
       </c>
     </row>
-    <row r="206" ht="17" customHeight="1">
-      <c r="A206" s="26" t="n">
+    <row r="206">
+      <c r="A206" s="23" t="n">
         <v>45971</v>
       </c>
       <c r="B206" s="9" t="inlineStr">
@@ -7428,7 +7395,7 @@
           <t>Grocery (Doordash)</t>
         </is>
       </c>
-      <c r="C206" s="10" t="n">
+      <c r="C206" s="24" t="n">
         <v>105</v>
       </c>
       <c r="D206" s="9" t="inlineStr">
@@ -7453,8 +7420,8 @@
       </c>
       <c r="H206" s="9" t="n"/>
     </row>
-    <row r="207" ht="17" customHeight="1">
-      <c r="A207" s="26" t="n">
+    <row r="207">
+      <c r="A207" s="23" t="n">
         <v>45970</v>
       </c>
       <c r="B207" s="9" t="inlineStr">
@@ -7462,7 +7429,7 @@
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C207" s="10" t="n">
+      <c r="C207" s="24" t="n">
         <v>53.43</v>
       </c>
       <c r="D207" s="9" t="inlineStr">
@@ -7487,8 +7454,8 @@
         </is>
       </c>
     </row>
-    <row r="208" ht="17" customHeight="1">
-      <c r="A208" s="26" t="n">
+    <row r="208">
+      <c r="A208" s="23" t="n">
         <v>45967</v>
       </c>
       <c r="B208" s="9" t="inlineStr">
@@ -7496,7 +7463,7 @@
           <t>Bodega</t>
         </is>
       </c>
-      <c r="C208" s="10" t="n">
+      <c r="C208" s="24" t="n">
         <v>2.8</v>
       </c>
       <c r="D208" s="9" t="inlineStr">
@@ -7517,8 +7484,8 @@
       <c r="G208" s="9" t="inlineStr"/>
       <c r="H208" s="9" t="n"/>
     </row>
-    <row r="209" ht="17" customHeight="1">
-      <c r="A209" s="26" t="n">
+    <row r="209">
+      <c r="A209" s="23" t="n">
         <v>45967</v>
       </c>
       <c r="B209" s="9" t="inlineStr">
@@ -7526,7 +7493,7 @@
           <t>Saint Michel</t>
         </is>
       </c>
-      <c r="C209" s="10" t="n">
+      <c r="C209" s="24" t="n">
         <v>7.8</v>
       </c>
       <c r="D209" s="9" t="inlineStr">
@@ -7547,8 +7514,8 @@
       <c r="G209" s="9" t="inlineStr"/>
       <c r="H209" s="9" t="n"/>
     </row>
-    <row r="210" ht="17" customHeight="1">
-      <c r="A210" s="26" t="n">
+    <row r="210">
+      <c r="A210" s="23" t="n">
         <v>45967</v>
       </c>
       <c r="B210" s="9" t="inlineStr">
@@ -7556,7 +7523,7 @@
           <t>Bathroom Shelves</t>
         </is>
       </c>
-      <c r="C210" s="10" t="n">
+      <c r="C210" s="24" t="n">
         <v>15.23</v>
       </c>
       <c r="D210" s="9" t="inlineStr">
@@ -7577,8 +7544,8 @@
       <c r="G210" s="9" t="inlineStr"/>
       <c r="H210" s="9" t="n"/>
     </row>
-    <row r="211" ht="17" customHeight="1">
-      <c r="A211" s="26" t="n">
+    <row r="211">
+      <c r="A211" s="23" t="n">
         <v>45967</v>
       </c>
       <c r="B211" s="9" t="inlineStr">
@@ -7586,7 +7553,7 @@
           <t>Mrs. Meyers Soap</t>
         </is>
       </c>
-      <c r="C211" s="10" t="n">
+      <c r="C211" s="24" t="n">
         <v>22.84</v>
       </c>
       <c r="D211" s="9" t="inlineStr">
@@ -7611,8 +7578,8 @@
         </is>
       </c>
     </row>
-    <row r="212" ht="17" customHeight="1">
-      <c r="A212" s="26" t="n">
+    <row r="212">
+      <c r="A212" s="23" t="n">
         <v>45967</v>
       </c>
       <c r="B212" s="9" t="inlineStr">
@@ -7620,7 +7587,7 @@
           <t>Journal</t>
         </is>
       </c>
-      <c r="C212" s="10" t="n">
+      <c r="C212" s="24" t="n">
         <v>14.14</v>
       </c>
       <c r="D212" s="9" t="inlineStr">
@@ -7645,8 +7612,8 @@
         </is>
       </c>
     </row>
-    <row r="213" ht="17" customHeight="1">
-      <c r="A213" s="26" t="n">
+    <row r="213">
+      <c r="A213" s="23" t="n">
         <v>45966</v>
       </c>
       <c r="B213" s="9" t="inlineStr">
@@ -7654,7 +7621,7 @@
           <t>Magician bar</t>
         </is>
       </c>
-      <c r="C213" s="10" t="n">
+      <c r="C213" s="24" t="n">
         <v>11</v>
       </c>
       <c r="D213" s="9" t="inlineStr">
@@ -7675,8 +7642,8 @@
       <c r="G213" s="9" t="inlineStr"/>
       <c r="H213" s="9" t="n"/>
     </row>
-    <row r="214" ht="17" customHeight="1">
-      <c r="A214" s="26" t="n">
+    <row r="214">
+      <c r="A214" s="23" t="n">
         <v>45966</v>
       </c>
       <c r="B214" s="9" t="inlineStr">
@@ -7684,7 +7651,7 @@
           <t>Bar revival</t>
         </is>
       </c>
-      <c r="C214" s="10" t="n">
+      <c r="C214" s="24" t="n">
         <v>35</v>
       </c>
       <c r="D214" s="9" t="inlineStr">
@@ -7705,8 +7672,8 @@
       <c r="G214" s="9" t="inlineStr"/>
       <c r="H214" s="9" t="n"/>
     </row>
-    <row r="215" ht="17" customHeight="1">
-      <c r="A215" s="26" t="n">
+    <row r="215">
+      <c r="A215" s="23" t="n">
         <v>45966</v>
       </c>
       <c r="B215" s="9" t="inlineStr">
@@ -7714,7 +7681,7 @@
           <t>Weed</t>
         </is>
       </c>
-      <c r="C215" s="10" t="n">
+      <c r="C215" s="24" t="n">
         <v>10</v>
       </c>
       <c r="D215" s="9" t="inlineStr">
@@ -7735,8 +7702,8 @@
       <c r="G215" s="9" t="inlineStr"/>
       <c r="H215" s="9" t="n"/>
     </row>
-    <row r="216" ht="17" customHeight="1">
-      <c r="A216" s="26" t="n">
+    <row r="216">
+      <c r="A216" s="23" t="n">
         <v>45965</v>
       </c>
       <c r="B216" s="9" t="inlineStr">
@@ -7744,7 +7711,7 @@
           <t>Selva Latte</t>
         </is>
       </c>
-      <c r="C216" s="10" t="n">
+      <c r="C216" s="24" t="n">
         <v>7.41</v>
       </c>
       <c r="D216" s="9" t="inlineStr">
@@ -7765,8 +7732,8 @@
       <c r="G216" s="9" t="inlineStr"/>
       <c r="H216" s="9" t="n"/>
     </row>
-    <row r="217" ht="17" customHeight="1">
-      <c r="A217" s="26" t="n">
+    <row r="217">
+      <c r="A217" s="23" t="n">
         <v>45965</v>
       </c>
       <c r="B217" s="9" t="inlineStr">
@@ -7774,7 +7741,7 @@
           <t>Mari GoFundMe</t>
         </is>
       </c>
-      <c r="C217" s="10" t="n">
+      <c r="C217" s="24" t="n">
         <v>145</v>
       </c>
       <c r="D217" s="9" t="inlineStr">
@@ -7795,8 +7762,8 @@
       <c r="G217" s="9" t="inlineStr"/>
       <c r="H217" s="9" t="n"/>
     </row>
-    <row r="218" ht="17" customHeight="1">
-      <c r="A218" s="26" t="n">
+    <row r="218">
+      <c r="A218" s="23" t="n">
         <v>45964</v>
       </c>
       <c r="B218" s="9" t="inlineStr">
@@ -7804,7 +7771,7 @@
           <t>Ace Hardware (Shelf bracket)</t>
         </is>
       </c>
-      <c r="C218" s="10" t="n">
+      <c r="C218" s="24" t="n">
         <v>6.52</v>
       </c>
       <c r="D218" s="9" t="inlineStr">
@@ -7825,8 +7792,8 @@
       <c r="G218" s="9" t="inlineStr"/>
       <c r="H218" s="9" t="n"/>
     </row>
-    <row r="219" ht="17" customHeight="1">
-      <c r="A219" s="26" t="n">
+    <row r="219">
+      <c r="A219" s="23" t="n">
         <v>45964</v>
       </c>
       <c r="B219" s="9" t="inlineStr">
@@ -7834,7 +7801,7 @@
           <t>Uber</t>
         </is>
       </c>
-      <c r="C219" s="10" t="n">
+      <c r="C219" s="24" t="n">
         <v>11.96</v>
       </c>
       <c r="D219" s="9" t="inlineStr">
@@ -7855,8 +7822,8 @@
       <c r="G219" s="9" t="inlineStr"/>
       <c r="H219" s="9" t="n"/>
     </row>
-    <row r="220" ht="17" customHeight="1">
-      <c r="A220" s="26" t="n">
+    <row r="220">
+      <c r="A220" s="23" t="n">
         <v>45964</v>
       </c>
       <c r="B220" s="9" t="inlineStr">
@@ -7864,7 +7831,7 @@
           <t>Good Judy</t>
         </is>
       </c>
-      <c r="C220" s="10" t="n">
+      <c r="C220" s="24" t="n">
         <v>13.5</v>
       </c>
       <c r="D220" s="9" t="inlineStr">
@@ -7885,8 +7852,8 @@
       <c r="G220" s="9" t="inlineStr"/>
       <c r="H220" s="9" t="n"/>
     </row>
-    <row r="221" ht="17" customHeight="1">
-      <c r="A221" s="26" t="n">
+    <row r="221">
+      <c r="A221" s="23" t="n">
         <v>45964</v>
       </c>
       <c r="B221" s="9" t="inlineStr">
@@ -7894,7 +7861,7 @@
           <t>Doordash</t>
         </is>
       </c>
-      <c r="C221" s="10" t="n">
+      <c r="C221" s="24" t="n">
         <v>23.13</v>
       </c>
       <c r="D221" s="9" t="inlineStr">
@@ -7915,8 +7882,8 @@
       <c r="G221" s="9" t="inlineStr"/>
       <c r="H221" s="9" t="n"/>
     </row>
-    <row r="222" ht="17" customHeight="1">
-      <c r="A222" s="26" t="n">
+    <row r="222">
+      <c r="A222" s="23" t="n">
         <v>45964</v>
       </c>
       <c r="B222" s="9" t="inlineStr">
@@ -7924,7 +7891,7 @@
           <t>Uber</t>
         </is>
       </c>
-      <c r="C222" s="10" t="n">
+      <c r="C222" s="24" t="n">
         <v>30.98</v>
       </c>
       <c r="D222" s="9" t="inlineStr">
@@ -7945,8 +7912,8 @@
       <c r="G222" s="9" t="inlineStr"/>
       <c r="H222" s="9" t="n"/>
     </row>
-    <row r="223" ht="17" customHeight="1">
-      <c r="A223" s="26" t="n">
+    <row r="223">
+      <c r="A223" s="23" t="n">
         <v>45964</v>
       </c>
       <c r="B223" s="9" t="inlineStr">
@@ -7954,7 +7921,7 @@
           <t>Liqour Store</t>
         </is>
       </c>
-      <c r="C223" s="10" t="n">
+      <c r="C223" s="24" t="n">
         <v>41</v>
       </c>
       <c r="D223" s="9" t="inlineStr">
@@ -7975,8 +7942,8 @@
       <c r="G223" s="9" t="inlineStr"/>
       <c r="H223" s="9" t="n"/>
     </row>
-    <row r="224" ht="17" customHeight="1">
-      <c r="A224" s="26" t="n">
+    <row r="224">
+      <c r="A224" s="23" t="n">
         <v>45964</v>
       </c>
       <c r="B224" s="9" t="inlineStr">
@@ -7984,7 +7951,7 @@
           <t>Venmo spend</t>
         </is>
       </c>
-      <c r="C224" s="10" t="n">
+      <c r="C224" s="24" t="n">
         <v>10</v>
       </c>
       <c r="D224" s="9" t="inlineStr">
@@ -8005,8 +7972,8 @@
       <c r="G224" s="9" t="inlineStr"/>
       <c r="H224" s="9" t="n"/>
     </row>
-    <row r="225" ht="17" customHeight="1">
-      <c r="A225" s="26" t="n">
+    <row r="225">
+      <c r="A225" s="23" t="n">
         <v>45964</v>
       </c>
       <c r="B225" s="9" t="inlineStr">
@@ -8014,7 +7981,7 @@
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C225" s="10" t="n">
+      <c r="C225" s="24" t="n">
         <v>27.75</v>
       </c>
       <c r="D225" s="9" t="inlineStr">
@@ -8039,8 +8006,8 @@
         </is>
       </c>
     </row>
-    <row r="226" ht="17" customHeight="1">
-      <c r="A226" s="26" t="n">
+    <row r="226">
+      <c r="A226" s="23" t="n">
         <v>45962</v>
       </c>
       <c r="B226" s="9" t="inlineStr">
@@ -8048,7 +8015,7 @@
           <t>ATM Widthdrawl</t>
         </is>
       </c>
-      <c r="C226" s="10" t="n">
+      <c r="C226" s="24" t="n">
         <v>102</v>
       </c>
       <c r="D226" s="9" t="inlineStr">
@@ -8077,8 +8044,8 @@
         </is>
       </c>
     </row>
-    <row r="227" ht="17" customHeight="1">
-      <c r="A227" s="26" t="n">
+    <row r="227">
+      <c r="A227" s="23" t="n">
         <v>45957</v>
       </c>
       <c r="B227" s="9" t="inlineStr">
@@ -8086,7 +8053,7 @@
           <t>Grocery (DoorDash)</t>
         </is>
       </c>
-      <c r="C227" s="10" t="n">
+      <c r="C227" s="24" t="n">
         <v>129.72</v>
       </c>
       <c r="D227" s="9" t="inlineStr">
@@ -8115,8 +8082,8 @@
         </is>
       </c>
     </row>
-    <row r="228" ht="17" customHeight="1">
-      <c r="A228" s="26" t="n">
+    <row r="228">
+      <c r="A228" s="23" t="n">
         <v>45955</v>
       </c>
       <c r="B228" s="9" t="inlineStr">
@@ -8124,7 +8091,7 @@
           <t>City fresh</t>
         </is>
       </c>
-      <c r="C228" s="10" t="n">
+      <c r="C228" s="24" t="n">
         <v>33.97</v>
       </c>
       <c r="D228" s="9" t="inlineStr">
@@ -8149,8 +8116,8 @@
       </c>
       <c r="H228" s="9" t="n"/>
     </row>
-    <row r="229" ht="17" customHeight="1">
-      <c r="A229" s="26" t="n">
+    <row r="229">
+      <c r="A229" s="23" t="n">
         <v>45955</v>
       </c>
       <c r="B229" s="9" t="inlineStr">
@@ -8158,7 +8125,7 @@
           <t>Honey's Bar</t>
         </is>
       </c>
-      <c r="C229" s="10" t="n">
+      <c r="C229" s="24" t="n">
         <v>32.1</v>
       </c>
       <c r="D229" s="9" t="inlineStr">
@@ -8183,8 +8150,8 @@
       </c>
       <c r="H229" s="9" t="n"/>
     </row>
-    <row r="230" ht="17" customHeight="1">
-      <c r="A230" s="26" t="n">
+    <row r="230">
+      <c r="A230" s="23" t="n">
         <v>45955</v>
       </c>
       <c r="B230" s="9" t="inlineStr">
@@ -8192,7 +8159,7 @@
           <t>Stainless Steel Shelves</t>
         </is>
       </c>
-      <c r="C230" s="10" t="n">
+      <c r="C230" s="24" t="n">
         <v>58</v>
       </c>
       <c r="D230" s="9" t="inlineStr">
@@ -8217,8 +8184,8 @@
       </c>
       <c r="H230" s="9" t="n"/>
     </row>
-    <row r="231" ht="17" customHeight="1">
-      <c r="A231" s="26" t="n">
+    <row r="231">
+      <c r="A231" s="23" t="n">
         <v>45953</v>
       </c>
       <c r="B231" s="9" t="inlineStr">
@@ -8226,7 +8193,7 @@
           <t>Signal Tickets for halloween</t>
         </is>
       </c>
-      <c r="C231" s="10" t="n">
+      <c r="C231" s="24" t="n">
         <v>60</v>
       </c>
       <c r="D231" s="9" t="inlineStr">
@@ -8251,8 +8218,8 @@
       </c>
       <c r="H231" s="9" t="n"/>
     </row>
-    <row r="232" ht="17" customHeight="1">
-      <c r="A232" s="26" t="n">
+    <row r="232">
+      <c r="A232" s="23" t="n">
         <v>45952</v>
       </c>
       <c r="B232" s="9" t="inlineStr">
@@ -8260,7 +8227,7 @@
           <t>Bodega</t>
         </is>
       </c>
-      <c r="C232" s="10" t="n">
+      <c r="C232" s="24" t="n">
         <v>4.16</v>
       </c>
       <c r="D232" s="9" t="inlineStr">
@@ -8285,8 +8252,8 @@
       </c>
       <c r="H232" s="9" t="n"/>
     </row>
-    <row r="233" ht="17" customHeight="1">
-      <c r="A233" s="26" t="n">
+    <row r="233">
+      <c r="A233" s="23" t="n">
         <v>45952</v>
       </c>
       <c r="B233" s="9" t="inlineStr">
@@ -8294,7 +8261,7 @@
           <t>Bodega</t>
         </is>
       </c>
-      <c r="C233" s="10" t="n">
+      <c r="C233" s="24" t="n">
         <v>7.28</v>
       </c>
       <c r="D233" s="9" t="inlineStr">
@@ -8319,8 +8286,8 @@
       </c>
       <c r="H233" s="9" t="n"/>
     </row>
-    <row r="234" ht="17" customHeight="1">
-      <c r="A234" s="26" t="n">
+    <row r="234">
+      <c r="A234" s="23" t="n">
         <v>45952</v>
       </c>
       <c r="B234" s="9" t="inlineStr">
@@ -8328,7 +8295,7 @@
           <t>City Fresh</t>
         </is>
       </c>
-      <c r="C234" s="10" t="n">
+      <c r="C234" s="24" t="n">
         <v>9.73</v>
       </c>
       <c r="D234" s="9" t="inlineStr">
@@ -8353,8 +8320,8 @@
       </c>
       <c r="H234" s="9" t="n"/>
     </row>
-    <row r="235" ht="17" customHeight="1">
-      <c r="A235" s="26" t="n">
+    <row r="235">
+      <c r="A235" s="23" t="n">
         <v>45949</v>
       </c>
       <c r="B235" s="9" t="inlineStr">
@@ -8362,7 +8329,7 @@
           <t>Home Depot</t>
         </is>
       </c>
-      <c r="C235" s="10" t="n">
+      <c r="C235" s="24" t="n">
         <v>19.03</v>
       </c>
       <c r="D235" s="9" t="inlineStr">
@@ -8387,8 +8354,8 @@
       </c>
       <c r="H235" s="9" t="n"/>
     </row>
-    <row r="236" ht="17" customHeight="1">
-      <c r="A236" s="26" t="n">
+    <row r="236">
+      <c r="A236" s="23" t="n">
         <v>45949</v>
       </c>
       <c r="B236" s="9" t="inlineStr">
@@ -8396,7 +8363,7 @@
           <t>Adorama</t>
         </is>
       </c>
-      <c r="C236" s="10" t="n">
+      <c r="C236" s="24" t="n">
         <v>38.09</v>
       </c>
       <c r="D236" s="9" t="inlineStr">
@@ -8421,8 +8388,8 @@
       </c>
       <c r="H236" s="9" t="n"/>
     </row>
-    <row r="237" ht="17" customHeight="1">
-      <c r="A237" s="26" t="n">
+    <row r="237">
+      <c r="A237" s="23" t="n">
         <v>45949</v>
       </c>
       <c r="B237" s="9" t="inlineStr">
@@ -8430,7 +8397,7 @@
           <t>Transit to NJ</t>
         </is>
       </c>
-      <c r="C237" s="10" t="n">
+      <c r="C237" s="24" t="n">
         <v>18</v>
       </c>
       <c r="D237" s="9" t="inlineStr">
@@ -8455,8 +8422,8 @@
       </c>
       <c r="H237" s="9" t="n"/>
     </row>
-    <row r="238" ht="17" customHeight="1">
-      <c r="A238" s="26" t="n">
+    <row r="238">
+      <c r="A238" s="23" t="n">
         <v>45949</v>
       </c>
       <c r="B238" s="9" t="inlineStr">
@@ -8464,7 +8431,7 @@
           <t>DoorDash for Mari</t>
         </is>
       </c>
-      <c r="C238" s="10" t="n">
+      <c r="C238" s="24" t="n">
         <v>100</v>
       </c>
       <c r="D238" s="9" t="inlineStr">
@@ -8489,8 +8456,8 @@
       </c>
       <c r="H238" s="9" t="n"/>
     </row>
-    <row r="239" ht="17" customHeight="1">
-      <c r="A239" s="26" t="n">
+    <row r="239">
+      <c r="A239" s="23" t="n">
         <v>45947</v>
       </c>
       <c r="B239" s="9" t="inlineStr">
@@ -8498,7 +8465,7 @@
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C239" s="10" t="n">
+      <c r="C239" s="24" t="n">
         <v>33.69</v>
       </c>
       <c r="D239" s="9" t="inlineStr">
@@ -8527,8 +8494,8 @@
         </is>
       </c>
     </row>
-    <row r="240" ht="17" customHeight="1">
-      <c r="A240" s="26" t="n">
+    <row r="240">
+      <c r="A240" s="23" t="n">
         <v>45947</v>
       </c>
       <c r="B240" s="9" t="inlineStr">
@@ -8536,7 +8503,7 @@
           <t>Amazon</t>
         </is>
       </c>
-      <c r="C240" s="10" t="n">
+      <c r="C240" s="24" t="n">
         <v>184.98</v>
       </c>
       <c r="D240" s="9" t="inlineStr">
@@ -8565,8 +8532,8 @@
         </is>
       </c>
     </row>
-    <row r="241" ht="17" customHeight="1">
-      <c r="A241" s="26" t="n">
+    <row r="241">
+      <c r="A241" s="23" t="n">
         <v>45947</v>
       </c>
       <c r="B241" s="9" t="inlineStr">
@@ -8574,7 +8541,7 @@
           <t>Uniqlo</t>
         </is>
       </c>
-      <c r="C241" s="10" t="n">
+      <c r="C241" s="24" t="n">
         <v>62</v>
       </c>
       <c r="D241" s="9" t="inlineStr">
@@ -8599,8 +8566,8 @@
       </c>
       <c r="H241" s="9" t="n"/>
     </row>
-    <row r="242" ht="17" customHeight="1">
-      <c r="A242" s="26" t="n">
+    <row r="242">
+      <c r="A242" s="23" t="n">
         <v>45947</v>
       </c>
       <c r="B242" s="9" t="inlineStr">
@@ -8608,7 +8575,7 @@
           <t>Palmetto</t>
         </is>
       </c>
-      <c r="C242" s="10" t="n">
+      <c r="C242" s="24" t="n">
         <v>67.02</v>
       </c>
       <c r="D242" s="9" t="inlineStr">
@@ -8633,8 +8600,8 @@
       </c>
       <c r="H242" s="9" t="n"/>
     </row>
-    <row r="243" ht="17" customHeight="1">
-      <c r="A243" s="26" t="n">
+    <row r="243">
+      <c r="A243" s="23" t="n">
         <v>45947</v>
       </c>
       <c r="B243" s="9" t="inlineStr">
@@ -8642,7 +8609,7 @@
           <t>Caraotas</t>
         </is>
       </c>
-      <c r="C243" s="10" t="n">
+      <c r="C243" s="24" t="n">
         <v>12</v>
       </c>
       <c r="D243" s="9" t="inlineStr">
@@ -8667,8 +8634,8 @@
       </c>
       <c r="H243" s="9" t="n"/>
     </row>
-    <row r="244" ht="17" customHeight="1">
-      <c r="A244" s="26" t="n">
+    <row r="244">
+      <c r="A244" s="23" t="n">
         <v>45943</v>
       </c>
       <c r="B244" s="9" t="inlineStr">
@@ -8676,7 +8643,7 @@
           <t>Grocery (Doordash)</t>
         </is>
       </c>
-      <c r="C244" s="10" t="n">
+      <c r="C244" s="24" t="n">
         <v>140</v>
       </c>
       <c r="D244" s="9" t="inlineStr">
@@ -8705,8 +8672,8 @@
         </is>
       </c>
     </row>
-    <row r="245" ht="17" customHeight="1">
-      <c r="A245" s="26" t="n">
+    <row r="245">
+      <c r="A245" s="23" t="n">
         <v>45940</v>
       </c>
       <c r="B245" s="9" t="inlineStr">
@@ -8714,7 +8681,7 @@
           <t>Bodega</t>
         </is>
       </c>
-      <c r="C245" s="10" t="n">
+      <c r="C245" s="24" t="n">
         <v>8</v>
       </c>
       <c r="D245" s="9" t="inlineStr">
@@ -8739,8 +8706,8 @@
       </c>
       <c r="H245" s="9" t="n"/>
     </row>
-    <row r="246" ht="17" customHeight="1">
-      <c r="A246" s="26" t="n">
+    <row r="246">
+      <c r="A246" s="23" t="n">
         <v>45940</v>
       </c>
       <c r="B246" s="9" t="inlineStr">
@@ -8748,7 +8715,7 @@
           <t>Bodega</t>
         </is>
       </c>
-      <c r="C246" s="10" t="n">
+      <c r="C246" s="24" t="n">
         <v>4.16</v>
       </c>
       <c r="D246" s="9" t="inlineStr">
@@ -8773,8 +8740,8 @@
       </c>
       <c r="H246" s="9" t="n"/>
     </row>
-    <row r="247" ht="17" customHeight="1">
-      <c r="A247" s="26" t="n">
+    <row r="247">
+      <c r="A247" s="23" t="n">
         <v>45940</v>
       </c>
       <c r="B247" s="9" t="inlineStr">
@@ -8782,7 +8749,7 @@
           <t>Drink (captain Dan)</t>
         </is>
       </c>
-      <c r="C247" s="10" t="n">
+      <c r="C247" s="24" t="n">
         <v>15</v>
       </c>
       <c r="D247" s="9" t="inlineStr">
@@ -8807,8 +8774,8 @@
       </c>
       <c r="H247" s="9" t="n"/>
     </row>
-    <row r="248" ht="17" customHeight="1">
-      <c r="A248" s="26" t="n">
+    <row r="248">
+      <c r="A248" s="23" t="n">
         <v>45940</v>
       </c>
       <c r="B248" s="9" t="inlineStr">
@@ -8816,7 +8783,7 @@
           <t>CVS</t>
         </is>
       </c>
-      <c r="C248" s="10" t="n">
+      <c r="C248" s="24" t="n">
         <v>10.14</v>
       </c>
       <c r="D248" s="9" t="inlineStr">
@@ -8841,8 +8808,8 @@
       </c>
       <c r="H248" s="9" t="n"/>
     </row>
-    <row r="249" ht="17" customHeight="1">
-      <c r="A249" s="26" t="n">
+    <row r="249">
+      <c r="A249" s="23" t="n">
         <v>45940</v>
       </c>
       <c r="B249" s="9" t="inlineStr">
@@ -8850,7 +8817,7 @@
           <t>Bodega</t>
         </is>
       </c>
-      <c r="C249" s="10" t="n">
+      <c r="C249" s="24" t="n">
         <v>18.78</v>
       </c>
       <c r="D249" s="9" t="inlineStr">
@@ -8875,8 +8842,8 @@
       </c>
       <c r="H249" s="9" t="n"/>
     </row>
-    <row r="250" ht="17" customHeight="1">
-      <c r="A250" s="26" t="n">
+    <row r="250">
+      <c r="A250" s="23" t="n">
         <v>45940</v>
       </c>
       <c r="B250" s="9" t="inlineStr">
@@ -8884,7 +8851,7 @@
           <t>Brunch</t>
         </is>
       </c>
-      <c r="C250" s="10" t="n">
+      <c r="C250" s="24" t="n">
         <v>25</v>
       </c>
       <c r="D250" s="9" t="inlineStr">
@@ -8909,8 +8876,8 @@
       </c>
       <c r="H250" s="9" t="n"/>
     </row>
-    <row r="251" ht="17" customHeight="1">
-      <c r="A251" s="26" t="n">
+    <row r="251">
+      <c r="A251" s="23" t="n">
         <v>45940</v>
       </c>
       <c r="B251" s="9" t="inlineStr">
@@ -8918,7 +8885,7 @@
           <t>amazon usb c</t>
         </is>
       </c>
-      <c r="C251" s="10" t="n">
+      <c r="C251" s="24" t="n">
         <v>10</v>
       </c>
       <c r="D251" s="9" t="inlineStr">
@@ -8943,8 +8910,8 @@
       </c>
       <c r="H251" s="9" t="n"/>
     </row>
-    <row r="252" ht="17" customHeight="1">
-      <c r="A252" s="26" t="n">
+    <row r="252">
+      <c r="A252" s="23" t="n">
         <v>45940</v>
       </c>
       <c r="B252" s="9" t="inlineStr">
@@ -8952,7 +8919,7 @@
           <t>City Fresh</t>
         </is>
       </c>
-      <c r="C252" s="10" t="n">
+      <c r="C252" s="24" t="n">
         <v>17.3</v>
       </c>
       <c r="D252" s="9" t="inlineStr">
@@ -8981,8 +8948,8 @@
         </is>
       </c>
     </row>
-    <row r="253" ht="17" customHeight="1">
-      <c r="A253" s="26" t="n">
+    <row r="253">
+      <c r="A253" s="23" t="n">
         <v>45939</v>
       </c>
       <c r="B253" s="9" t="inlineStr">
@@ -8990,7 +8957,7 @@
           <t>Amazon Ice Roller</t>
         </is>
       </c>
-      <c r="C253" s="10" t="n">
+      <c r="C253" s="24" t="n">
         <v>8</v>
       </c>
       <c r="D253" s="9" t="inlineStr">
@@ -9015,8 +8982,8 @@
       </c>
       <c r="H253" s="9" t="n"/>
     </row>
-    <row r="254" ht="17" customHeight="1">
-      <c r="A254" s="26" t="n">
+    <row r="254">
+      <c r="A254" s="23" t="n">
         <v>45939</v>
       </c>
       <c r="B254" s="9" t="inlineStr">
@@ -9024,7 +8991,7 @@
           <t>Bread (City Fresh)</t>
         </is>
       </c>
-      <c r="C254" s="10" t="n">
+      <c r="C254" s="24" t="n">
         <v>21.19</v>
       </c>
       <c r="D254" s="9" t="inlineStr">
@@ -9053,8 +9020,8 @@
         </is>
       </c>
     </row>
-    <row r="255" ht="17" customHeight="1">
-      <c r="A255" s="26" t="n">
+    <row r="255">
+      <c r="A255" s="23" t="n">
         <v>45937</v>
       </c>
       <c r="B255" s="9" t="inlineStr">
@@ -9062,7 +9029,7 @@
           <t>Iced Latte</t>
         </is>
       </c>
-      <c r="C255" s="10" t="n">
+      <c r="C255" s="24" t="n">
         <v>7</v>
       </c>
       <c r="D255" s="9" t="inlineStr">
@@ -9087,8 +9054,8 @@
       </c>
       <c r="H255" s="9" t="n"/>
     </row>
-    <row r="256" ht="17" customHeight="1">
-      <c r="A256" s="26" t="n">
+    <row r="256">
+      <c r="A256" s="23" t="n">
         <v>45937</v>
       </c>
       <c r="B256" s="9" t="inlineStr">
@@ -9096,7 +9063,7 @@
           <t>Calendar</t>
         </is>
       </c>
-      <c r="C256" s="10" t="n">
+      <c r="C256" s="24" t="n">
         <v>6</v>
       </c>
       <c r="D256" s="9" t="inlineStr">
@@ -9121,8 +9088,8 @@
       </c>
       <c r="H256" s="9" t="n"/>
     </row>
-    <row r="257" ht="17" customHeight="1">
-      <c r="A257" s="26" t="n">
+    <row r="257">
+      <c r="A257" s="23" t="n">
         <v>45936</v>
       </c>
       <c r="B257" s="9" t="inlineStr">
@@ -9130,7 +9097,7 @@
           <t>Bodega</t>
         </is>
       </c>
-      <c r="C257" s="10" t="n">
+      <c r="C257" s="24" t="n">
         <v>8.32</v>
       </c>
       <c r="D257" s="9" t="inlineStr">
@@ -9155,8 +9122,8 @@
       </c>
       <c r="H257" s="9" t="n"/>
     </row>
-    <row r="258" ht="17" customHeight="1">
-      <c r="A258" s="26" t="n">
+    <row r="258">
+      <c r="A258" s="23" t="n">
         <v>45936</v>
       </c>
       <c r="B258" s="9" t="inlineStr">
@@ -9164,7 +9131,7 @@
           <t>Bodega</t>
         </is>
       </c>
-      <c r="C258" s="10" t="n">
+      <c r="C258" s="24" t="n">
         <v>4.36</v>
       </c>
       <c r="D258" s="9" t="inlineStr">
@@ -9189,8 +9156,8 @@
       </c>
       <c r="H258" s="9" t="n"/>
     </row>
-    <row r="259" ht="17" customHeight="1">
-      <c r="A259" s="26" t="n">
+    <row r="259">
+      <c r="A259" s="23" t="n">
         <v>45933</v>
       </c>
       <c r="B259" s="9" t="inlineStr">
@@ -9198,7 +9165,7 @@
           <t>Toothbrush</t>
         </is>
       </c>
-      <c r="C259" s="10" t="n">
+      <c r="C259" s="24" t="n">
         <v>51.16</v>
       </c>
       <c r="D259" s="9" t="inlineStr">
@@ -9223,8 +9190,8 @@
       </c>
       <c r="H259" s="9" t="n"/>
     </row>
-    <row r="260" ht="17" customHeight="1">
-      <c r="A260" s="26" t="n">
+    <row r="260">
+      <c r="A260" s="23" t="n">
         <v>45933</v>
       </c>
       <c r="B260" s="9" t="inlineStr">
@@ -9232,7 +9199,7 @@
           <t>Diane's</t>
         </is>
       </c>
-      <c r="C260" s="10" t="n">
+      <c r="C260" s="24" t="n">
         <v>11.03</v>
       </c>
       <c r="D260" s="9" t="inlineStr">
@@ -9257,8 +9224,8 @@
       </c>
       <c r="H260" s="9" t="n"/>
     </row>
-    <row r="261" ht="17" customHeight="1">
-      <c r="A261" s="26" t="n">
+    <row r="261">
+      <c r="A261" s="23" t="n">
         <v>45933</v>
       </c>
       <c r="B261" s="9" t="inlineStr">
@@ -9266,7 +9233,7 @@
           <t>Diane's</t>
         </is>
       </c>
-      <c r="C261" s="10" t="n">
+      <c r="C261" s="24" t="n">
         <v>19.93</v>
       </c>
       <c r="D261" s="9" t="inlineStr">
@@ -9291,8 +9258,8 @@
       </c>
       <c r="H261" s="9" t="n"/>
     </row>
-    <row r="262" ht="17" customHeight="1">
-      <c r="A262" s="26" t="n">
+    <row r="262">
+      <c r="A262" s="23" t="n">
         <v>45933</v>
       </c>
       <c r="B262" s="9" t="inlineStr">
@@ -9300,7 +9267,7 @@
           <t>Shake Shack</t>
         </is>
       </c>
-      <c r="C262" s="10" t="n">
+      <c r="C262" s="24" t="n">
         <v>38.12</v>
       </c>
       <c r="D262" s="9" t="inlineStr">
@@ -9325,8 +9292,8 @@
       </c>
       <c r="H262" s="9" t="n"/>
     </row>
-    <row r="263" ht="17" customHeight="1">
-      <c r="A263" s="26" t="n">
+    <row r="263">
+      <c r="A263" s="23" t="n">
         <v>45933</v>
       </c>
       <c r="B263" s="9" t="inlineStr">
@@ -9334,7 +9301,7 @@
           <t>Bodega</t>
         </is>
       </c>
-      <c r="C263" s="10" t="n">
+      <c r="C263" s="24" t="n">
         <v>6.23</v>
       </c>
       <c r="D263" s="9" t="inlineStr">
@@ -9359,8 +9326,8 @@
       </c>
       <c r="H263" s="9" t="n"/>
     </row>
-    <row r="264" ht="17" customHeight="1">
-      <c r="A264" s="26" t="n">
+    <row r="264">
+      <c r="A264" s="23" t="n">
         <v>45932</v>
       </c>
       <c r="B264" s="9" t="inlineStr">
@@ -9368,7 +9335,7 @@
           <t>Iced latte</t>
         </is>
       </c>
-      <c r="C264" s="10" t="n">
+      <c r="C264" s="24" t="n">
         <v>4.92</v>
       </c>
       <c r="D264" s="9" t="inlineStr">
@@ -9393,8 +9360,8 @@
       </c>
       <c r="H264" s="9" t="n"/>
     </row>
-    <row r="265" ht="17" customHeight="1">
-      <c r="A265" s="26" t="n">
+    <row r="265">
+      <c r="A265" s="23" t="n">
         <v>45932</v>
       </c>
       <c r="B265" s="9" t="inlineStr">
@@ -9402,7 +9369,7 @@
           <t>Shirt (other ppls clothes)</t>
         </is>
       </c>
-      <c r="C265" s="10" t="n">
+      <c r="C265" s="24" t="n">
         <v>24.98</v>
       </c>
       <c r="D265" s="9" t="inlineStr">
@@ -9427,8 +9394,8 @@
       </c>
       <c r="H265" s="9" t="n"/>
     </row>
-    <row r="266" ht="17" customHeight="1">
-      <c r="A266" s="26" t="n">
+    <row r="266">
+      <c r="A266" s="23" t="n">
         <v>45929</v>
       </c>
       <c r="B266" s="9" t="inlineStr">
@@ -9436,7 +9403,7 @@
           <t>Iced Latte</t>
         </is>
       </c>
-      <c r="C266" s="10" t="n">
+      <c r="C266" s="24" t="n">
         <v>4.01</v>
       </c>
       <c r="D266" s="9" t="inlineStr">
@@ -9461,8 +9428,8 @@
       </c>
       <c r="H266" s="9" t="n"/>
     </row>
-    <row r="267" ht="17" customHeight="1">
-      <c r="A267" s="26" t="n">
+    <row r="267">
+      <c r="A267" s="23" t="n">
         <v>45928</v>
       </c>
       <c r="B267" s="9" t="inlineStr">
@@ -9470,7 +9437,7 @@
           <t>Amazon Order</t>
         </is>
       </c>
-      <c r="C267" s="10" t="n">
+      <c r="C267" s="24" t="n">
         <v>90.2</v>
       </c>
       <c r="D267" s="9" t="inlineStr">
@@ -9499,8 +9466,8 @@
         </is>
       </c>
     </row>
-    <row r="268" ht="17" customHeight="1">
-      <c r="A268" s="26" t="n">
+    <row r="268">
+      <c r="A268" s="23" t="n">
         <v>45928</v>
       </c>
       <c r="B268" s="9" t="inlineStr">
@@ -9508,7 +9475,7 @@
           <t>ATM</t>
         </is>
       </c>
-      <c r="C268" s="10" t="n">
+      <c r="C268" s="24" t="n">
         <v>31.16</v>
       </c>
       <c r="D268" s="9" t="inlineStr">
@@ -9533,8 +9500,8 @@
       </c>
       <c r="H268" s="9" t="n"/>
     </row>
-    <row r="269" ht="17" customHeight="1">
-      <c r="A269" s="26" t="n">
+    <row r="269">
+      <c r="A269" s="23" t="n">
         <v>45928</v>
       </c>
       <c r="B269" s="9" t="inlineStr">
@@ -9542,7 +9509,7 @@
           <t>Iced Latte</t>
         </is>
       </c>
-      <c r="C269" s="10" t="n">
+      <c r="C269" s="24" t="n">
         <v>5.21</v>
       </c>
       <c r="D269" s="9" t="inlineStr">
@@ -9567,8 +9534,8 @@
       </c>
       <c r="H269" s="9" t="n"/>
     </row>
-    <row r="270" ht="17" customHeight="1">
-      <c r="A270" s="26" t="n">
+    <row r="270">
+      <c r="A270" s="23" t="n">
         <v>45928</v>
       </c>
       <c r="B270" s="9" t="inlineStr">
@@ -9576,7 +9543,7 @@
           <t>Grocery (Doordash)</t>
         </is>
       </c>
-      <c r="C270" s="10" t="n">
+      <c r="C270" s="24" t="n">
         <v>59.46</v>
       </c>
       <c r="D270" s="9" t="inlineStr">
@@ -9606,419 +9573,419 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="27" t="n"/>
-      <c r="B271" s="28" t="n"/>
-      <c r="C271" s="29" t="n"/>
-      <c r="D271" s="28" t="n"/>
-      <c r="E271" s="28" t="n"/>
-      <c r="F271" s="28" t="n"/>
-      <c r="G271" s="28" t="n"/>
-      <c r="H271" s="28" t="n"/>
+      <c r="A271" s="25" t="n"/>
+      <c r="B271" s="26" t="n"/>
+      <c r="C271" s="10" t="n"/>
+      <c r="D271" s="26" t="n"/>
+      <c r="E271" s="26" t="n"/>
+      <c r="F271" s="26" t="n"/>
+      <c r="G271" s="26" t="n"/>
+      <c r="H271" s="26" t="n"/>
     </row>
     <row r="272">
-      <c r="A272" s="27" t="n"/>
-      <c r="B272" s="28" t="n"/>
-      <c r="C272" s="29" t="n"/>
-      <c r="D272" s="28" t="n"/>
-      <c r="E272" s="28" t="n"/>
-      <c r="F272" s="28" t="n"/>
-      <c r="G272" s="28" t="n"/>
-      <c r="H272" s="28" t="n"/>
+      <c r="A272" s="25" t="n"/>
+      <c r="B272" s="26" t="n"/>
+      <c r="C272" s="10" t="n"/>
+      <c r="D272" s="26" t="n"/>
+      <c r="E272" s="26" t="n"/>
+      <c r="F272" s="26" t="n"/>
+      <c r="G272" s="26" t="n"/>
+      <c r="H272" s="26" t="n"/>
     </row>
     <row r="273">
-      <c r="A273" s="27" t="n"/>
-      <c r="B273" s="28" t="n"/>
-      <c r="C273" s="29" t="n"/>
-      <c r="D273" s="28" t="n"/>
-      <c r="E273" s="28" t="n"/>
-      <c r="F273" s="28" t="n"/>
-      <c r="G273" s="28" t="n"/>
-      <c r="H273" s="28" t="n"/>
+      <c r="A273" s="25" t="n"/>
+      <c r="B273" s="26" t="n"/>
+      <c r="C273" s="10" t="n"/>
+      <c r="D273" s="26" t="n"/>
+      <c r="E273" s="26" t="n"/>
+      <c r="F273" s="26" t="n"/>
+      <c r="G273" s="26" t="n"/>
+      <c r="H273" s="26" t="n"/>
     </row>
     <row r="274">
-      <c r="A274" s="27" t="n"/>
-      <c r="B274" s="28" t="n"/>
-      <c r="C274" s="29" t="n"/>
-      <c r="D274" s="28" t="n"/>
-      <c r="E274" s="28" t="n"/>
-      <c r="F274" s="28" t="n"/>
-      <c r="G274" s="28" t="n"/>
-      <c r="H274" s="28" t="n"/>
+      <c r="A274" s="25" t="n"/>
+      <c r="B274" s="26" t="n"/>
+      <c r="C274" s="10" t="n"/>
+      <c r="D274" s="26" t="n"/>
+      <c r="E274" s="26" t="n"/>
+      <c r="F274" s="26" t="n"/>
+      <c r="G274" s="26" t="n"/>
+      <c r="H274" s="26" t="n"/>
     </row>
     <row r="275">
-      <c r="A275" s="27" t="n"/>
-      <c r="B275" s="28" t="n"/>
-      <c r="C275" s="29" t="n"/>
-      <c r="D275" s="28" t="n"/>
-      <c r="E275" s="28" t="n"/>
-      <c r="F275" s="28" t="n"/>
-      <c r="G275" s="28" t="n"/>
-      <c r="H275" s="28" t="n"/>
+      <c r="A275" s="25" t="n"/>
+      <c r="B275" s="26" t="n"/>
+      <c r="C275" s="10" t="n"/>
+      <c r="D275" s="26" t="n"/>
+      <c r="E275" s="26" t="n"/>
+      <c r="F275" s="26" t="n"/>
+      <c r="G275" s="26" t="n"/>
+      <c r="H275" s="26" t="n"/>
     </row>
     <row r="276">
-      <c r="A276" s="27" t="n"/>
-      <c r="B276" s="28" t="n"/>
-      <c r="C276" s="29" t="n"/>
-      <c r="D276" s="28" t="n"/>
-      <c r="E276" s="28" t="n"/>
-      <c r="F276" s="28" t="n"/>
-      <c r="G276" s="28" t="n"/>
-      <c r="H276" s="28" t="n"/>
+      <c r="A276" s="25" t="n"/>
+      <c r="B276" s="26" t="n"/>
+      <c r="C276" s="10" t="n"/>
+      <c r="D276" s="26" t="n"/>
+      <c r="E276" s="26" t="n"/>
+      <c r="F276" s="26" t="n"/>
+      <c r="G276" s="26" t="n"/>
+      <c r="H276" s="26" t="n"/>
     </row>
     <row r="277">
-      <c r="A277" s="27" t="n"/>
-      <c r="B277" s="28" t="n"/>
-      <c r="C277" s="29" t="n"/>
-      <c r="D277" s="28" t="n"/>
-      <c r="E277" s="28" t="n"/>
-      <c r="F277" s="28" t="n"/>
-      <c r="G277" s="28" t="n"/>
-      <c r="H277" s="28" t="n"/>
+      <c r="A277" s="25" t="n"/>
+      <c r="B277" s="26" t="n"/>
+      <c r="C277" s="10" t="n"/>
+      <c r="D277" s="26" t="n"/>
+      <c r="E277" s="26" t="n"/>
+      <c r="F277" s="26" t="n"/>
+      <c r="G277" s="26" t="n"/>
+      <c r="H277" s="26" t="n"/>
     </row>
     <row r="278">
-      <c r="A278" s="27" t="n"/>
-      <c r="B278" s="28" t="n"/>
-      <c r="C278" s="29" t="n"/>
-      <c r="D278" s="28" t="n"/>
-      <c r="E278" s="28" t="n"/>
-      <c r="F278" s="28" t="n"/>
-      <c r="G278" s="28" t="n"/>
-      <c r="H278" s="28" t="n"/>
+      <c r="A278" s="25" t="n"/>
+      <c r="B278" s="26" t="n"/>
+      <c r="C278" s="10" t="n"/>
+      <c r="D278" s="26" t="n"/>
+      <c r="E278" s="26" t="n"/>
+      <c r="F278" s="26" t="n"/>
+      <c r="G278" s="26" t="n"/>
+      <c r="H278" s="26" t="n"/>
     </row>
     <row r="279">
-      <c r="A279" s="27" t="n"/>
-      <c r="B279" s="28" t="n"/>
-      <c r="C279" s="29" t="n"/>
-      <c r="D279" s="28" t="n"/>
-      <c r="E279" s="28" t="n"/>
-      <c r="F279" s="28" t="n"/>
-      <c r="G279" s="28" t="n"/>
-      <c r="H279" s="28" t="n"/>
+      <c r="A279" s="25" t="n"/>
+      <c r="B279" s="26" t="n"/>
+      <c r="C279" s="10" t="n"/>
+      <c r="D279" s="26" t="n"/>
+      <c r="E279" s="26" t="n"/>
+      <c r="F279" s="26" t="n"/>
+      <c r="G279" s="26" t="n"/>
+      <c r="H279" s="26" t="n"/>
     </row>
     <row r="280">
-      <c r="A280" s="27" t="n"/>
-      <c r="B280" s="28" t="n"/>
-      <c r="C280" s="29" t="n"/>
-      <c r="D280" s="28" t="n"/>
-      <c r="E280" s="28" t="n"/>
-      <c r="F280" s="28" t="n"/>
-      <c r="G280" s="28" t="n"/>
-      <c r="H280" s="28" t="n"/>
+      <c r="A280" s="25" t="n"/>
+      <c r="B280" s="26" t="n"/>
+      <c r="C280" s="10" t="n"/>
+      <c r="D280" s="26" t="n"/>
+      <c r="E280" s="26" t="n"/>
+      <c r="F280" s="26" t="n"/>
+      <c r="G280" s="26" t="n"/>
+      <c r="H280" s="26" t="n"/>
     </row>
     <row r="281">
-      <c r="A281" s="27" t="n"/>
-      <c r="B281" s="28" t="n"/>
-      <c r="C281" s="29" t="n"/>
-      <c r="D281" s="28" t="n"/>
-      <c r="E281" s="28" t="n"/>
-      <c r="F281" s="28" t="n"/>
-      <c r="G281" s="28" t="n"/>
-      <c r="H281" s="28" t="n"/>
+      <c r="A281" s="25" t="n"/>
+      <c r="B281" s="26" t="n"/>
+      <c r="C281" s="10" t="n"/>
+      <c r="D281" s="26" t="n"/>
+      <c r="E281" s="26" t="n"/>
+      <c r="F281" s="26" t="n"/>
+      <c r="G281" s="26" t="n"/>
+      <c r="H281" s="26" t="n"/>
     </row>
     <row r="282">
-      <c r="A282" s="27" t="n"/>
-      <c r="B282" s="28" t="n"/>
-      <c r="C282" s="29" t="n"/>
-      <c r="D282" s="28" t="n"/>
-      <c r="E282" s="28" t="n"/>
-      <c r="F282" s="28" t="n"/>
-      <c r="G282" s="28" t="n"/>
-      <c r="H282" s="28" t="n"/>
+      <c r="A282" s="25" t="n"/>
+      <c r="B282" s="26" t="n"/>
+      <c r="C282" s="10" t="n"/>
+      <c r="D282" s="26" t="n"/>
+      <c r="E282" s="26" t="n"/>
+      <c r="F282" s="26" t="n"/>
+      <c r="G282" s="26" t="n"/>
+      <c r="H282" s="26" t="n"/>
     </row>
     <row r="283">
-      <c r="A283" s="27" t="n"/>
-      <c r="B283" s="28" t="n"/>
-      <c r="C283" s="29" t="n"/>
-      <c r="D283" s="28" t="n"/>
-      <c r="E283" s="28" t="n"/>
-      <c r="F283" s="28" t="n"/>
-      <c r="G283" s="28" t="n"/>
-      <c r="H283" s="28" t="n"/>
+      <c r="A283" s="25" t="n"/>
+      <c r="B283" s="26" t="n"/>
+      <c r="C283" s="10" t="n"/>
+      <c r="D283" s="26" t="n"/>
+      <c r="E283" s="26" t="n"/>
+      <c r="F283" s="26" t="n"/>
+      <c r="G283" s="26" t="n"/>
+      <c r="H283" s="26" t="n"/>
     </row>
     <row r="284">
-      <c r="A284" s="27" t="n"/>
-      <c r="B284" s="28" t="n"/>
-      <c r="C284" s="29" t="n"/>
-      <c r="D284" s="28" t="n"/>
-      <c r="E284" s="28" t="n"/>
-      <c r="F284" s="28" t="n"/>
-      <c r="G284" s="28" t="n"/>
-      <c r="H284" s="28" t="n"/>
+      <c r="A284" s="25" t="n"/>
+      <c r="B284" s="26" t="n"/>
+      <c r="C284" s="10" t="n"/>
+      <c r="D284" s="26" t="n"/>
+      <c r="E284" s="26" t="n"/>
+      <c r="F284" s="26" t="n"/>
+      <c r="G284" s="26" t="n"/>
+      <c r="H284" s="26" t="n"/>
     </row>
     <row r="285">
-      <c r="A285" s="27" t="n"/>
-      <c r="B285" s="28" t="n"/>
-      <c r="C285" s="29" t="n"/>
-      <c r="D285" s="28" t="n"/>
-      <c r="E285" s="28" t="n"/>
-      <c r="F285" s="28" t="n"/>
-      <c r="G285" s="28" t="n"/>
-      <c r="H285" s="28" t="n"/>
+      <c r="A285" s="25" t="n"/>
+      <c r="B285" s="26" t="n"/>
+      <c r="C285" s="10" t="n"/>
+      <c r="D285" s="26" t="n"/>
+      <c r="E285" s="26" t="n"/>
+      <c r="F285" s="26" t="n"/>
+      <c r="G285" s="26" t="n"/>
+      <c r="H285" s="26" t="n"/>
     </row>
     <row r="286">
-      <c r="A286" s="27" t="n"/>
-      <c r="B286" s="28" t="n"/>
-      <c r="C286" s="29" t="n"/>
-      <c r="D286" s="28" t="n"/>
-      <c r="E286" s="28" t="n"/>
-      <c r="F286" s="28" t="n"/>
-      <c r="G286" s="28" t="n"/>
-      <c r="H286" s="28" t="n"/>
+      <c r="A286" s="25" t="n"/>
+      <c r="B286" s="26" t="n"/>
+      <c r="C286" s="10" t="n"/>
+      <c r="D286" s="26" t="n"/>
+      <c r="E286" s="26" t="n"/>
+      <c r="F286" s="26" t="n"/>
+      <c r="G286" s="26" t="n"/>
+      <c r="H286" s="26" t="n"/>
     </row>
     <row r="287">
-      <c r="A287" s="27" t="n"/>
-      <c r="B287" s="28" t="n"/>
-      <c r="C287" s="29" t="n"/>
-      <c r="D287" s="28" t="n"/>
-      <c r="E287" s="28" t="n"/>
-      <c r="F287" s="28" t="n"/>
-      <c r="G287" s="28" t="n"/>
-      <c r="H287" s="28" t="n"/>
+      <c r="A287" s="25" t="n"/>
+      <c r="B287" s="26" t="n"/>
+      <c r="C287" s="10" t="n"/>
+      <c r="D287" s="26" t="n"/>
+      <c r="E287" s="26" t="n"/>
+      <c r="F287" s="26" t="n"/>
+      <c r="G287" s="26" t="n"/>
+      <c r="H287" s="26" t="n"/>
     </row>
     <row r="288">
-      <c r="A288" s="27" t="n"/>
-      <c r="B288" s="28" t="n"/>
-      <c r="C288" s="29" t="n"/>
-      <c r="D288" s="28" t="n"/>
-      <c r="E288" s="28" t="n"/>
-      <c r="F288" s="28" t="n"/>
-      <c r="G288" s="28" t="n"/>
-      <c r="H288" s="28" t="n"/>
+      <c r="A288" s="25" t="n"/>
+      <c r="B288" s="26" t="n"/>
+      <c r="C288" s="10" t="n"/>
+      <c r="D288" s="26" t="n"/>
+      <c r="E288" s="26" t="n"/>
+      <c r="F288" s="26" t="n"/>
+      <c r="G288" s="26" t="n"/>
+      <c r="H288" s="26" t="n"/>
     </row>
     <row r="289">
-      <c r="A289" s="27" t="n"/>
-      <c r="B289" s="28" t="n"/>
-      <c r="C289" s="29" t="n"/>
-      <c r="D289" s="28" t="n"/>
-      <c r="E289" s="28" t="n"/>
-      <c r="F289" s="28" t="n"/>
-      <c r="G289" s="28" t="n"/>
-      <c r="H289" s="28" t="n"/>
+      <c r="A289" s="25" t="n"/>
+      <c r="B289" s="26" t="n"/>
+      <c r="C289" s="10" t="n"/>
+      <c r="D289" s="26" t="n"/>
+      <c r="E289" s="26" t="n"/>
+      <c r="F289" s="26" t="n"/>
+      <c r="G289" s="26" t="n"/>
+      <c r="H289" s="26" t="n"/>
     </row>
     <row r="290">
-      <c r="A290" s="27" t="n"/>
-      <c r="B290" s="28" t="n"/>
-      <c r="C290" s="29" t="n"/>
-      <c r="D290" s="28" t="n"/>
-      <c r="E290" s="28" t="n"/>
-      <c r="F290" s="28" t="n"/>
-      <c r="G290" s="28" t="n"/>
-      <c r="H290" s="28" t="n"/>
+      <c r="A290" s="25" t="n"/>
+      <c r="B290" s="26" t="n"/>
+      <c r="C290" s="10" t="n"/>
+      <c r="D290" s="26" t="n"/>
+      <c r="E290" s="26" t="n"/>
+      <c r="F290" s="26" t="n"/>
+      <c r="G290" s="26" t="n"/>
+      <c r="H290" s="26" t="n"/>
     </row>
     <row r="291">
-      <c r="A291" s="27" t="n"/>
-      <c r="B291" s="28" t="n"/>
-      <c r="C291" s="29" t="n"/>
-      <c r="D291" s="28" t="n"/>
-      <c r="E291" s="28" t="n"/>
-      <c r="F291" s="28" t="n"/>
-      <c r="G291" s="28" t="n"/>
-      <c r="H291" s="28" t="n"/>
+      <c r="A291" s="25" t="n"/>
+      <c r="B291" s="26" t="n"/>
+      <c r="C291" s="10" t="n"/>
+      <c r="D291" s="26" t="n"/>
+      <c r="E291" s="26" t="n"/>
+      <c r="F291" s="26" t="n"/>
+      <c r="G291" s="26" t="n"/>
+      <c r="H291" s="26" t="n"/>
     </row>
     <row r="292">
-      <c r="A292" s="27" t="n"/>
-      <c r="B292" s="28" t="n"/>
-      <c r="C292" s="29" t="n"/>
-      <c r="D292" s="28" t="n"/>
-      <c r="E292" s="28" t="n"/>
-      <c r="F292" s="28" t="n"/>
-      <c r="G292" s="28" t="n"/>
-      <c r="H292" s="28" t="n"/>
+      <c r="A292" s="25" t="n"/>
+      <c r="B292" s="26" t="n"/>
+      <c r="C292" s="10" t="n"/>
+      <c r="D292" s="26" t="n"/>
+      <c r="E292" s="26" t="n"/>
+      <c r="F292" s="26" t="n"/>
+      <c r="G292" s="26" t="n"/>
+      <c r="H292" s="26" t="n"/>
     </row>
     <row r="293">
-      <c r="A293" s="27" t="n"/>
-      <c r="B293" s="28" t="n"/>
-      <c r="C293" s="29" t="n"/>
-      <c r="D293" s="28" t="n"/>
-      <c r="E293" s="28" t="n"/>
-      <c r="F293" s="28" t="n"/>
-      <c r="G293" s="28" t="n"/>
-      <c r="H293" s="28" t="n"/>
+      <c r="A293" s="25" t="n"/>
+      <c r="B293" s="26" t="n"/>
+      <c r="C293" s="10" t="n"/>
+      <c r="D293" s="26" t="n"/>
+      <c r="E293" s="26" t="n"/>
+      <c r="F293" s="26" t="n"/>
+      <c r="G293" s="26" t="n"/>
+      <c r="H293" s="26" t="n"/>
     </row>
     <row r="294">
-      <c r="A294" s="27" t="n"/>
-      <c r="B294" s="28" t="n"/>
-      <c r="C294" s="29" t="n"/>
-      <c r="D294" s="28" t="n"/>
-      <c r="E294" s="28" t="n"/>
-      <c r="F294" s="28" t="n"/>
-      <c r="G294" s="28" t="n"/>
-      <c r="H294" s="28" t="n"/>
+      <c r="A294" s="25" t="n"/>
+      <c r="B294" s="26" t="n"/>
+      <c r="C294" s="10" t="n"/>
+      <c r="D294" s="26" t="n"/>
+      <c r="E294" s="26" t="n"/>
+      <c r="F294" s="26" t="n"/>
+      <c r="G294" s="26" t="n"/>
+      <c r="H294" s="26" t="n"/>
     </row>
     <row r="295">
-      <c r="A295" s="27" t="n"/>
-      <c r="B295" s="28" t="n"/>
-      <c r="C295" s="29" t="n"/>
-      <c r="D295" s="28" t="n"/>
-      <c r="E295" s="28" t="n"/>
-      <c r="F295" s="28" t="n"/>
-      <c r="G295" s="28" t="n"/>
-      <c r="H295" s="28" t="n"/>
+      <c r="A295" s="25" t="n"/>
+      <c r="B295" s="26" t="n"/>
+      <c r="C295" s="10" t="n"/>
+      <c r="D295" s="26" t="n"/>
+      <c r="E295" s="26" t="n"/>
+      <c r="F295" s="26" t="n"/>
+      <c r="G295" s="26" t="n"/>
+      <c r="H295" s="26" t="n"/>
     </row>
     <row r="296">
-      <c r="A296" s="27" t="n"/>
-      <c r="B296" s="28" t="n"/>
-      <c r="C296" s="29" t="n"/>
-      <c r="D296" s="28" t="n"/>
-      <c r="E296" s="28" t="n"/>
-      <c r="F296" s="28" t="n"/>
-      <c r="G296" s="28" t="n"/>
-      <c r="H296" s="28" t="n"/>
+      <c r="A296" s="25" t="n"/>
+      <c r="B296" s="26" t="n"/>
+      <c r="C296" s="10" t="n"/>
+      <c r="D296" s="26" t="n"/>
+      <c r="E296" s="26" t="n"/>
+      <c r="F296" s="26" t="n"/>
+      <c r="G296" s="26" t="n"/>
+      <c r="H296" s="26" t="n"/>
     </row>
     <row r="297">
-      <c r="A297" s="27" t="n"/>
-      <c r="B297" s="28" t="n"/>
-      <c r="C297" s="29" t="n"/>
-      <c r="D297" s="28" t="n"/>
-      <c r="E297" s="28" t="n"/>
-      <c r="F297" s="28" t="n"/>
-      <c r="G297" s="28" t="n"/>
-      <c r="H297" s="28" t="n"/>
+      <c r="A297" s="25" t="n"/>
+      <c r="B297" s="26" t="n"/>
+      <c r="C297" s="10" t="n"/>
+      <c r="D297" s="26" t="n"/>
+      <c r="E297" s="26" t="n"/>
+      <c r="F297" s="26" t="n"/>
+      <c r="G297" s="26" t="n"/>
+      <c r="H297" s="26" t="n"/>
     </row>
     <row r="298">
-      <c r="A298" s="27" t="n"/>
-      <c r="B298" s="28" t="n"/>
-      <c r="C298" s="29" t="n"/>
-      <c r="D298" s="28" t="n"/>
-      <c r="E298" s="28" t="n"/>
-      <c r="F298" s="28" t="n"/>
-      <c r="G298" s="28" t="n"/>
-      <c r="H298" s="28" t="n"/>
+      <c r="A298" s="25" t="n"/>
+      <c r="B298" s="26" t="n"/>
+      <c r="C298" s="10" t="n"/>
+      <c r="D298" s="26" t="n"/>
+      <c r="E298" s="26" t="n"/>
+      <c r="F298" s="26" t="n"/>
+      <c r="G298" s="26" t="n"/>
+      <c r="H298" s="26" t="n"/>
     </row>
     <row r="299">
-      <c r="A299" s="27" t="n"/>
-      <c r="B299" s="28" t="n"/>
-      <c r="C299" s="29" t="n"/>
-      <c r="D299" s="28" t="n"/>
-      <c r="E299" s="28" t="n"/>
-      <c r="F299" s="28" t="n"/>
-      <c r="G299" s="28" t="n"/>
-      <c r="H299" s="28" t="n"/>
+      <c r="A299" s="25" t="n"/>
+      <c r="B299" s="26" t="n"/>
+      <c r="C299" s="10" t="n"/>
+      <c r="D299" s="26" t="n"/>
+      <c r="E299" s="26" t="n"/>
+      <c r="F299" s="26" t="n"/>
+      <c r="G299" s="26" t="n"/>
+      <c r="H299" s="26" t="n"/>
     </row>
     <row r="300">
-      <c r="A300" s="27" t="n"/>
-      <c r="B300" s="28" t="n"/>
-      <c r="C300" s="29" t="n"/>
-      <c r="D300" s="28" t="n"/>
-      <c r="E300" s="28" t="n"/>
-      <c r="F300" s="28" t="n"/>
-      <c r="G300" s="28" t="n"/>
-      <c r="H300" s="28" t="n"/>
+      <c r="A300" s="25" t="n"/>
+      <c r="B300" s="26" t="n"/>
+      <c r="C300" s="10" t="n"/>
+      <c r="D300" s="26" t="n"/>
+      <c r="E300" s="26" t="n"/>
+      <c r="F300" s="26" t="n"/>
+      <c r="G300" s="26" t="n"/>
+      <c r="H300" s="26" t="n"/>
     </row>
     <row r="301">
-      <c r="A301" s="27" t="n"/>
-      <c r="B301" s="28" t="n"/>
-      <c r="C301" s="29" t="n"/>
-      <c r="D301" s="28" t="n"/>
-      <c r="E301" s="28" t="n"/>
-      <c r="F301" s="28" t="n"/>
-      <c r="G301" s="28" t="n"/>
-      <c r="H301" s="28" t="n"/>
+      <c r="A301" s="25" t="n"/>
+      <c r="B301" s="26" t="n"/>
+      <c r="C301" s="10" t="n"/>
+      <c r="D301" s="26" t="n"/>
+      <c r="E301" s="26" t="n"/>
+      <c r="F301" s="26" t="n"/>
+      <c r="G301" s="26" t="n"/>
+      <c r="H301" s="26" t="n"/>
     </row>
     <row r="302">
-      <c r="A302" s="27" t="n"/>
-      <c r="B302" s="28" t="n"/>
-      <c r="C302" s="29" t="n"/>
-      <c r="D302" s="28" t="n"/>
-      <c r="E302" s="28" t="n"/>
-      <c r="F302" s="28" t="n"/>
-      <c r="G302" s="28" t="n"/>
-      <c r="H302" s="28" t="n"/>
+      <c r="A302" s="25" t="n"/>
+      <c r="B302" s="26" t="n"/>
+      <c r="C302" s="10" t="n"/>
+      <c r="D302" s="26" t="n"/>
+      <c r="E302" s="26" t="n"/>
+      <c r="F302" s="26" t="n"/>
+      <c r="G302" s="26" t="n"/>
+      <c r="H302" s="26" t="n"/>
     </row>
     <row r="303">
-      <c r="A303" s="27" t="n"/>
-      <c r="B303" s="28" t="n"/>
-      <c r="C303" s="29" t="n"/>
-      <c r="D303" s="28" t="n"/>
-      <c r="E303" s="28" t="n"/>
-      <c r="F303" s="28" t="n"/>
-      <c r="G303" s="28" t="n"/>
-      <c r="H303" s="28" t="n"/>
+      <c r="A303" s="25" t="n"/>
+      <c r="B303" s="26" t="n"/>
+      <c r="C303" s="10" t="n"/>
+      <c r="D303" s="26" t="n"/>
+      <c r="E303" s="26" t="n"/>
+      <c r="F303" s="26" t="n"/>
+      <c r="G303" s="26" t="n"/>
+      <c r="H303" s="26" t="n"/>
     </row>
     <row r="304">
-      <c r="A304" s="27" t="n"/>
-      <c r="B304" s="28" t="n"/>
-      <c r="C304" s="29" t="n"/>
-      <c r="D304" s="28" t="n"/>
-      <c r="E304" s="28" t="n"/>
-      <c r="F304" s="28" t="n"/>
-      <c r="G304" s="28" t="n"/>
-      <c r="H304" s="28" t="n"/>
+      <c r="A304" s="25" t="n"/>
+      <c r="B304" s="26" t="n"/>
+      <c r="C304" s="10" t="n"/>
+      <c r="D304" s="26" t="n"/>
+      <c r="E304" s="26" t="n"/>
+      <c r="F304" s="26" t="n"/>
+      <c r="G304" s="26" t="n"/>
+      <c r="H304" s="26" t="n"/>
     </row>
     <row r="305">
-      <c r="A305" s="27" t="n"/>
-      <c r="B305" s="28" t="n"/>
-      <c r="C305" s="29" t="n"/>
-      <c r="D305" s="28" t="n"/>
-      <c r="E305" s="28" t="n"/>
-      <c r="F305" s="28" t="n"/>
-      <c r="G305" s="28" t="n"/>
-      <c r="H305" s="28" t="n"/>
+      <c r="A305" s="25" t="n"/>
+      <c r="B305" s="26" t="n"/>
+      <c r="C305" s="10" t="n"/>
+      <c r="D305" s="26" t="n"/>
+      <c r="E305" s="26" t="n"/>
+      <c r="F305" s="26" t="n"/>
+      <c r="G305" s="26" t="n"/>
+      <c r="H305" s="26" t="n"/>
     </row>
     <row r="306">
-      <c r="A306" s="27" t="n"/>
-      <c r="B306" s="28" t="n"/>
-      <c r="C306" s="29" t="n"/>
-      <c r="D306" s="28" t="n"/>
-      <c r="E306" s="28" t="n"/>
-      <c r="F306" s="28" t="n"/>
-      <c r="G306" s="28" t="n"/>
-      <c r="H306" s="28" t="n"/>
+      <c r="A306" s="25" t="n"/>
+      <c r="B306" s="26" t="n"/>
+      <c r="C306" s="10" t="n"/>
+      <c r="D306" s="26" t="n"/>
+      <c r="E306" s="26" t="n"/>
+      <c r="F306" s="26" t="n"/>
+      <c r="G306" s="26" t="n"/>
+      <c r="H306" s="26" t="n"/>
     </row>
     <row r="307">
-      <c r="A307" s="27" t="n"/>
-      <c r="B307" s="28" t="n"/>
-      <c r="C307" s="29" t="n"/>
-      <c r="D307" s="28" t="n"/>
-      <c r="E307" s="28" t="n"/>
-      <c r="F307" s="28" t="n"/>
-      <c r="G307" s="28" t="n"/>
-      <c r="H307" s="28" t="n"/>
+      <c r="A307" s="25" t="n"/>
+      <c r="B307" s="26" t="n"/>
+      <c r="C307" s="10" t="n"/>
+      <c r="D307" s="26" t="n"/>
+      <c r="E307" s="26" t="n"/>
+      <c r="F307" s="26" t="n"/>
+      <c r="G307" s="26" t="n"/>
+      <c r="H307" s="26" t="n"/>
     </row>
     <row r="308">
-      <c r="A308" s="27" t="n"/>
-      <c r="B308" s="28" t="n"/>
-      <c r="C308" s="29" t="n"/>
-      <c r="D308" s="28" t="n"/>
-      <c r="E308" s="28" t="n"/>
-      <c r="F308" s="28" t="n"/>
-      <c r="G308" s="28" t="n"/>
-      <c r="H308" s="28" t="n"/>
+      <c r="A308" s="25" t="n"/>
+      <c r="B308" s="26" t="n"/>
+      <c r="C308" s="10" t="n"/>
+      <c r="D308" s="26" t="n"/>
+      <c r="E308" s="26" t="n"/>
+      <c r="F308" s="26" t="n"/>
+      <c r="G308" s="26" t="n"/>
+      <c r="H308" s="26" t="n"/>
     </row>
     <row r="309">
-      <c r="A309" s="27" t="n"/>
-      <c r="B309" s="28" t="n"/>
-      <c r="C309" s="29" t="n"/>
-      <c r="D309" s="28" t="n"/>
-      <c r="E309" s="28" t="n"/>
-      <c r="F309" s="28" t="n"/>
-      <c r="G309" s="28" t="n"/>
-      <c r="H309" s="28" t="n"/>
+      <c r="A309" s="25" t="n"/>
+      <c r="B309" s="26" t="n"/>
+      <c r="C309" s="10" t="n"/>
+      <c r="D309" s="26" t="n"/>
+      <c r="E309" s="26" t="n"/>
+      <c r="F309" s="26" t="n"/>
+      <c r="G309" s="26" t="n"/>
+      <c r="H309" s="26" t="n"/>
     </row>
     <row r="310">
-      <c r="A310" s="27" t="n"/>
-      <c r="B310" s="28" t="n"/>
-      <c r="C310" s="29" t="n"/>
-      <c r="D310" s="28" t="n"/>
-      <c r="E310" s="28" t="n"/>
-      <c r="F310" s="28" t="n"/>
-      <c r="G310" s="28" t="n"/>
-      <c r="H310" s="28" t="n"/>
+      <c r="A310" s="25" t="n"/>
+      <c r="B310" s="26" t="n"/>
+      <c r="C310" s="10" t="n"/>
+      <c r="D310" s="26" t="n"/>
+      <c r="E310" s="26" t="n"/>
+      <c r="F310" s="26" t="n"/>
+      <c r="G310" s="26" t="n"/>
+      <c r="H310" s="26" t="n"/>
     </row>
     <row r="311">
-      <c r="A311" s="27" t="n"/>
-      <c r="B311" s="28" t="n"/>
-      <c r="C311" s="29" t="n"/>
-      <c r="D311" s="28" t="n"/>
-      <c r="E311" s="28" t="n"/>
-      <c r="F311" s="28" t="n"/>
-      <c r="G311" s="28" t="n"/>
-      <c r="H311" s="28" t="n"/>
+      <c r="A311" s="25" t="n"/>
+      <c r="B311" s="26" t="n"/>
+      <c r="C311" s="10" t="n"/>
+      <c r="D311" s="26" t="n"/>
+      <c r="E311" s="26" t="n"/>
+      <c r="F311" s="26" t="n"/>
+      <c r="G311" s="26" t="n"/>
+      <c r="H311" s="26" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:H311"/>
   <mergeCells count="1">
-    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A3:H3"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation sqref="D5:D311" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -10044,19 +10011,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>MONEY</t>
         </is>
@@ -10072,7 +10042,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Set once. Touch rarely. This Month reads from here.</t>
+          <t>Set once. Bills marked ON auto-subtract on This Month.</t>
         </is>
       </c>
     </row>
@@ -10087,6 +10057,11 @@
           <t>INCOME</t>
         </is>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>BILLS BY CATEGORY</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -10109,6 +10084,16 @@
           <t>AMOUNT</t>
         </is>
       </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>CATEGORY</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -10116,7 +10101,7 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B6" s="24" t="n">
+      <c r="B6" s="27" t="n">
         <v>1120</v>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -10124,8 +10109,17 @@
           <t>Paycheck 1</t>
         </is>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="27" t="n">
         <v>1615</v>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="I6" s="13">
+        <f>SUMIF($G$24:$G$40,H6,$F$24:$F$40)</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -10134,7 +10128,7 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="27" t="n">
         <v>80</v>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -10142,8 +10136,17 @@
           <t>Paycheck 2</t>
         </is>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="27" t="n">
         <v>1615</v>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="I7" s="13">
+        <f>SUMIF($G$24:$G$40,H7,$F$24:$F$40)</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -10152,7 +10155,7 @@
           <t>Subscriptions</t>
         </is>
       </c>
-      <c r="B8" s="24" t="n">
+      <c r="B8" s="27" t="n">
         <v>254</v>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -10160,8 +10163,17 @@
           <t>Alliance Stipend</t>
         </is>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="27" t="n">
         <v>75</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>Subscriptions</t>
+        </is>
+      </c>
+      <c r="I8" s="13">
+        <f>SUMIF($G$24:$G$40,H8,$F$24:$F$40)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -10170,7 +10182,7 @@
           <t>Grocery</t>
         </is>
       </c>
-      <c r="B9" s="24" t="n">
+      <c r="B9" s="27" t="n">
         <v>400</v>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -10178,8 +10190,17 @@
           <t>Extra income</t>
         </is>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="27" t="n">
         <v>0</v>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="I9" s="13">
+        <f>SUMIF($G$24:$G$40,H9,$F$24:$F$40)</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -10188,8 +10209,17 @@
           <t>Dining</t>
         </is>
       </c>
-      <c r="B10" s="24" t="n">
+      <c r="B10" s="27" t="n">
         <v>200</v>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>Dining</t>
+        </is>
+      </c>
+      <c r="I10" s="13">
+        <f>SUMIF($G$24:$G$40,H10,$F$24:$F$40)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -10198,7 +10228,7 @@
           <t>Transit</t>
         </is>
       </c>
-      <c r="B11" s="24" t="n">
+      <c r="B11" s="27" t="n">
         <v>60</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -10206,10 +10236,19 @@
           <t>EXPECTED / MONTH</t>
         </is>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="28">
         <f>SUM(E6:E9)</f>
         <v/>
       </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>Transit</t>
+        </is>
+      </c>
+      <c r="I11" s="13">
+        <f>SUMIF($G$24:$G$40,H11,$F$24:$F$40)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
@@ -10217,8 +10256,17 @@
           <t>Shopping</t>
         </is>
       </c>
-      <c r="B12" s="24" t="n">
+      <c r="B12" s="27" t="n">
         <v>150</v>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>Shopping</t>
+        </is>
+      </c>
+      <c r="I12" s="13">
+        <f>SUMIF($G$24:$G$40,H12,$F$24:$F$40)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -10227,8 +10275,17 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="27" t="n">
         <v>75</v>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="I13" s="13">
+        <f>SUMIF($G$24:$G$40,H13,$F$24:$F$40)</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -10237,8 +10294,17 @@
           <t>Home</t>
         </is>
       </c>
-      <c r="B14" s="24" t="n">
+      <c r="B14" s="27" t="n">
         <v>50</v>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="I14" s="13">
+        <f>SUMIF($G$24:$G$40,H14,$F$24:$F$40)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -10247,8 +10313,17 @@
           <t>Health</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n">
+      <c r="B15" s="27" t="n">
         <v>20</v>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="I15" s="13">
+        <f>SUMIF($G$24:$G$40,H15,$F$24:$F$40)</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -10257,8 +10332,17 @@
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="B16" s="24" t="n">
+      <c r="B16" s="27" t="n">
         <v>40</v>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="I16" s="13">
+        <f>SUMIF($G$24:$G$40,H16,$F$24:$F$40)</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -10267,8 +10351,17 @@
           <t>Savings</t>
         </is>
       </c>
-      <c r="B17" s="24" t="n">
+      <c r="B17" s="27" t="n">
         <v>200</v>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>Savings</t>
+        </is>
+      </c>
+      <c r="I17" s="13">
+        <f>SUMIF($G$24:$G$40,H17,$F$24:$F$40)</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -10277,17 +10370,26 @@
           <t>Misc</t>
         </is>
       </c>
-      <c r="B18" s="24" t="n">
+      <c r="B18" s="27" t="n">
         <v>100</v>
       </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="I18" s="13">
+        <f>SUMIF($G$24:$G$40,H18,$F$24:$F$40)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="16">
         <f>SUM(B6:B18)</f>
         <v/>
       </c>
@@ -10298,11 +10400,22 @@
           <t>EXPECTED INCOME REF</t>
         </is>
       </c>
-      <c r="B20" s="32">
+      <c r="B20" s="29">
         <f>E11</f>
         <v/>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>BILLS AUTO-COUNT (monthly)</t>
+        </is>
+      </c>
+      <c r="B21" s="30">
+        <f>SUM(F24:F40)</f>
+        <v/>
+      </c>
+    </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
@@ -10336,6 +10449,16 @@
           <t>ON</t>
         </is>
       </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>MONTHLY</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>CATEGORY</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
@@ -10343,22 +10466,31 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B24" s="30" t="n">
+      <c r="B24" s="27" t="n">
         <v>1120</v>
       </c>
-      <c r="C24" s="33" t="inlineStr">
+      <c r="C24" s="31" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="D24" s="33" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="D24" s="31" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F24" s="13">
+        <f>IF(E24&lt;&gt;"Y",0,IF(C24="Annually",B24/12,IF(C24="Quarterly",B24/3,IF(C24="Weekly",B24*52/12,IF(C24="Biweekly",B24*26/12,B24)))))</f>
+        <v/>
+      </c>
+      <c r="G24" s="32" t="inlineStr">
+        <is>
+          <t>Rent</t>
         </is>
       </c>
     </row>
@@ -10368,22 +10500,31 @@
           <t>Electricity (ConEd)</t>
         </is>
       </c>
-      <c r="B25" s="30" t="n">
+      <c r="B25" s="27" t="n">
         <v>52</v>
       </c>
-      <c r="C25" s="33" t="inlineStr">
+      <c r="C25" s="31" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="D25" s="33" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="D25" s="31" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F25" s="13">
+        <f>IF(E25&lt;&gt;"Y",0,IF(C25="Annually",B25/12,IF(C25="Quarterly",B25/3,IF(C25="Weekly",B25*52/12,IF(C25="Biweekly",B25*26/12,B25)))))</f>
+        <v/>
+      </c>
+      <c r="G25" s="32" t="inlineStr">
+        <is>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
@@ -10393,22 +10534,31 @@
           <t>Gas (National Grid)</t>
         </is>
       </c>
-      <c r="B26" s="30" t="n">
+      <c r="B26" s="27" t="n">
         <v>26</v>
       </c>
-      <c r="C26" s="33" t="inlineStr">
+      <c r="C26" s="31" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="D26" s="33" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="D26" s="31" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F26" s="13">
+        <f>IF(E26&lt;&gt;"Y",0,IF(C26="Annually",B26/12,IF(C26="Quarterly",B26/3,IF(C26="Weekly",B26*52/12,IF(C26="Biweekly",B26*26/12,B26)))))</f>
+        <v/>
+      </c>
+      <c r="G26" s="32" t="inlineStr">
+        <is>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
@@ -10418,22 +10568,31 @@
           <t>Transit</t>
         </is>
       </c>
-      <c r="B27" s="30" t="n">
+      <c r="B27" s="27" t="n">
         <v>60</v>
       </c>
-      <c r="C27" s="33" t="inlineStr">
+      <c r="C27" s="31" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="D27" s="33" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F27" s="13">
+        <f>IF(E27&lt;&gt;"Y",0,IF(C27="Annually",B27/12,IF(C27="Quarterly",B27/3,IF(C27="Weekly",B27*52/12,IF(C27="Biweekly",B27*26/12,B27)))))</f>
+        <v/>
+      </c>
+      <c r="G27" s="32" t="inlineStr">
+        <is>
+          <t>Transit</t>
         </is>
       </c>
     </row>
@@ -10443,22 +10602,31 @@
           <t>Savings transfer</t>
         </is>
       </c>
-      <c r="B28" s="30" t="n">
+      <c r="B28" s="27" t="n">
         <v>200</v>
       </c>
-      <c r="C28" s="33" t="inlineStr">
+      <c r="C28" s="31" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="D28" s="33" t="inlineStr">
+      <c r="D28" s="31" t="inlineStr">
         <is>
           <t>Ally Savings</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E28" s="18" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F28" s="13">
+        <f>IF(E28&lt;&gt;"Y",0,IF(C28="Annually",B28/12,IF(C28="Quarterly",B28/3,IF(C28="Weekly",B28*52/12,IF(C28="Biweekly",B28*26/12,B28)))))</f>
+        <v/>
+      </c>
+      <c r="G28" s="32" t="inlineStr">
+        <is>
+          <t>Savings</t>
         </is>
       </c>
     </row>
@@ -10468,22 +10636,31 @@
           <t>Amazon Prime</t>
         </is>
       </c>
-      <c r="B29" s="30" t="n">
+      <c r="B29" s="27" t="n">
         <v>16.32</v>
       </c>
-      <c r="C29" s="33" t="inlineStr">
+      <c r="C29" s="31" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="D29" s="33" t="inlineStr">
+      <c r="D29" s="31" t="inlineStr">
         <is>
           <t>Bilt</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E29" s="18" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F29" s="13">
+        <f>IF(E29&lt;&gt;"Y",0,IF(C29="Annually",B29/12,IF(C29="Quarterly",B29/3,IF(C29="Weekly",B29*52/12,IF(C29="Biweekly",B29*26/12,B29)))))</f>
+        <v/>
+      </c>
+      <c r="G29" s="32" t="inlineStr">
+        <is>
+          <t>Subscriptions</t>
         </is>
       </c>
     </row>
@@ -10493,22 +10670,31 @@
           <t>Splice</t>
         </is>
       </c>
-      <c r="B30" s="30" t="n">
+      <c r="B30" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="C30" s="33" t="inlineStr">
+      <c r="C30" s="31" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="D30" s="33" t="inlineStr">
+      <c r="D30" s="31" t="inlineStr">
         <is>
           <t>Bilt</t>
         </is>
       </c>
-      <c r="E30" s="23" t="inlineStr">
+      <c r="E30" s="18" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F30" s="13">
+        <f>IF(E30&lt;&gt;"Y",0,IF(C30="Annually",B30/12,IF(C30="Quarterly",B30/3,IF(C30="Weekly",B30*52/12,IF(C30="Biweekly",B30*26/12,B30)))))</f>
+        <v/>
+      </c>
+      <c r="G30" s="32" t="inlineStr">
+        <is>
+          <t>Subscriptions</t>
         </is>
       </c>
     </row>
@@ -10518,22 +10704,31 @@
           <t>iCloud</t>
         </is>
       </c>
-      <c r="B31" s="30" t="n">
+      <c r="B31" s="27" t="n">
         <v>2.99</v>
       </c>
-      <c r="C31" s="33" t="inlineStr">
+      <c r="C31" s="31" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="D31" s="33" t="inlineStr">
+      <c r="D31" s="31" t="inlineStr">
         <is>
           <t>Apple Card</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E31" s="18" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F31" s="13">
+        <f>IF(E31&lt;&gt;"Y",0,IF(C31="Annually",B31/12,IF(C31="Quarterly",B31/3,IF(C31="Weekly",B31*52/12,IF(C31="Biweekly",B31*26/12,B31)))))</f>
+        <v/>
+      </c>
+      <c r="G31" s="32" t="inlineStr">
+        <is>
+          <t>Subscriptions</t>
         </is>
       </c>
     </row>
@@ -10543,22 +10738,31 @@
           <t>Tidal</t>
         </is>
       </c>
-      <c r="B32" s="30" t="n">
+      <c r="B32" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="C32" s="33" t="inlineStr">
+      <c r="C32" s="31" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="D32" s="33" t="inlineStr">
+      <c r="D32" s="31" t="inlineStr">
         <is>
           <t>Bilt</t>
         </is>
       </c>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="E32" s="18" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F32" s="13">
+        <f>IF(E32&lt;&gt;"Y",0,IF(C32="Annually",B32/12,IF(C32="Quarterly",B32/3,IF(C32="Weekly",B32*52/12,IF(C32="Biweekly",B32*26/12,B32)))))</f>
+        <v/>
+      </c>
+      <c r="G32" s="32" t="inlineStr">
+        <is>
+          <t>Subscriptions</t>
         </is>
       </c>
     </row>
@@ -10568,22 +10772,31 @@
           <t>Internet</t>
         </is>
       </c>
-      <c r="B33" s="30" t="n">
+      <c r="B33" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="C33" s="33" t="inlineStr">
+      <c r="C33" s="31" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="D33" s="33" t="inlineStr">
+      <c r="D33" s="31" t="inlineStr">
         <is>
           <t>Bilt</t>
         </is>
       </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="E33" s="18" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F33" s="13">
+        <f>IF(E33&lt;&gt;"Y",0,IF(C33="Annually",B33/12,IF(C33="Quarterly",B33/3,IF(C33="Weekly",B33*52/12,IF(C33="Biweekly",B33*26/12,B33)))))</f>
+        <v/>
+      </c>
+      <c r="G33" s="32" t="inlineStr">
+        <is>
+          <t>Subscriptions</t>
         </is>
       </c>
     </row>
@@ -10593,22 +10806,31 @@
           <t>Absolute Power</t>
         </is>
       </c>
-      <c r="B34" s="30" t="n">
+      <c r="B34" s="27" t="n">
         <v>53.25</v>
       </c>
-      <c r="C34" s="33" t="inlineStr">
+      <c r="C34" s="31" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="D34" s="33" t="inlineStr">
+      <c r="D34" s="31" t="inlineStr">
         <is>
           <t>Bilt</t>
         </is>
       </c>
-      <c r="E34" s="23" t="inlineStr">
+      <c r="E34" s="18" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F34" s="13">
+        <f>IF(E34&lt;&gt;"Y",0,IF(C34="Annually",B34/12,IF(C34="Quarterly",B34/3,IF(C34="Weekly",B34*52/12,IF(C34="Biweekly",B34*26/12,B34)))))</f>
+        <v/>
+      </c>
+      <c r="G34" s="32" t="inlineStr">
+        <is>
+          <t>Subscriptions</t>
         </is>
       </c>
     </row>
@@ -10618,22 +10840,31 @@
           <t>finasteride</t>
         </is>
       </c>
-      <c r="B35" s="30" t="n">
+      <c r="B35" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="C35" s="33" t="inlineStr">
+      <c r="C35" s="31" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="D35" s="33" t="inlineStr">
+      <c r="D35" s="31" t="inlineStr">
         <is>
           <t>Bilt</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E35" s="18" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F35" s="13">
+        <f>IF(E35&lt;&gt;"Y",0,IF(C35="Annually",B35/12,IF(C35="Quarterly",B35/3,IF(C35="Weekly",B35*52/12,IF(C35="Biweekly",B35*26/12,B35)))))</f>
+        <v/>
+      </c>
+      <c r="G35" s="32" t="inlineStr">
+        <is>
+          <t>Subscriptions</t>
         </is>
       </c>
     </row>
@@ -10643,22 +10874,31 @@
           <t>Google Cloud</t>
         </is>
       </c>
-      <c r="B36" s="30" t="n">
+      <c r="B36" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="C36" s="33" t="inlineStr">
+      <c r="C36" s="31" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="D36" s="33" t="inlineStr">
-        <is>
-          <t>Checking</t>
-        </is>
-      </c>
-      <c r="E36" s="23" t="inlineStr">
+      <c r="D36" s="31" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F36" s="13">
+        <f>IF(E36&lt;&gt;"Y",0,IF(C36="Annually",B36/12,IF(C36="Quarterly",B36/3,IF(C36="Weekly",B36*52/12,IF(C36="Biweekly",B36*26/12,B36)))))</f>
+        <v/>
+      </c>
+      <c r="G36" s="32" t="inlineStr">
+        <is>
+          <t>Subscriptions</t>
         </is>
       </c>
     </row>
@@ -10668,22 +10908,31 @@
           <t>CursorAI</t>
         </is>
       </c>
-      <c r="B37" s="30" t="n">
+      <c r="B37" s="27" t="n">
         <v>60</v>
       </c>
-      <c r="C37" s="33" t="inlineStr">
+      <c r="C37" s="31" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="D37" s="33" t="inlineStr">
+      <c r="D37" s="31" t="inlineStr">
         <is>
           <t>Bilt</t>
         </is>
       </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="E37" s="18" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F37" s="13">
+        <f>IF(E37&lt;&gt;"Y",0,IF(C37="Annually",B37/12,IF(C37="Quarterly",B37/3,IF(C37="Weekly",B37*52/12,IF(C37="Biweekly",B37*26/12,B37)))))</f>
+        <v/>
+      </c>
+      <c r="G37" s="32" t="inlineStr">
+        <is>
+          <t>Subscriptions</t>
         </is>
       </c>
     </row>
@@ -10693,22 +10942,31 @@
           <t>Soundiiz</t>
         </is>
       </c>
-      <c r="B38" s="30" t="n">
+      <c r="B38" s="27" t="n">
         <v>24</v>
       </c>
-      <c r="C38" s="33" t="inlineStr">
+      <c r="C38" s="31" t="inlineStr">
         <is>
           <t>Annually</t>
         </is>
       </c>
-      <c r="D38" s="33" t="inlineStr">
+      <c r="D38" s="31" t="inlineStr">
         <is>
           <t>Bilt</t>
         </is>
       </c>
-      <c r="E38" s="23" t="inlineStr">
+      <c r="E38" s="18" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="F38" s="13">
+        <f>IF(E38&lt;&gt;"Y",0,IF(C38="Annually",B38/12,IF(C38="Quarterly",B38/3,IF(C38="Weekly",B38*52/12,IF(C38="Biweekly",B38*26/12,B38)))))</f>
+        <v/>
+      </c>
+      <c r="G38" s="32" t="inlineStr">
+        <is>
+          <t>Subscriptions</t>
         </is>
       </c>
     </row>
@@ -10718,46 +10976,88 @@
           <t>Healthy Vocal</t>
         </is>
       </c>
-      <c r="B39" s="30" t="n">
+      <c r="B39" s="27" t="n">
         <v>40</v>
       </c>
-      <c r="C39" s="33" t="inlineStr">
+      <c r="C39" s="31" t="inlineStr">
         <is>
           <t>Annually</t>
         </is>
       </c>
-      <c r="D39" s="33" t="inlineStr">
+      <c r="D39" s="31" t="inlineStr">
         <is>
           <t>Bilt</t>
         </is>
       </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="E39" s="18" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="F39" s="13">
+        <f>IF(E39&lt;&gt;"Y",0,IF(C39="Annually",B39/12,IF(C39="Quarterly",B39/3,IF(C39="Weekly",B39*52/12,IF(C39="Biweekly",B39*26/12,B39)))))</f>
+        <v/>
+      </c>
+      <c r="G39" s="32" t="inlineStr">
+        <is>
+          <t>Subscriptions</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="38" t="inlineStr">
-        <is>
-          <t>When a recurring charge hits, log it on Log. This list is the checklist — not the counter.</t>
-        </is>
-      </c>
-      <c r="B40" s="34" t="n"/>
-      <c r="C40" s="34" t="n"/>
-      <c r="D40" s="34" t="n"/>
-      <c r="E40" s="34" t="n"/>
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>Apple Dev program</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="n">
+        <v>99</v>
+      </c>
+      <c r="C40" s="31" t="inlineStr">
+        <is>
+          <t>Annually</t>
+        </is>
+      </c>
+      <c r="D40" s="31" t="inlineStr">
+        <is>
+          <t>Bilt</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F40" s="13">
+        <f>IF(E40&lt;&gt;"Y",0,IF(C40="Annually",B40/12,IF(C40="Quarterly",B40/3,IF(C40="Weekly",B40*52/12,IF(C40="Biweekly",B40*26/12,B40)))))</f>
+        <v/>
+      </c>
+      <c r="G40" s="32" t="inlineStr">
+        <is>
+          <t>Subscriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>ON = auto-subtracted. Do not log these on Log — only day-to-day spends.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A42:G42"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="E24:E50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation sqref="C24:C50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Lists!$E$1:$E$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="G24:G50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lists!$A$1:$A$15</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10779,7 +11079,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>MONEY</t>
         </is>
@@ -10822,10 +11122,10 @@
           <t>Checking</t>
         </is>
       </c>
-      <c r="B5" s="30" t="n">
+      <c r="B5" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="30" t="n">
+      <c r="C5" s="27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10835,10 +11135,10 @@
           <t>Bilt</t>
         </is>
       </c>
-      <c r="B6" s="30" t="n">
+      <c r="B6" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="30" t="n">
+      <c r="C6" s="27" t="n">
         <v>328.5</v>
       </c>
     </row>
@@ -10848,10 +11148,10 @@
           <t>Apple Card</t>
         </is>
       </c>
-      <c r="B7" s="30" t="n">
+      <c r="B7" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="30" t="n">
+      <c r="C7" s="27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10861,10 +11161,10 @@
           <t>USAA Credit Card</t>
         </is>
       </c>
-      <c r="B8" s="30" t="n">
+      <c r="B8" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="30" t="n">
+      <c r="C8" s="27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10874,10 +11174,10 @@
           <t>PayPal</t>
         </is>
       </c>
-      <c r="B9" s="30" t="n">
+      <c r="B9" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="30" t="n">
+      <c r="C9" s="27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10887,10 +11187,10 @@
           <t>Klarna</t>
         </is>
       </c>
-      <c r="B10" s="30" t="n">
+      <c r="B10" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="30" t="n">
+      <c r="C10" s="27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10900,10 +11200,10 @@
           <t>Ally Savings</t>
         </is>
       </c>
-      <c r="B11" s="30" t="n">
+      <c r="B11" s="27" t="n">
         <v>8525.549999999999</v>
       </c>
-      <c r="C11" s="30" t="n">
+      <c r="C11" s="27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10913,10 +11213,10 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="B12" s="30" t="n">
+      <c r="B12" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="30" t="n">
+      <c r="C12" s="27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10926,10 +11226,10 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="B13" s="30" t="n">
+      <c r="B13" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="30" t="n">
+      <c r="C13" s="27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10939,7 +11239,7 @@
           <t>OWED TOTAL</t>
         </is>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="28">
         <f>SUM(C5:C13)</f>
         <v/>
       </c>
@@ -10950,7 +11250,7 @@
           <t>CASH-LIKE</t>
         </is>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="14">
         <f>SUM(B5:B13)</f>
         <v/>
       </c>
